--- a/outputs/research_data_enrichment/Forschungsdaten_2024-heute_3_Sheets_konsolidiert_geprueft.xlsx
+++ b/outputs/research_data_enrichment/Forschungsdaten_2024-heute_3_Sheets_konsolidiert_geprueft.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Übersicht" sheetId="1" r:id="R597e2ffc7c454a30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forschungsdaten" sheetId="2" r:id="R4b6eba3876b74760"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forschungsgruppen" sheetId="3" r:id="R136cd4ea0bd14fac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Übersicht" sheetId="1" r:id="R17c0037bd173470d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forschungsdaten" sheetId="2" r:id="Re344329f36494409"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forschungsgruppen" sheetId="3" r:id="R51d1768a4f474d65"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -606,7 +606,7 @@
         <x:v>Forschungsdaten: ja</x:v>
       </x:c>
       <x:c r="B5" s="14" t="n">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -614,7 +614,7 @@
         <x:v>Forschungsdaten: nein</x:v>
       </x:c>
       <x:c r="B6" s="14" t="n">
-        <x:v>230</x:v>
+        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -622,7 +622,7 @@
         <x:v>Abdeckungsquote</x:v>
       </x:c>
       <x:c r="B7" s="15" t="n">
-        <x:v>0.17562724014336917</x:v>
+        <x:v>0.1827956989247312</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -630,7 +630,7 @@
         <x:v>Verifizierte Forschungsdatenlinks</x:v>
       </x:c>
       <x:c r="B8" s="14" t="n">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -702,7 +702,7 @@
         <x:v>Quellenpriorität</x:v>
       </x:c>
       <x:c r="B17" s="23" t="str">
-        <x:v>1. PuRe; 2. explizite Data-Availability-Aussagen; 3. DataCite/OSF/B2FIND mit engem Titel- oder Autor:innenbezug</x:v>
+        <x:v>1. gepflegte PuRe-Links; 2. explizite Data-Availability-Aussagen; 3. Repositorien mit engem Titel-/Autor:innenbezug und geprüften Datendateien</x:v>
       </x:c>
       <x:c r="C17" s="23" t="str"/>
       <x:c r="D17" s="23" t="str"/>
@@ -723,10 +723,10 @@
     </x:row>
     <x:row r="19" ht="42" customHeight="1">
       <x:c r="A19" s="22" t="str">
-        <x:v>OSF-Prüfung</x:v>
+        <x:v>Dateiprüfung</x:v>
       </x:c>
       <x:c r="B19" s="23" t="str">
-        <x:v>Dateistruktur rekursiv über OSF-API; mindestens eine erkennbare Datendatei oder ein expliziter Data-Availability-Nachweis</x:v>
+        <x:v>OSF- und GitHub-Dateibäume rekursiv über die jeweilige API; Zenodo-Archive werden bis auf Dateiebene geprüft</x:v>
       </x:c>
       <x:c r="C19" s="23" t="str"/>
       <x:c r="D19" s="23" t="str"/>
@@ -4019,7 +4019,7 @@
         <x:v>HTTP</x:v>
       </x:c>
       <x:c r="AZ33" s="31" t="str">
-        <x:v>GitHub-README mit exaktem Publikationstitel und geprüften Datendateien</x:v>
+        <x:v>GitHub-README mit exaktem Publikationstitel und geprüften Datendateien; 55 Datendatei(en) über GitHub-API bestätigt</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="34" customHeight="1">
@@ -13466,7 +13466,7 @@
         <x:v>HTTP</x:v>
       </x:c>
       <x:c r="AZ142" s="31" t="str">
-        <x:v>GitHub-README mit exaktem Publikationstitel und geprüften Datendateien</x:v>
+        <x:v>GitHub-README mit exaktem Publikationstitel und geprüften Datendateien; 7424 Datendatei(en) über GitHub-API bestätigt</x:v>
       </x:c>
     </x:row>
     <x:row r="143" ht="34" customHeight="1">
@@ -14948,19 +14948,27 @@
       <x:c r="J160" s="31" t="str">
         <x:v>no</x:v>
       </x:c>
-      <x:c r="K160" s="33" t="str">
-        <x:v>nein</x:v>
+      <x:c r="K160" s="32" t="str">
+        <x:v>ja</x:v>
       </x:c>
       <x:c r="L160" s="41" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M160" s="31" t="str">
-        <x:v>kein verifizierter Datenlink</x:v>
-      </x:c>
-      <x:c r="N160" s="37" t="str"/>
-      <x:c r="O160" s="31" t="str"/>
-      <x:c r="P160" s="31" t="str"/>
-      <x:c r="Q160" s="31" t="str"/>
+        <x:v>offen</x:v>
+      </x:c>
+      <x:c r="N160" s="37" t="str">
+        <x:v>https://github.com/nbreznau/how_many_replicators</x:v>
+      </x:c>
+      <x:c r="O160" s="31" t="str">
+        <x:v>Provider</x:v>
+      </x:c>
+      <x:c r="P160" s="31" t="str">
+        <x:v>offen</x:v>
+      </x:c>
+      <x:c r="Q160" s="31" t="str">
+        <x:v>HTTP 200; HTTP</x:v>
+      </x:c>
       <x:c r="R160" s="37" t="str"/>
       <x:c r="S160" s="31" t="str"/>
       <x:c r="T160" s="31" t="str"/>
@@ -14997,10 +15005,10 @@
         <x:v>2026-07-15</x:v>
       </x:c>
       <x:c r="AY160" s="31" t="str">
-        <x:v>HTTP + Playwright-Audit</x:v>
+        <x:v>HTTP</x:v>
       </x:c>
       <x:c r="AZ160" s="31" t="str">
-        <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
+        <x:v>Link aus expliziter Data-Availability-Statement; 202 Datendatei(en) über GitHub-API bestätigt</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="34" customHeight="1">
@@ -23402,19 +23410,27 @@
       <x:c r="J258" s="31" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="K258" s="33" t="str">
-        <x:v>nein</x:v>
+      <x:c r="K258" s="32" t="str">
+        <x:v>ja</x:v>
       </x:c>
       <x:c r="L258" s="41" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M258" s="31" t="str">
-        <x:v>kein verifizierter Datenlink</x:v>
-      </x:c>
-      <x:c r="N258" s="37" t="str"/>
-      <x:c r="O258" s="31" t="str"/>
-      <x:c r="P258" s="31" t="str"/>
-      <x:c r="Q258" s="31" t="str"/>
+        <x:v>offen</x:v>
+      </x:c>
+      <x:c r="N258" s="37" t="str">
+        <x:v>https://zenodo.org/records/10438859</x:v>
+      </x:c>
+      <x:c r="O258" s="31" t="str">
+        <x:v>Provider</x:v>
+      </x:c>
+      <x:c r="P258" s="31" t="str">
+        <x:v>offen</x:v>
+      </x:c>
+      <x:c r="Q258" s="31" t="str">
+        <x:v>HTTP 200; HTTP</x:v>
+      </x:c>
       <x:c r="R258" s="37" t="str"/>
       <x:c r="S258" s="31" t="str"/>
       <x:c r="T258" s="31" t="str"/>
@@ -23451,10 +23467,10 @@
         <x:v>2026-07-15</x:v>
       </x:c>
       <x:c r="AY258" s="31" t="str">
-        <x:v>HTTP + Playwright-Audit</x:v>
+        <x:v>HTTP</x:v>
       </x:c>
       <x:c r="AZ258" s="31" t="str">
-        <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
+        <x:v>Zenodo-Replikationspaket mit Titel-/Autor:innen-Match und geprüften Datendateien</x:v>
       </x:c>
     </x:row>
     <x:row r="259" ht="34" customHeight="1">
@@ -25344,7 +25360,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b9cfc2a5bd847f3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a17a9d77f2d4de0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25427,19 +25443,19 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="C5" s="31" t="n">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D5" s="31" t="n">
-        <x:v>100</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E5" s="49" t="n">
-        <x:v>0.15254237288135594</x:v>
+        <x:v>0.16101694915254236</x:v>
       </x:c>
       <x:c r="F5" s="31" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G5" s="31" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="28" customHeight="1">
@@ -25611,13 +25627,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C13" s="34" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D13" s="34" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D13" s="34" t="n">
-        <x:v>2</x:v>
-      </x:c>
       <x:c r="E13" s="50" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
       <x:c r="F13" s="34" t="n">
         <x:v>0</x:v>
@@ -25659,7 +25675,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4c3ee62b1474b71"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff384e42b90b4a7f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/research_data_enrichment/Forschungsdaten_2024-heute_3_Sheets_konsolidiert_geprueft.xlsx
+++ b/outputs/research_data_enrichment/Forschungsdaten_2024-heute_3_Sheets_konsolidiert_geprueft.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Übersicht" sheetId="1" r:id="R17c0037bd173470d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forschungsdaten" sheetId="2" r:id="Re344329f36494409"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forschungsgruppen" sheetId="3" r:id="R51d1768a4f474d65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Übersicht" sheetId="1" r:id="R1290edaebf634759"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forschungsdaten" sheetId="2" r:id="Rd7a69ad6e70d4438"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forschungsgruppen" sheetId="3" r:id="R990fdc6efef6495c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -606,7 +606,7 @@
         <x:v>Forschungsdaten: ja</x:v>
       </x:c>
       <x:c r="B5" s="14" t="n">
-        <x:v>51</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -614,7 +614,7 @@
         <x:v>Forschungsdaten: nein</x:v>
       </x:c>
       <x:c r="B6" s="14" t="n">
-        <x:v>228</x:v>
+        <x:v>219</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -622,7 +622,7 @@
         <x:v>Abdeckungsquote</x:v>
       </x:c>
       <x:c r="B7" s="15" t="n">
-        <x:v>0.1827956989247312</x:v>
+        <x:v>0.21505376344086022</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -630,7 +630,7 @@
         <x:v>Verifizierte Forschungsdatenlinks</x:v>
       </x:c>
       <x:c r="B8" s="14" t="n">
-        <x:v>76</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -750,7 +750,7 @@
         <x:v>Zugang</x:v>
       </x:c>
       <x:c r="B21" s="23" t="str">
-        <x:v>Paywall, Login, Embargo und Zugriffsbeschränkung erscheinen je Link in einer eigenen Spalte</x:v>
+        <x:v>Paywall, Login, Embargo, Zustimmungspflichten und View-only-Zugänge erscheinen je Link in einer eigenen Spalte</x:v>
       </x:c>
       <x:c r="C21" s="23" t="str"/>
       <x:c r="D21" s="23" t="str"/>
@@ -786,7 +786,7 @@
         <x:v>Gelb</x:v>
       </x:c>
       <x:c r="B26" s="14" t="str">
-        <x:v>Paywall, Login, Embargo oder Zugriffsbeschränkung</x:v>
+        <x:v>Paywall, Login, Embargo, Zustimmungspflicht oder View-only-Zugang</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -1587,27 +1587,35 @@
         <x:v>ja</x:v>
       </x:c>
       <x:c r="L7" s="41" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="M7" s="31" t="str">
-        <x:v>offen</x:v>
+        <x:v>Paywall/Login oder Zugriffsschutz; offen</x:v>
       </x:c>
       <x:c r="N7" s="37" t="str">
-        <x:v>https://dataverse.harvard.edu/dataset.xhtml?persistentId=doi:10.7910/DVN/DCSR0N</x:v>
+        <x:v>https://dataverse.harvard.edu/citation?persistentId=doi:10.7910/DVN/DCSR0N</x:v>
       </x:c>
       <x:c r="O7" s="31" t="str">
         <x:v>PuRe</x:v>
       </x:c>
-      <x:c r="P7" s="31" t="str">
+      <x:c r="P7" s="39" t="str">
+        <x:v>Paywall/Login oder Zugriffsschutz</x:v>
+      </x:c>
+      <x:c r="Q7" s="31" t="str">
+        <x:v>HTTP 403; Playwright</x:v>
+      </x:c>
+      <x:c r="R7" s="37" t="str">
+        <x:v>https://dataverse.harvard.edu/dataset.xhtml?persistentId=doi:10.7910/DVN/DCSR0N</x:v>
+      </x:c>
+      <x:c r="S7" s="31" t="str">
+        <x:v>Provider</x:v>
+      </x:c>
+      <x:c r="T7" s="31" t="str">
         <x:v>offen</x:v>
       </x:c>
-      <x:c r="Q7" s="31" t="str">
+      <x:c r="U7" s="31" t="str">
         <x:v>HTTP 202; Playwright</x:v>
       </x:c>
-      <x:c r="R7" s="37" t="str"/>
-      <x:c r="S7" s="31" t="str"/>
-      <x:c r="T7" s="31" t="str"/>
-      <x:c r="U7" s="31" t="str"/>
       <x:c r="V7" s="37" t="str"/>
       <x:c r="W7" s="31" t="str"/>
       <x:c r="X7" s="31" t="str"/>
@@ -1643,7 +1651,7 @@
         <x:v>Playwright</x:v>
       </x:c>
       <x:c r="AZ7" s="31" t="str">
-        <x:v>Kuratiertes PuRe-Forschungsdatenfeld</x:v>
+        <x:v>Kuratiertes PuRe-Forschungsdatenfeld; Landingpage antwortet mit HTTP 403 und ist zugriffsgeschützt; Titel-/Autor:innen-Match (1.00)</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="34" customHeight="1">
@@ -2186,7 +2194,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="M13" s="31" t="str">
-        <x:v>offen</x:v>
+        <x:v>offen über View-only-Link</x:v>
       </x:c>
       <x:c r="N13" s="37" t="str">
         <x:v>https://osf.io/b8zp4/?view_only=f331e7a632e54a6fbaf5763175393150</x:v>
@@ -2194,8 +2202,8 @@
       <x:c r="O13" s="31" t="str">
         <x:v>PuRe</x:v>
       </x:c>
-      <x:c r="P13" s="31" t="str">
-        <x:v>offen</x:v>
+      <x:c r="P13" s="39" t="str">
+        <x:v>offen über View-only-Link</x:v>
       </x:c>
       <x:c r="Q13" s="31" t="str">
         <x:v>HTTP 200; HTTP</x:v>
@@ -2280,7 +2288,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="M14" s="31" t="str">
-        <x:v>offen</x:v>
+        <x:v>offen über View-only-Link; offen</x:v>
       </x:c>
       <x:c r="N14" s="37" t="str">
         <x:v>https://osf.io/4n8hy/?view_only=fb104cd14ba548e0b01b997908fdbeb8</x:v>
@@ -2288,8 +2296,8 @@
       <x:c r="O14" s="31" t="str">
         <x:v>PuRe</x:v>
       </x:c>
-      <x:c r="P14" s="31" t="str">
-        <x:v>offen</x:v>
+      <x:c r="P14" s="39" t="str">
+        <x:v>offen über View-only-Link</x:v>
       </x:c>
       <x:c r="Q14" s="31" t="str">
         <x:v>HTTP 200; HTTP</x:v>
@@ -2341,7 +2349,7 @@
         <x:v>HTTP</x:v>
       </x:c>
       <x:c r="AZ14" s="31" t="str">
-        <x:v>Kuratiertes PuRe-Forschungsdatenfeld; Link aus Data-Availability-Abschnitt des öffentlichen PuRe-Volltexts</x:v>
+        <x:v>Kuratiertes PuRe-Forschungsdatenfeld; Link aus Data-Availability-Abschnitt des öffentlichen PuRe-Volltexts; 1 Datendatei(en) über OSF-API bestätigt</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="34" customHeight="1">
@@ -2883,7 +2891,7 @@
         <x:v>HTTP</x:v>
       </x:c>
       <x:c r="AZ20" s="31" t="str">
-        <x:v>Titel-/Autor:innen-Match (1.00)</x:v>
+        <x:v>Titel-/Autor:innen-Match (1.00); 1 Datendatei(en) über OSF-API bestätigt</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="34" customHeight="1">
@@ -3493,7 +3501,7 @@
         <x:v>HTTP</x:v>
       </x:c>
       <x:c r="AZ27" s="31" t="str">
-        <x:v>Titel-/Autor:innen-Match (1.00)</x:v>
+        <x:v>Titel-/Autor:innen-Match (1.00); 208 Datendatei(en) über OSF-API bestätigt</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="34" customHeight="1">
@@ -3587,7 +3595,7 @@
         <x:v>HTTP</x:v>
       </x:c>
       <x:c r="AZ28" s="31" t="str">
-        <x:v>Titel-/Autor:innen-Match (1.00)</x:v>
+        <x:v>Titel-/Autor:innen-Match (1.00); 7 Datendatei(en) über OSF-API bestätigt</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="34" customHeight="1">
@@ -3791,19 +3799,27 @@
       <x:c r="J31" s="31" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="K31" s="33" t="str">
-        <x:v>nein</x:v>
+      <x:c r="K31" s="32" t="str">
+        <x:v>ja</x:v>
       </x:c>
       <x:c r="L31" s="41" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M31" s="31" t="str">
-        <x:v>kein verifizierter Datenlink</x:v>
-      </x:c>
-      <x:c r="N31" s="37" t="str"/>
-      <x:c r="O31" s="31" t="str"/>
-      <x:c r="P31" s="31" t="str"/>
-      <x:c r="Q31" s="31" t="str"/>
+        <x:v>Zustimmung/E-Mail erforderlich</x:v>
+      </x:c>
+      <x:c r="N31" s="37" t="str">
+        <x:v>https://services.informs.org/dataset/mnsc/download.php?doi=mnsc.2022.00990</x:v>
+      </x:c>
+      <x:c r="O31" s="31" t="str">
+        <x:v>Provider</x:v>
+      </x:c>
+      <x:c r="P31" s="39" t="str">
+        <x:v>Zustimmung/E-Mail erforderlich</x:v>
+      </x:c>
+      <x:c r="Q31" s="31" t="str">
+        <x:v>HTTP 200; Playwright</x:v>
+      </x:c>
       <x:c r="R31" s="37" t="str"/>
       <x:c r="S31" s="31" t="str"/>
       <x:c r="T31" s="31" t="str"/>
@@ -3840,10 +3856,10 @@
         <x:v>2026-07-15</x:v>
       </x:c>
       <x:c r="AY31" s="31" t="str">
-        <x:v>HTTP + Playwright-Audit</x:v>
+        <x:v>Playwright</x:v>
       </x:c>
       <x:c r="AZ31" s="31" t="str">
-        <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
+        <x:v>Offizielles INFORMS-Replikationsarchiv mit geprüften Datendateien</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="34" customHeight="1">
@@ -3877,19 +3893,27 @@
       <x:c r="J32" s="31" t="str">
         <x:v>no</x:v>
       </x:c>
-      <x:c r="K32" s="33" t="str">
-        <x:v>nein</x:v>
+      <x:c r="K32" s="32" t="str">
+        <x:v>ja</x:v>
       </x:c>
       <x:c r="L32" s="41" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M32" s="31" t="str">
-        <x:v>kein verifizierter Datenlink</x:v>
-      </x:c>
-      <x:c r="N32" s="37" t="str"/>
-      <x:c r="O32" s="31" t="str"/>
-      <x:c r="P32" s="31" t="str"/>
-      <x:c r="Q32" s="31" t="str"/>
+        <x:v>offen über View-only-Link</x:v>
+      </x:c>
+      <x:c r="N32" s="37" t="str">
+        <x:v>https://osf.io/yef3k/?view_only=6d8e23c8ced94e3680c5f459a471fd1f</x:v>
+      </x:c>
+      <x:c r="O32" s="31" t="str">
+        <x:v>Provider</x:v>
+      </x:c>
+      <x:c r="P32" s="39" t="str">
+        <x:v>offen über View-only-Link</x:v>
+      </x:c>
+      <x:c r="Q32" s="31" t="str">
+        <x:v>HTTP 200; HTTP</x:v>
+      </x:c>
       <x:c r="R32" s="37" t="str"/>
       <x:c r="S32" s="31" t="str"/>
       <x:c r="T32" s="31" t="str"/>
@@ -3926,10 +3950,10 @@
         <x:v>2026-07-15</x:v>
       </x:c>
       <x:c r="AY32" s="31" t="str">
-        <x:v>HTTP + Playwright-Audit</x:v>
+        <x:v>HTTP</x:v>
       </x:c>
       <x:c r="AZ32" s="31" t="str">
-        <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
+        <x:v>Wiley-Datenverfügbarkeitsaussage mit rekursiv geprüften OSF-Datendateien; 17 Datendatei(en) über OSF-API bestätigt</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="34" customHeight="1">
@@ -5185,10 +5209,10 @@
         <x:v>ja</x:v>
       </x:c>
       <x:c r="L47" s="41" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M47" s="31" t="str">
-        <x:v>offen</x:v>
+        <x:v>offen über View-only-Link</x:v>
       </x:c>
       <x:c r="N47" s="37" t="str">
         <x:v>https://osf.io/s43na/?view_only=ecc07a520bf64f9397adb25d70c7deb5</x:v>
@@ -5196,24 +5220,16 @@
       <x:c r="O47" s="31" t="str">
         <x:v>Provider</x:v>
       </x:c>
-      <x:c r="P47" s="31" t="str">
-        <x:v>offen</x:v>
+      <x:c r="P47" s="39" t="str">
+        <x:v>offen über View-only-Link</x:v>
       </x:c>
       <x:c r="Q47" s="31" t="str">
         <x:v>HTTP 200; HTTP</x:v>
       </x:c>
-      <x:c r="R47" s="37" t="str">
-        <x:v>https://osf.io/d2fex/?view_only=daca41c653574a8aa1fb40d6b6a7f46c</x:v>
-      </x:c>
-      <x:c r="S47" s="31" t="str">
-        <x:v>Provider</x:v>
-      </x:c>
-      <x:c r="T47" s="31" t="str">
-        <x:v>offen</x:v>
-      </x:c>
-      <x:c r="U47" s="31" t="str">
-        <x:v>HTTP 200; HTTP</x:v>
-      </x:c>
+      <x:c r="R47" s="37" t="str"/>
+      <x:c r="S47" s="31" t="str"/>
+      <x:c r="T47" s="31" t="str"/>
+      <x:c r="U47" s="31" t="str"/>
       <x:c r="V47" s="37" t="str"/>
       <x:c r="W47" s="31" t="str"/>
       <x:c r="X47" s="31" t="str"/>
@@ -5249,7 +5265,7 @@
         <x:v>HTTP</x:v>
       </x:c>
       <x:c r="AZ47" s="31" t="str">
-        <x:v>Link aus expliziter Data-Availability-Statement</x:v>
+        <x:v>Link aus expliziter Data-Availability-Statement; 6 Datendatei(en) über OSF-API bestätigt</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="34" customHeight="1">
@@ -5343,7 +5359,7 @@
         <x:v>HTTP</x:v>
       </x:c>
       <x:c r="AZ48" s="31" t="str">
-        <x:v>Titel-/Autor:innen-Match (1.00)</x:v>
+        <x:v>Titel-/Autor:innen-Match (1.00); 9 Datendatei(en) über OSF-API bestätigt</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="34" customHeight="1">
@@ -7936,7 +7952,7 @@
         <x:v>HTTP</x:v>
       </x:c>
       <x:c r="AZ78" s="31" t="str">
-        <x:v>Link aus expliziter Data-Availability-Statement</x:v>
+        <x:v>Link aus expliziter Data-Availability-Statement; 6 Datendatei(en) über OSF-API bestätigt</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="34" customHeight="1">
@@ -10099,7 +10115,7 @@
         <x:v>HTTP</x:v>
       </x:c>
       <x:c r="AZ103" s="31" t="str">
-        <x:v>Link aus Data-Availability-Abschnitt des öffentlichen PuRe-Volltexts</x:v>
+        <x:v>Link aus Data-Availability-Abschnitt des öffentlichen PuRe-Volltexts; 1 Datendatei(en) über OSF-API bestätigt</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="34" customHeight="1">
@@ -11758,7 +11774,7 @@
         <x:v>HTTP</x:v>
       </x:c>
       <x:c r="AZ122" s="31" t="str">
-        <x:v>Link aus expliziter Data-Availability-Statement</x:v>
+        <x:v>Link aus expliziter Data-Availability-Statement; 6 Datendatei(en) über OSF-API bestätigt; Link aus expliziter Data-Availability-Statement</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="34" customHeight="1">
@@ -12130,19 +12146,27 @@
       <x:c r="J127" s="31" t="str">
         <x:v>no</x:v>
       </x:c>
-      <x:c r="K127" s="33" t="str">
-        <x:v>nein</x:v>
+      <x:c r="K127" s="32" t="str">
+        <x:v>ja</x:v>
       </x:c>
       <x:c r="L127" s="41" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M127" s="31" t="str">
-        <x:v>kein verifizierter Datenlink</x:v>
-      </x:c>
-      <x:c r="N127" s="37" t="str"/>
-      <x:c r="O127" s="31" t="str"/>
-      <x:c r="P127" s="31" t="str"/>
-      <x:c r="Q127" s="31" t="str"/>
+        <x:v>offen</x:v>
+      </x:c>
+      <x:c r="N127" s="37" t="str">
+        <x:v>https://github.com/predictive-clinical-neuroscience/PCNtoolkit-demo/tree/main/tutorials/Long_NM</x:v>
+      </x:c>
+      <x:c r="O127" s="31" t="str">
+        <x:v>Provider</x:v>
+      </x:c>
+      <x:c r="P127" s="31" t="str">
+        <x:v>offen</x:v>
+      </x:c>
+      <x:c r="Q127" s="31" t="str">
+        <x:v>HTTP 200; HTTP</x:v>
+      </x:c>
       <x:c r="R127" s="37" t="str"/>
       <x:c r="S127" s="31" t="str"/>
       <x:c r="T127" s="31" t="str"/>
@@ -12179,10 +12203,10 @@
         <x:v>2026-07-15</x:v>
       </x:c>
       <x:c r="AY127" s="31" t="str">
-        <x:v>HTTP + Playwright-Audit</x:v>
+        <x:v>HTTP</x:v>
       </x:c>
       <x:c r="AZ127" s="31" t="str">
-        <x:v>Verlagsseite nennt keine eindeutige vorhandene Datenausgabe</x:v>
+        <x:v>Strukturierte eLife-Data-Availability-Aussage mit öffentlichem Datensatzlink; 32 Datendatei(en) über GitHub-API bestätigt</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="34" customHeight="1">
@@ -12896,19 +12920,27 @@
       <x:c r="J136" s="31" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="K136" s="33" t="str">
-        <x:v>nein</x:v>
+      <x:c r="K136" s="32" t="str">
+        <x:v>ja</x:v>
       </x:c>
       <x:c r="L136" s="41" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M136" s="31" t="str">
-        <x:v>kein verifizierter Datenlink</x:v>
-      </x:c>
-      <x:c r="N136" s="37" t="str"/>
-      <x:c r="O136" s="31" t="str"/>
-      <x:c r="P136" s="31" t="str"/>
-      <x:c r="Q136" s="31" t="str"/>
+        <x:v>Zustimmung/E-Mail erforderlich</x:v>
+      </x:c>
+      <x:c r="N136" s="37" t="str">
+        <x:v>https://services.informs.org/dataset/mnsc/download.php?doi=mnsc.2022.03362</x:v>
+      </x:c>
+      <x:c r="O136" s="31" t="str">
+        <x:v>Provider</x:v>
+      </x:c>
+      <x:c r="P136" s="39" t="str">
+        <x:v>Zustimmung/E-Mail erforderlich</x:v>
+      </x:c>
+      <x:c r="Q136" s="31" t="str">
+        <x:v>HTTP 200; Playwright</x:v>
+      </x:c>
       <x:c r="R136" s="37" t="str"/>
       <x:c r="S136" s="31" t="str"/>
       <x:c r="T136" s="31" t="str"/>
@@ -12945,10 +12977,10 @@
         <x:v>2026-07-15</x:v>
       </x:c>
       <x:c r="AY136" s="31" t="str">
-        <x:v>HTTP + Playwright-Audit</x:v>
+        <x:v>Playwright</x:v>
       </x:c>
       <x:c r="AZ136" s="31" t="str">
-        <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
+        <x:v>Offizielles INFORMS-Replikationsarchiv mit geprüften Datendateien</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="34" customHeight="1">
@@ -14006,19 +14038,27 @@
       <x:c r="J149" s="31" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="K149" s="33" t="str">
-        <x:v>nein</x:v>
+      <x:c r="K149" s="32" t="str">
+        <x:v>ja</x:v>
       </x:c>
       <x:c r="L149" s="41" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M149" s="31" t="str">
-        <x:v>kein verifizierter Datenlink</x:v>
-      </x:c>
-      <x:c r="N149" s="37" t="str"/>
-      <x:c r="O149" s="31" t="str"/>
-      <x:c r="P149" s="31" t="str"/>
-      <x:c r="Q149" s="31" t="str"/>
+        <x:v>Zustimmung/E-Mail erforderlich</x:v>
+      </x:c>
+      <x:c r="N149" s="37" t="str">
+        <x:v>https://services.informs.org/dataset/mnsc/download.php?doi=mnsc.2022.00652</x:v>
+      </x:c>
+      <x:c r="O149" s="31" t="str">
+        <x:v>Provider</x:v>
+      </x:c>
+      <x:c r="P149" s="39" t="str">
+        <x:v>Zustimmung/E-Mail erforderlich</x:v>
+      </x:c>
+      <x:c r="Q149" s="31" t="str">
+        <x:v>HTTP 200; Playwright</x:v>
+      </x:c>
       <x:c r="R149" s="37" t="str"/>
       <x:c r="S149" s="31" t="str"/>
       <x:c r="T149" s="31" t="str"/>
@@ -14055,10 +14095,10 @@
         <x:v>2026-07-15</x:v>
       </x:c>
       <x:c r="AY149" s="31" t="str">
-        <x:v>HTTP + Playwright-Audit</x:v>
+        <x:v>Playwright</x:v>
       </x:c>
       <x:c r="AZ149" s="31" t="str">
-        <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
+        <x:v>Offizielles INFORMS-Replikationsarchiv mit geprüften Datendateien</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="34" customHeight="1">
@@ -16212,7 +16252,7 @@
         <x:v>HTTP</x:v>
       </x:c>
       <x:c r="AZ174" s="31" t="str">
-        <x:v>Identischer normalisierter Titel und starke Autor:innenüberschneidung mit item_3686548; Titel-/Autor:innen-Match (1.00)</x:v>
+        <x:v>Identischer normalisierter Titel und starke Autor:innenüberschneidung mit item_3686548; Titel-/Autor:innen-Match (1.00); 208 Datendatei(en) über OSF-API bestätigt</x:v>
       </x:c>
     </x:row>
     <x:row r="175" ht="34" customHeight="1">
@@ -16306,7 +16346,7 @@
         <x:v>HTTP</x:v>
       </x:c>
       <x:c r="AZ175" s="31" t="str">
-        <x:v>Link aus expliziter Data-Availability-Statement</x:v>
+        <x:v>Link aus expliziter Data-Availability-Statement; 1 Datendatei(en) über OSF-API bestätigt</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="34" customHeight="1">
@@ -19686,7 +19726,7 @@
         <x:v>HTTP</x:v>
       </x:c>
       <x:c r="AZ214" s="31" t="str">
-        <x:v>Identischer normalisierter Titel und starke Autor:innenüberschneidung mit item_3657005; Link aus expliziter Data-Availability-Statement</x:v>
+        <x:v>Identischer normalisierter Titel und starke Autor:innenüberschneidung mit item_3657005; Link aus expliziter Data-Availability-Statement; 6 Datendatei(en) über OSF-API bestätigt; Identischer normalisierter Titel und starke Autor:innenüberschneidung mit item_3657005; Link aus expliziter Data-Availability-Statement</x:v>
       </x:c>
     </x:row>
     <x:row r="215" ht="34" customHeight="1">
@@ -20408,19 +20448,27 @@
       <x:c r="J223" s="31" t="str">
         <x:v>no</x:v>
       </x:c>
-      <x:c r="K223" s="33" t="str">
-        <x:v>nein</x:v>
+      <x:c r="K223" s="32" t="str">
+        <x:v>ja</x:v>
       </x:c>
       <x:c r="L223" s="41" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M223" s="31" t="str">
-        <x:v>kein verifizierter Datenlink</x:v>
-      </x:c>
-      <x:c r="N223" s="37" t="str"/>
-      <x:c r="O223" s="31" t="str"/>
-      <x:c r="P223" s="31" t="str"/>
-      <x:c r="Q223" s="31" t="str"/>
+        <x:v>offen über View-only-Link</x:v>
+      </x:c>
+      <x:c r="N223" s="37" t="str">
+        <x:v>https://osf.io/z34es/?view_only=634f9aba0001450d8baef233da73a1a4</x:v>
+      </x:c>
+      <x:c r="O223" s="31" t="str">
+        <x:v>Provider</x:v>
+      </x:c>
+      <x:c r="P223" s="39" t="str">
+        <x:v>offen über View-only-Link</x:v>
+      </x:c>
+      <x:c r="Q223" s="31" t="str">
+        <x:v>HTTP 200; HTTP</x:v>
+      </x:c>
       <x:c r="R223" s="37" t="str"/>
       <x:c r="S223" s="31" t="str"/>
       <x:c r="T223" s="31" t="str"/>
@@ -20457,10 +20505,10 @@
         <x:v>2026-07-15</x:v>
       </x:c>
       <x:c r="AY223" s="31" t="str">
-        <x:v>HTTP + Playwright-Audit</x:v>
+        <x:v>HTTP</x:v>
       </x:c>
       <x:c r="AZ223" s="31" t="str">
-        <x:v>Dataset-Treffer ohne hinreichend engen Publikationsbezug (0.09)</x:v>
+        <x:v>Wiley-Datenverfügbarkeitsaussage mit rekursiv geprüften OSF-Datendateien; 2 Datendatei(en) über OSF-API bestätigt</x:v>
       </x:c>
     </x:row>
     <x:row r="224" ht="34" customHeight="1">
@@ -20892,7 +20940,7 @@
         <x:v>HTTP</x:v>
       </x:c>
       <x:c r="AZ228" s="31" t="str">
-        <x:v>Link aus expliziter Data-Availability-Statement</x:v>
+        <x:v>Link aus expliziter Data-Availability-Statement; 3 Datendatei(en) über OSF-API bestätigt</x:v>
       </x:c>
     </x:row>
     <x:row r="229" ht="34" customHeight="1">
@@ -21012,19 +21060,27 @@
       <x:c r="J230" s="31" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="K230" s="33" t="str">
-        <x:v>nein</x:v>
+      <x:c r="K230" s="32" t="str">
+        <x:v>ja</x:v>
       </x:c>
       <x:c r="L230" s="41" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M230" s="31" t="str">
-        <x:v>kein verifizierter Datenlink</x:v>
-      </x:c>
-      <x:c r="N230" s="37" t="str"/>
-      <x:c r="O230" s="31" t="str"/>
-      <x:c r="P230" s="31" t="str"/>
-      <x:c r="Q230" s="31" t="str"/>
+        <x:v>Zustimmung/E-Mail erforderlich</x:v>
+      </x:c>
+      <x:c r="N230" s="37" t="str">
+        <x:v>https://services.informs.org/dataset/mnsc/download.php?doi=mnsc.2023.4838</x:v>
+      </x:c>
+      <x:c r="O230" s="31" t="str">
+        <x:v>Provider</x:v>
+      </x:c>
+      <x:c r="P230" s="39" t="str">
+        <x:v>Zustimmung/E-Mail erforderlich</x:v>
+      </x:c>
+      <x:c r="Q230" s="31" t="str">
+        <x:v>HTTP 200; Playwright</x:v>
+      </x:c>
       <x:c r="R230" s="37" t="str"/>
       <x:c r="S230" s="31" t="str"/>
       <x:c r="T230" s="31" t="str"/>
@@ -21061,10 +21117,10 @@
         <x:v>2026-07-15</x:v>
       </x:c>
       <x:c r="AY230" s="31" t="str">
-        <x:v>HTTP + Playwright-Audit</x:v>
+        <x:v>Playwright</x:v>
       </x:c>
       <x:c r="AZ230" s="31" t="str">
-        <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
+        <x:v>Offizielles INFORMS-Replikationsarchiv mit geprüften Datendateien</x:v>
       </x:c>
     </x:row>
     <x:row r="231" ht="34" customHeight="1">
@@ -21610,19 +21666,27 @@
       <x:c r="J237" s="31" t="str">
         <x:v>no</x:v>
       </x:c>
-      <x:c r="K237" s="33" t="str">
-        <x:v>nein</x:v>
+      <x:c r="K237" s="32" t="str">
+        <x:v>ja</x:v>
       </x:c>
       <x:c r="L237" s="41" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M237" s="31" t="str">
-        <x:v>kein verifizierter Datenlink</x:v>
-      </x:c>
-      <x:c r="N237" s="37" t="str"/>
-      <x:c r="O237" s="31" t="str"/>
-      <x:c r="P237" s="31" t="str"/>
-      <x:c r="Q237" s="31" t="str"/>
+        <x:v>offen</x:v>
+      </x:c>
+      <x:c r="N237" s="37" t="str">
+        <x:v>https://osf.io/rgeq8</x:v>
+      </x:c>
+      <x:c r="O237" s="31" t="str">
+        <x:v>Provider</x:v>
+      </x:c>
+      <x:c r="P237" s="31" t="str">
+        <x:v>offen</x:v>
+      </x:c>
+      <x:c r="Q237" s="31" t="str">
+        <x:v>HTTP 200; HTTP</x:v>
+      </x:c>
       <x:c r="R237" s="37" t="str"/>
       <x:c r="S237" s="31" t="str"/>
       <x:c r="T237" s="31" t="str"/>
@@ -21659,10 +21723,10 @@
         <x:v>2026-07-15</x:v>
       </x:c>
       <x:c r="AY237" s="31" t="str">
-        <x:v>HTTP + Playwright-Audit</x:v>
+        <x:v>HTTP</x:v>
       </x:c>
       <x:c r="AZ237" s="31" t="str">
-        <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
+        <x:v>Bereits auditierter Datensatz einer stark identifizierten Publikationsfassung; 3 Datendatei(en) über OSF-API bestätigt</x:v>
       </x:c>
     </x:row>
     <x:row r="238" ht="34" customHeight="1">
@@ -22944,7 +23008,7 @@
         <x:v>HTTP</x:v>
       </x:c>
       <x:c r="AZ252" s="31" t="str">
-        <x:v>Link aus Data-Availability-Abschnitt des öffentlichen PuRe-Volltexts</x:v>
+        <x:v>Link aus Data-Availability-Abschnitt des öffentlichen PuRe-Volltexts; 3 Datendatei(en) über OSF-API bestätigt</x:v>
       </x:c>
     </x:row>
     <x:row r="253" ht="34" customHeight="1">
@@ -23756,19 +23820,27 @@
       <x:c r="J262" s="31" t="str">
         <x:v>no</x:v>
       </x:c>
-      <x:c r="K262" s="33" t="str">
-        <x:v>nein</x:v>
+      <x:c r="K262" s="32" t="str">
+        <x:v>ja</x:v>
       </x:c>
       <x:c r="L262" s="41" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M262" s="31" t="str">
-        <x:v>kein verifizierter Datenlink</x:v>
-      </x:c>
-      <x:c r="N262" s="37" t="str"/>
-      <x:c r="O262" s="31" t="str"/>
-      <x:c r="P262" s="31" t="str"/>
-      <x:c r="Q262" s="31" t="str"/>
+        <x:v>offen</x:v>
+      </x:c>
+      <x:c r="N262" s="37" t="str">
+        <x:v>https://dataverse.harvard.edu/dataset.xhtml?persistentId=doi:10.7910/DVN/SPJFJ5</x:v>
+      </x:c>
+      <x:c r="O262" s="31" t="str">
+        <x:v>Provider</x:v>
+      </x:c>
+      <x:c r="P262" s="31" t="str">
+        <x:v>offen</x:v>
+      </x:c>
+      <x:c r="Q262" s="31" t="str">
+        <x:v>HTTP 202; Playwright</x:v>
+      </x:c>
       <x:c r="R262" s="37" t="str"/>
       <x:c r="S262" s="31" t="str"/>
       <x:c r="T262" s="31" t="str"/>
@@ -23805,10 +23877,10 @@
         <x:v>2026-07-15</x:v>
       </x:c>
       <x:c r="AY262" s="31" t="str">
-        <x:v>HTTP + Playwright-Audit</x:v>
+        <x:v>Playwright</x:v>
       </x:c>
       <x:c r="AZ262" s="31" t="str">
-        <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
+        <x:v>Bereits auditierter Datensatz einer stark identifizierten Publikationsfassung</x:v>
       </x:c>
     </x:row>
     <x:row r="263" ht="34" customHeight="1">
@@ -25360,7 +25432,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a17a9d77f2d4de0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14488b790c734584"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25420,13 +25492,13 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="C4" s="29" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D4" s="29" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D4" s="29" t="n">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="E4" s="48" t="n">
-        <x:v>0.4444444444444444</x:v>
+        <x:v>0.5555555555555556</x:v>
       </x:c>
       <x:c r="F4" s="29" t="n">
         <x:v>3</x:v>
@@ -25443,13 +25515,13 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="C5" s="31" t="n">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D5" s="31" t="n">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E5" s="49" t="n">
-        <x:v>0.16101694915254236</x:v>
+        <x:v>0.1864406779661017</x:v>
       </x:c>
       <x:c r="F5" s="31" t="n">
         <x:v>11</x:v>
@@ -25558,19 +25630,19 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C10" s="31" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D10" s="31" t="n">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E10" s="49" t="n">
-        <x:v>0.0851063829787234</x:v>
+        <x:v>0.14893617021276595</x:v>
       </x:c>
       <x:c r="F10" s="31" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G10" s="31" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="28" customHeight="1">
@@ -25604,19 +25676,19 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="C12" s="31" t="n">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D12" s="31" t="n">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E12" s="49" t="n">
-        <x:v>0.20270270270270271</x:v>
+        <x:v>0.22972972972972974</x:v>
       </x:c>
       <x:c r="F12" s="31" t="n">
         <x:v>23</x:v>
       </x:c>
       <x:c r="G12" s="31" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="28" customHeight="1">
@@ -25675,7 +25747,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff384e42b90b4a7f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbef09546561d4f55"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/research_data_enrichment/Forschungsdaten_2024-heute_3_Sheets_konsolidiert_geprueft.xlsx
+++ b/outputs/research_data_enrichment/Forschungsdaten_2024-heute_3_Sheets_konsolidiert_geprueft.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Übersicht" sheetId="1" r:id="R1290edaebf634759"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forschungsdaten" sheetId="2" r:id="Rd7a69ad6e70d4438"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forschungsgruppen" sheetId="3" r:id="R990fdc6efef6495c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Übersicht" sheetId="1" r:id="Rc9aa335f44db4feb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forschungsdaten" sheetId="2" r:id="Rc42e9556e298453f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forschungsgruppen" sheetId="3" r:id="Ra09f842f8f7b4b08"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -298,8 +298,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tbl_Forschungsdaten" displayName="tbl_Forschungsdaten" ref="A1:AZ280" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="52">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tbl_Forschungsdaten" displayName="tbl_Forschungsdaten" ref="A1:AV280" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="48">
     <x:tableColumn id="1" name="PuRe-ID"/>
     <x:tableColumn id="2" name="Titel"/>
     <x:tableColumn id="3" name="Autor:innen"/>
@@ -345,13 +345,9 @@
     <x:tableColumn id="43" name="Quelle Link 8"/>
     <x:tableColumn id="44" name="Zugang Link 8"/>
     <x:tableColumn id="45" name="Prüfung Link 8"/>
-    <x:tableColumn id="46" name="Forschungsdaten-Link 9"/>
-    <x:tableColumn id="47" name="Quelle Link 9"/>
-    <x:tableColumn id="48" name="Zugang Link 9"/>
-    <x:tableColumn id="49" name="Prüfung Link 9"/>
-    <x:tableColumn id="50" name="Geprüft am"/>
-    <x:tableColumn id="51" name="Prüfverfahren"/>
-    <x:tableColumn id="52" name="Nachweis / Entscheidung"/>
+    <x:tableColumn id="46" name="Geprüft am"/>
+    <x:tableColumn id="47" name="Prüfverfahren"/>
+    <x:tableColumn id="48" name="Nachweis / Entscheidung"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -606,7 +602,7 @@
         <x:v>Forschungsdaten: ja</x:v>
       </x:c>
       <x:c r="B5" s="14" t="n">
-        <x:v>60</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -614,7 +610,7 @@
         <x:v>Forschungsdaten: nein</x:v>
       </x:c>
       <x:c r="B6" s="14" t="n">
-        <x:v>219</x:v>
+        <x:v>215</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -622,7 +618,7 @@
         <x:v>Abdeckungsquote</x:v>
       </x:c>
       <x:c r="B7" s="15" t="n">
-        <x:v>0.21505376344086022</x:v>
+        <x:v>0.22939068100358423</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -630,7 +626,7 @@
         <x:v>Verifizierte Forschungsdatenlinks</x:v>
       </x:c>
       <x:c r="B8" s="14" t="n">
-        <x:v>85</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -829,9 +825,9 @@
     <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="52" max="52" width="52" hidden="0" customWidth="1"/>
-    <x:col min="50" max="50" width="18" hidden="0" customWidth="1"/>
-    <x:col min="51" max="51" width="18" hidden="0" customWidth="1"/>
+    <x:col min="48" max="48" width="52" hidden="0" customWidth="1"/>
+    <x:col min="46" max="46" width="18" hidden="0" customWidth="1"/>
+    <x:col min="47" max="47" width="18" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="38" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="15" hidden="0" customWidth="1"/>
     <x:col min="16" max="16" width="23" hidden="0" customWidth="1"/>
@@ -864,10 +860,6 @@
     <x:col min="43" max="43" width="15" hidden="0" customWidth="1"/>
     <x:col min="44" max="44" width="23" hidden="0" customWidth="1"/>
     <x:col min="45" max="45" width="19" hidden="0" customWidth="1"/>
-    <x:col min="46" max="46" width="38" hidden="0" customWidth="1"/>
-    <x:col min="47" max="47" width="15" hidden="0" customWidth="1"/>
-    <x:col min="48" max="48" width="23" hidden="0" customWidth="1"/>
-    <x:col min="49" max="49" width="19" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="44" customHeight="1">
@@ -1007,24 +999,12 @@
         <x:v>Prüfung Link 8</x:v>
       </x:c>
       <x:c r="AT1" s="16" t="str">
-        <x:v>Forschungsdaten-Link 9</x:v>
+        <x:v>Geprüft am</x:v>
       </x:c>
       <x:c r="AU1" s="16" t="str">
-        <x:v>Quelle Link 9</x:v>
-      </x:c>
-      <x:c r="AV1" s="16" t="str">
-        <x:v>Zugang Link 9</x:v>
-      </x:c>
-      <x:c r="AW1" s="16" t="str">
-        <x:v>Prüfung Link 9</x:v>
-      </x:c>
-      <x:c r="AX1" s="16" t="str">
-        <x:v>Geprüft am</x:v>
-      </x:c>
-      <x:c r="AY1" s="16" t="str">
         <x:v>Prüfverfahren</x:v>
       </x:c>
-      <x:c r="AZ1" s="8" t="str">
+      <x:c r="AV1" s="8" t="str">
         <x:v>Nachweis / Entscheidung</x:v>
       </x:c>
     </x:row>
@@ -1108,18 +1088,14 @@
       <x:c r="AQ2" s="29" t="str"/>
       <x:c r="AR2" s="29" t="str"/>
       <x:c r="AS2" s="29" t="str"/>
-      <x:c r="AT2" s="36" t="str"/>
-      <x:c r="AU2" s="29" t="str"/>
-      <x:c r="AV2" s="29" t="str"/>
-      <x:c r="AW2" s="29" t="str"/>
-      <x:c r="AX2" s="29" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY2" s="29" t="str">
+      <x:c r="AT2" s="29" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU2" s="29" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ2" s="29" t="str">
-        <x:v>Kuratiertes PuRe-Forschungsdatenfeld</x:v>
+      <x:c r="AV2" s="29" t="str">
+        <x:v>Kuratiertes PuRe-Forschungsdatenfeld; 148 Datendatei(en) über OSF-API bestätigt</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="34" customHeight="1">
@@ -1202,17 +1178,13 @@
       <x:c r="AQ3" s="31" t="str"/>
       <x:c r="AR3" s="31" t="str"/>
       <x:c r="AS3" s="31" t="str"/>
-      <x:c r="AT3" s="37" t="str"/>
-      <x:c r="AU3" s="31" t="str"/>
-      <x:c r="AV3" s="31" t="str"/>
-      <x:c r="AW3" s="31" t="str"/>
-      <x:c r="AX3" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY3" s="31" t="str">
+      <x:c r="AT3" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU3" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ3" s="31" t="str">
+      <x:c r="AV3" s="31" t="str">
         <x:v>Kuratiertes PuRe-Forschungsdatenfeld</x:v>
       </x:c>
     </x:row>
@@ -1286,17 +1258,13 @@
       <x:c r="AQ4" s="31" t="str"/>
       <x:c r="AR4" s="31" t="str"/>
       <x:c r="AS4" s="31" t="str"/>
-      <x:c r="AT4" s="37" t="str"/>
-      <x:c r="AU4" s="31" t="str"/>
-      <x:c r="AV4" s="31" t="str"/>
-      <x:c r="AW4" s="31" t="str"/>
-      <x:c r="AX4" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY4" s="31" t="str">
+      <x:c r="AT4" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU4" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ4" s="31" t="str">
+      <x:c r="AV4" s="31" t="str">
         <x:v>Interaktive Publikationsseite, kein Datensatznachweis</x:v>
       </x:c>
     </x:row>
@@ -1335,7 +1303,7 @@
         <x:v>ja</x:v>
       </x:c>
       <x:c r="L5" s="41" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="M5" s="31" t="str">
         <x:v>offen</x:v>
@@ -1389,7 +1357,7 @@
         <x:v>HTTP 200; HTTP</x:v>
       </x:c>
       <x:c r="AD5" s="37" t="str">
-        <x:v>https://osf.io/ngjb2</x:v>
+        <x:v>https://psycharchives.org/en/item/10bd0124-e5ff-4010-81a1-afd3383b7562</x:v>
       </x:c>
       <x:c r="AE5" s="31" t="str">
         <x:v>Provider</x:v>
@@ -1401,7 +1369,7 @@
         <x:v>HTTP 200; HTTP</x:v>
       </x:c>
       <x:c r="AH5" s="37" t="str">
-        <x:v>https://psycharchives.org/en/item/10bd0124-e5ff-4010-81a1-afd3383b7562</x:v>
+        <x:v>https://osf.io/76un5</x:v>
       </x:c>
       <x:c r="AI5" s="31" t="str">
         <x:v>Provider</x:v>
@@ -1413,7 +1381,7 @@
         <x:v>HTTP 200; HTTP</x:v>
       </x:c>
       <x:c r="AL5" s="37" t="str">
-        <x:v>https://osf.io/76un5</x:v>
+        <x:v>https://osf.io/ed5mv</x:v>
       </x:c>
       <x:c r="AM5" s="31" t="str">
         <x:v>Provider</x:v>
@@ -1425,7 +1393,7 @@
         <x:v>HTTP 200; HTTP</x:v>
       </x:c>
       <x:c r="AP5" s="37" t="str">
-        <x:v>https://osf.io/ed5mv</x:v>
+        <x:v>https://osf.io/ecpgx</x:v>
       </x:c>
       <x:c r="AQ5" s="31" t="str">
         <x:v>Provider</x:v>
@@ -1436,26 +1404,14 @@
       <x:c r="AS5" s="31" t="str">
         <x:v>HTTP 200; HTTP</x:v>
       </x:c>
-      <x:c r="AT5" s="37" t="str">
-        <x:v>https://osf.io/ecpgx</x:v>
+      <x:c r="AT5" s="31" t="str">
+        <x:v>2026-07-15</x:v>
       </x:c>
       <x:c r="AU5" s="31" t="str">
-        <x:v>Provider</x:v>
+        <x:v>HTTP</x:v>
       </x:c>
       <x:c r="AV5" s="31" t="str">
-        <x:v>offen</x:v>
-      </x:c>
-      <x:c r="AW5" s="31" t="str">
-        <x:v>HTTP 200; HTTP</x:v>
-      </x:c>
-      <x:c r="AX5" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY5" s="31" t="str">
-        <x:v>HTTP</x:v>
-      </x:c>
-      <x:c r="AZ5" s="31" t="str">
-        <x:v>Kuratiertes PuRe-Forschungsdatenfeld; Link aus expliziter Data-Availability-Statement</x:v>
+        <x:v>Kuratiertes PuRe-Forschungsdatenfeld; 1 Datendatei(en) über OSF-API bestätigt; Link aus expliziter Data-Availability-Statement; 6 Datendatei(en) über OSF-API bestätigt; Link aus expliziter Data-Availability-Statement</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
@@ -1538,18 +1494,14 @@
       <x:c r="AQ6" s="31" t="str"/>
       <x:c r="AR6" s="31" t="str"/>
       <x:c r="AS6" s="31" t="str"/>
-      <x:c r="AT6" s="37" t="str"/>
-      <x:c r="AU6" s="31" t="str"/>
-      <x:c r="AV6" s="31" t="str"/>
-      <x:c r="AW6" s="31" t="str"/>
-      <x:c r="AX6" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY6" s="31" t="str">
+      <x:c r="AT6" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU6" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ6" s="31" t="str">
-        <x:v>Kuratiertes PuRe-Forschungsdatenfeld</x:v>
+      <x:c r="AV6" s="31" t="str">
+        <x:v>Kuratiertes PuRe-Forschungsdatenfeld; 1 Datendatei(en) über OSF-API bestätigt</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="34" customHeight="1">
@@ -1587,35 +1539,27 @@
         <x:v>ja</x:v>
       </x:c>
       <x:c r="L7" s="41" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M7" s="31" t="str">
-        <x:v>Paywall/Login oder Zugriffsschutz; offen</x:v>
+        <x:v>offen</x:v>
       </x:c>
       <x:c r="N7" s="37" t="str">
-        <x:v>https://dataverse.harvard.edu/citation?persistentId=doi:10.7910/DVN/DCSR0N</x:v>
+        <x:v>https://dataverse.harvard.edu/dataset.xhtml?persistentId=doi:10.7910/DVN/DCSR0N</x:v>
       </x:c>
       <x:c r="O7" s="31" t="str">
         <x:v>PuRe</x:v>
       </x:c>
-      <x:c r="P7" s="39" t="str">
-        <x:v>Paywall/Login oder Zugriffsschutz</x:v>
+      <x:c r="P7" s="31" t="str">
+        <x:v>offen</x:v>
       </x:c>
       <x:c r="Q7" s="31" t="str">
-        <x:v>HTTP 403; Playwright</x:v>
-      </x:c>
-      <x:c r="R7" s="37" t="str">
-        <x:v>https://dataverse.harvard.edu/dataset.xhtml?persistentId=doi:10.7910/DVN/DCSR0N</x:v>
-      </x:c>
-      <x:c r="S7" s="31" t="str">
-        <x:v>Provider</x:v>
-      </x:c>
-      <x:c r="T7" s="31" t="str">
-        <x:v>offen</x:v>
-      </x:c>
-      <x:c r="U7" s="31" t="str">
         <x:v>HTTP 202; Playwright</x:v>
       </x:c>
+      <x:c r="R7" s="37" t="str"/>
+      <x:c r="S7" s="31" t="str"/>
+      <x:c r="T7" s="31" t="str"/>
+      <x:c r="U7" s="31" t="str"/>
       <x:c r="V7" s="37" t="str"/>
       <x:c r="W7" s="31" t="str"/>
       <x:c r="X7" s="31" t="str"/>
@@ -1640,18 +1584,14 @@
       <x:c r="AQ7" s="31" t="str"/>
       <x:c r="AR7" s="31" t="str"/>
       <x:c r="AS7" s="31" t="str"/>
-      <x:c r="AT7" s="37" t="str"/>
-      <x:c r="AU7" s="31" t="str"/>
-      <x:c r="AV7" s="31" t="str"/>
-      <x:c r="AW7" s="31" t="str"/>
-      <x:c r="AX7" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY7" s="31" t="str">
+      <x:c r="AT7" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU7" s="31" t="str">
         <x:v>Playwright</x:v>
       </x:c>
-      <x:c r="AZ7" s="31" t="str">
-        <x:v>Kuratiertes PuRe-Forschungsdatenfeld; Landingpage antwortet mit HTTP 403 und ist zugriffsgeschützt; Titel-/Autor:innen-Match (1.00)</x:v>
+      <x:c r="AV7" s="31" t="str">
+        <x:v>Kuratiertes PuRe-Forschungsdatenfeld</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="34" customHeight="1">
@@ -1734,17 +1674,13 @@
       <x:c r="AQ8" s="31" t="str"/>
       <x:c r="AR8" s="31" t="str"/>
       <x:c r="AS8" s="31" t="str"/>
-      <x:c r="AT8" s="37" t="str"/>
-      <x:c r="AU8" s="31" t="str"/>
-      <x:c r="AV8" s="31" t="str"/>
-      <x:c r="AW8" s="31" t="str"/>
-      <x:c r="AX8" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY8" s="31" t="str">
+      <x:c r="AT8" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU8" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ8" s="31" t="str">
+      <x:c r="AV8" s="31" t="str">
         <x:v>Kuratiertes PuRe-Forschungsdatenfeld</x:v>
       </x:c>
     </x:row>
@@ -1828,18 +1764,14 @@
       <x:c r="AQ9" s="31" t="str"/>
       <x:c r="AR9" s="31" t="str"/>
       <x:c r="AS9" s="31" t="str"/>
-      <x:c r="AT9" s="37" t="str"/>
-      <x:c r="AU9" s="31" t="str"/>
-      <x:c r="AV9" s="31" t="str"/>
-      <x:c r="AW9" s="31" t="str"/>
-      <x:c r="AX9" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY9" s="31" t="str">
+      <x:c r="AT9" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU9" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ9" s="31" t="str">
-        <x:v>Kuratiertes PuRe-Forschungsdatenfeld</x:v>
+      <x:c r="AV9" s="31" t="str">
+        <x:v>Kuratiertes PuRe-Forschungsdatenfeld; 36 Datendatei(en) über OSF-API bestätigt</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="34" customHeight="1">
@@ -1946,17 +1878,13 @@
       <x:c r="AQ10" s="31" t="str"/>
       <x:c r="AR10" s="31" t="str"/>
       <x:c r="AS10" s="31" t="str"/>
-      <x:c r="AT10" s="37" t="str"/>
-      <x:c r="AU10" s="31" t="str"/>
-      <x:c r="AV10" s="31" t="str"/>
-      <x:c r="AW10" s="31" t="str"/>
-      <x:c r="AX10" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY10" s="31" t="str">
+      <x:c r="AT10" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU10" s="31" t="str">
         <x:v>Playwright</x:v>
       </x:c>
-      <x:c r="AZ10" s="31" t="str">
+      <x:c r="AV10" s="31" t="str">
         <x:v>Kuratiertes PuRe-Forschungsdatenfeld; Landingpage antwortet mit HTTP 403 und ist zugriffsgeschützt; Titel-/Autor:innen-Match (1.00); Landingpage antwortet mit HTTP 403 und ist zugriffsgeschützt</x:v>
       </x:c>
     </x:row>
@@ -2048,17 +1976,13 @@
       <x:c r="AQ11" s="31" t="str"/>
       <x:c r="AR11" s="31" t="str"/>
       <x:c r="AS11" s="31" t="str"/>
-      <x:c r="AT11" s="37" t="str"/>
-      <x:c r="AU11" s="31" t="str"/>
-      <x:c r="AV11" s="31" t="str"/>
-      <x:c r="AW11" s="31" t="str"/>
-      <x:c r="AX11" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY11" s="31" t="str">
+      <x:c r="AT11" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU11" s="31" t="str">
         <x:v>Playwright</x:v>
       </x:c>
-      <x:c r="AZ11" s="31" t="str">
+      <x:c r="AV11" s="31" t="str">
         <x:v>Kuratiertes PuRe-Forschungsdatenfeld; Landingpage antwortet mit HTTP 403 und ist zugriffsgeschützt; Titel-/Autor:innen-Match (1.00); Landingpage antwortet mit HTTP 403 und ist zugriffsgeschützt</x:v>
       </x:c>
     </x:row>
@@ -2142,18 +2066,14 @@
       <x:c r="AQ12" s="31" t="str"/>
       <x:c r="AR12" s="31" t="str"/>
       <x:c r="AS12" s="31" t="str"/>
-      <x:c r="AT12" s="37" t="str"/>
-      <x:c r="AU12" s="31" t="str"/>
-      <x:c r="AV12" s="31" t="str"/>
-      <x:c r="AW12" s="31" t="str"/>
-      <x:c r="AX12" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY12" s="31" t="str">
+      <x:c r="AT12" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU12" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ12" s="31" t="str">
-        <x:v>Kuratiertes PuRe-Forschungsdatenfeld</x:v>
+      <x:c r="AV12" s="31" t="str">
+        <x:v>Kuratiertes PuRe-Forschungsdatenfeld; 5 Datendatei(en) über OSF-API bestätigt</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="34" customHeight="1">
@@ -2236,18 +2156,14 @@
       <x:c r="AQ13" s="31" t="str"/>
       <x:c r="AR13" s="31" t="str"/>
       <x:c r="AS13" s="31" t="str"/>
-      <x:c r="AT13" s="37" t="str"/>
-      <x:c r="AU13" s="31" t="str"/>
-      <x:c r="AV13" s="31" t="str"/>
-      <x:c r="AW13" s="31" t="str"/>
-      <x:c r="AX13" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY13" s="31" t="str">
+      <x:c r="AT13" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU13" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ13" s="31" t="str">
-        <x:v>Kuratiertes PuRe-Forschungsdatenfeld</x:v>
+      <x:c r="AV13" s="31" t="str">
+        <x:v>Kuratiertes PuRe-Forschungsdatenfeld; 1 Datendatei(en) über OSF-API bestätigt</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="34" customHeight="1">
@@ -2338,18 +2254,14 @@
       <x:c r="AQ14" s="31" t="str"/>
       <x:c r="AR14" s="31" t="str"/>
       <x:c r="AS14" s="31" t="str"/>
-      <x:c r="AT14" s="37" t="str"/>
-      <x:c r="AU14" s="31" t="str"/>
-      <x:c r="AV14" s="31" t="str"/>
-      <x:c r="AW14" s="31" t="str"/>
-      <x:c r="AX14" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY14" s="31" t="str">
+      <x:c r="AT14" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU14" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ14" s="31" t="str">
-        <x:v>Kuratiertes PuRe-Forschungsdatenfeld; Link aus Data-Availability-Abschnitt des öffentlichen PuRe-Volltexts; 1 Datendatei(en) über OSF-API bestätigt</x:v>
+      <x:c r="AV14" s="31" t="str">
+        <x:v>Kuratiertes PuRe-Forschungsdatenfeld; 1 Datendatei(en) über OSF-API bestätigt; Link aus Data-Availability-Abschnitt des öffentlichen PuRe-Volltexts; 1 Datendatei(en) über OSF-API bestätigt</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="34" customHeight="1">
@@ -2432,18 +2344,14 @@
       <x:c r="AQ15" s="31" t="str"/>
       <x:c r="AR15" s="31" t="str"/>
       <x:c r="AS15" s="31" t="str"/>
-      <x:c r="AT15" s="37" t="str"/>
-      <x:c r="AU15" s="31" t="str"/>
-      <x:c r="AV15" s="31" t="str"/>
-      <x:c r="AW15" s="31" t="str"/>
-      <x:c r="AX15" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY15" s="31" t="str">
+      <x:c r="AT15" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU15" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ15" s="31" t="str">
-        <x:v>Kuratiertes PuRe-Forschungsdatenfeld</x:v>
+      <x:c r="AV15" s="31" t="str">
+        <x:v>Kuratiertes PuRe-Forschungsdatenfeld; 1 Datendatei(en) über OSF-API bestätigt</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -2526,18 +2434,14 @@
       <x:c r="AQ16" s="31" t="str"/>
       <x:c r="AR16" s="31" t="str"/>
       <x:c r="AS16" s="31" t="str"/>
-      <x:c r="AT16" s="37" t="str"/>
-      <x:c r="AU16" s="31" t="str"/>
-      <x:c r="AV16" s="31" t="str"/>
-      <x:c r="AW16" s="31" t="str"/>
-      <x:c r="AX16" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY16" s="31" t="str">
+      <x:c r="AT16" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU16" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ16" s="31" t="str">
-        <x:v>Kuratiertes PuRe-Forschungsdatenfeld</x:v>
+      <x:c r="AV16" s="31" t="str">
+        <x:v>Kuratiertes PuRe-Forschungsdatenfeld; 6 Datendatei(en) über OSF-API bestätigt</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="34" customHeight="1">
@@ -2620,17 +2524,13 @@
       <x:c r="AQ17" s="31" t="str"/>
       <x:c r="AR17" s="31" t="str"/>
       <x:c r="AS17" s="31" t="str"/>
-      <x:c r="AT17" s="37" t="str"/>
-      <x:c r="AU17" s="31" t="str"/>
-      <x:c r="AV17" s="31" t="str"/>
-      <x:c r="AW17" s="31" t="str"/>
-      <x:c r="AX17" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY17" s="31" t="str">
+      <x:c r="AT17" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU17" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ17" s="31" t="str">
+      <x:c r="AV17" s="31" t="str">
         <x:v>Titel-/Autor:innen-Match (1.00)</x:v>
       </x:c>
     </x:row>
@@ -2706,17 +2606,13 @@
       <x:c r="AQ18" s="31" t="str"/>
       <x:c r="AR18" s="31" t="str"/>
       <x:c r="AS18" s="31" t="str"/>
-      <x:c r="AT18" s="37" t="str"/>
-      <x:c r="AU18" s="31" t="str"/>
-      <x:c r="AV18" s="31" t="str"/>
-      <x:c r="AW18" s="31" t="str"/>
-      <x:c r="AX18" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY18" s="31" t="str">
+      <x:c r="AT18" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU18" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ18" s="31" t="str">
+      <x:c r="AV18" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -2788,17 +2684,13 @@
       <x:c r="AQ19" s="31" t="str"/>
       <x:c r="AR19" s="31" t="str"/>
       <x:c r="AS19" s="31" t="str"/>
-      <x:c r="AT19" s="37" t="str"/>
-      <x:c r="AU19" s="31" t="str"/>
-      <x:c r="AV19" s="31" t="str"/>
-      <x:c r="AW19" s="31" t="str"/>
-      <x:c r="AX19" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY19" s="31" t="str">
+      <x:c r="AT19" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU19" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ19" s="31" t="str">
+      <x:c r="AV19" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -2880,17 +2772,13 @@
       <x:c r="AQ20" s="31" t="str"/>
       <x:c r="AR20" s="31" t="str"/>
       <x:c r="AS20" s="31" t="str"/>
-      <x:c r="AT20" s="37" t="str"/>
-      <x:c r="AU20" s="31" t="str"/>
-      <x:c r="AV20" s="31" t="str"/>
-      <x:c r="AW20" s="31" t="str"/>
-      <x:c r="AX20" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY20" s="31" t="str">
+      <x:c r="AT20" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU20" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ20" s="31" t="str">
+      <x:c r="AV20" s="31" t="str">
         <x:v>Titel-/Autor:innen-Match (1.00); 1 Datendatei(en) über OSF-API bestätigt</x:v>
       </x:c>
     </x:row>
@@ -2974,17 +2862,13 @@
       <x:c r="AQ21" s="31" t="str"/>
       <x:c r="AR21" s="31" t="str"/>
       <x:c r="AS21" s="31" t="str"/>
-      <x:c r="AT21" s="37" t="str"/>
-      <x:c r="AU21" s="31" t="str"/>
-      <x:c r="AV21" s="31" t="str"/>
-      <x:c r="AW21" s="31" t="str"/>
-      <x:c r="AX21" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY21" s="31" t="str">
+      <x:c r="AT21" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU21" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ21" s="31" t="str">
+      <x:c r="AV21" s="31" t="str">
         <x:v>Titel-/Autor:innen-Match (1.00)</x:v>
       </x:c>
     </x:row>
@@ -3058,17 +2942,13 @@
       <x:c r="AQ22" s="31" t="str"/>
       <x:c r="AR22" s="31" t="str"/>
       <x:c r="AS22" s="31" t="str"/>
-      <x:c r="AT22" s="37" t="str"/>
-      <x:c r="AU22" s="31" t="str"/>
-      <x:c r="AV22" s="31" t="str"/>
-      <x:c r="AW22" s="31" t="str"/>
-      <x:c r="AX22" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY22" s="31" t="str">
+      <x:c r="AT22" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU22" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ22" s="31" t="str">
+      <x:c r="AV22" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -3144,17 +3024,13 @@
       <x:c r="AQ23" s="31" t="str"/>
       <x:c r="AR23" s="31" t="str"/>
       <x:c r="AS23" s="31" t="str"/>
-      <x:c r="AT23" s="37" t="str"/>
-      <x:c r="AU23" s="31" t="str"/>
-      <x:c r="AV23" s="31" t="str"/>
-      <x:c r="AW23" s="31" t="str"/>
-      <x:c r="AX23" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY23" s="31" t="str">
+      <x:c r="AT23" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU23" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ23" s="31" t="str">
+      <x:c r="AV23" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -3226,17 +3102,13 @@
       <x:c r="AQ24" s="31" t="str"/>
       <x:c r="AR24" s="31" t="str"/>
       <x:c r="AS24" s="31" t="str"/>
-      <x:c r="AT24" s="37" t="str"/>
-      <x:c r="AU24" s="31" t="str"/>
-      <x:c r="AV24" s="31" t="str"/>
-      <x:c r="AW24" s="31" t="str"/>
-      <x:c r="AX24" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY24" s="31" t="str">
+      <x:c r="AT24" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU24" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ24" s="31" t="str">
+      <x:c r="AV24" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -3312,17 +3184,13 @@
       <x:c r="AQ25" s="31" t="str"/>
       <x:c r="AR25" s="31" t="str"/>
       <x:c r="AS25" s="31" t="str"/>
-      <x:c r="AT25" s="37" t="str"/>
-      <x:c r="AU25" s="31" t="str"/>
-      <x:c r="AV25" s="31" t="str"/>
-      <x:c r="AW25" s="31" t="str"/>
-      <x:c r="AX25" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY25" s="31" t="str">
+      <x:c r="AT25" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU25" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ25" s="31" t="str">
+      <x:c r="AV25" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -3396,17 +3264,13 @@
       <x:c r="AQ26" s="31" t="str"/>
       <x:c r="AR26" s="31" t="str"/>
       <x:c r="AS26" s="31" t="str"/>
-      <x:c r="AT26" s="37" t="str"/>
-      <x:c r="AU26" s="31" t="str"/>
-      <x:c r="AV26" s="31" t="str"/>
-      <x:c r="AW26" s="31" t="str"/>
-      <x:c r="AX26" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY26" s="31" t="str">
+      <x:c r="AT26" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU26" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ26" s="31" t="str">
+      <x:c r="AV26" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -3490,17 +3354,13 @@
       <x:c r="AQ27" s="31" t="str"/>
       <x:c r="AR27" s="31" t="str"/>
       <x:c r="AS27" s="31" t="str"/>
-      <x:c r="AT27" s="37" t="str"/>
-      <x:c r="AU27" s="31" t="str"/>
-      <x:c r="AV27" s="31" t="str"/>
-      <x:c r="AW27" s="31" t="str"/>
-      <x:c r="AX27" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY27" s="31" t="str">
+      <x:c r="AT27" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU27" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ27" s="31" t="str">
+      <x:c r="AV27" s="31" t="str">
         <x:v>Titel-/Autor:innen-Match (1.00); 208 Datendatei(en) über OSF-API bestätigt</x:v>
       </x:c>
     </x:row>
@@ -3584,17 +3444,13 @@
       <x:c r="AQ28" s="31" t="str"/>
       <x:c r="AR28" s="31" t="str"/>
       <x:c r="AS28" s="31" t="str"/>
-      <x:c r="AT28" s="37" t="str"/>
-      <x:c r="AU28" s="31" t="str"/>
-      <x:c r="AV28" s="31" t="str"/>
-      <x:c r="AW28" s="31" t="str"/>
-      <x:c r="AX28" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY28" s="31" t="str">
+      <x:c r="AT28" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU28" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ28" s="31" t="str">
+      <x:c r="AV28" s="31" t="str">
         <x:v>Titel-/Autor:innen-Match (1.00); 7 Datendatei(en) über OSF-API bestätigt</x:v>
       </x:c>
     </x:row>
@@ -3668,17 +3524,13 @@
       <x:c r="AQ29" s="31" t="str"/>
       <x:c r="AR29" s="31" t="str"/>
       <x:c r="AS29" s="31" t="str"/>
-      <x:c r="AT29" s="37" t="str"/>
-      <x:c r="AU29" s="31" t="str"/>
-      <x:c r="AV29" s="31" t="str"/>
-      <x:c r="AW29" s="31" t="str"/>
-      <x:c r="AX29" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY29" s="31" t="str">
+      <x:c r="AT29" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU29" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ29" s="31" t="str">
+      <x:c r="AV29" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -3754,17 +3606,13 @@
       <x:c r="AQ30" s="31" t="str"/>
       <x:c r="AR30" s="31" t="str"/>
       <x:c r="AS30" s="31" t="str"/>
-      <x:c r="AT30" s="37" t="str"/>
-      <x:c r="AU30" s="31" t="str"/>
-      <x:c r="AV30" s="31" t="str"/>
-      <x:c r="AW30" s="31" t="str"/>
-      <x:c r="AX30" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY30" s="31" t="str">
+      <x:c r="AT30" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU30" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ30" s="31" t="str">
+      <x:c r="AV30" s="31" t="str">
         <x:v>Studienprotokoll/Registered Report ohne bereits belegte Datenausgabe</x:v>
       </x:c>
     </x:row>
@@ -3848,17 +3696,13 @@
       <x:c r="AQ31" s="31" t="str"/>
       <x:c r="AR31" s="31" t="str"/>
       <x:c r="AS31" s="31" t="str"/>
-      <x:c r="AT31" s="37" t="str"/>
-      <x:c r="AU31" s="31" t="str"/>
-      <x:c r="AV31" s="31" t="str"/>
-      <x:c r="AW31" s="31" t="str"/>
-      <x:c r="AX31" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY31" s="31" t="str">
+      <x:c r="AT31" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU31" s="31" t="str">
         <x:v>Playwright</x:v>
       </x:c>
-      <x:c r="AZ31" s="31" t="str">
+      <x:c r="AV31" s="31" t="str">
         <x:v>Offizielles INFORMS-Replikationsarchiv mit geprüften Datendateien</x:v>
       </x:c>
     </x:row>
@@ -3942,17 +3786,13 @@
       <x:c r="AQ32" s="31" t="str"/>
       <x:c r="AR32" s="31" t="str"/>
       <x:c r="AS32" s="31" t="str"/>
-      <x:c r="AT32" s="37" t="str"/>
-      <x:c r="AU32" s="31" t="str"/>
-      <x:c r="AV32" s="31" t="str"/>
-      <x:c r="AW32" s="31" t="str"/>
-      <x:c r="AX32" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY32" s="31" t="str">
+      <x:c r="AT32" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU32" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ32" s="31" t="str">
+      <x:c r="AV32" s="31" t="str">
         <x:v>Wiley-Datenverfügbarkeitsaussage mit rekursiv geprüften OSF-Datendateien; 17 Datendatei(en) über OSF-API bestätigt</x:v>
       </x:c>
     </x:row>
@@ -4032,17 +3872,13 @@
       <x:c r="AQ33" s="31" t="str"/>
       <x:c r="AR33" s="31" t="str"/>
       <x:c r="AS33" s="31" t="str"/>
-      <x:c r="AT33" s="37" t="str"/>
-      <x:c r="AU33" s="31" t="str"/>
-      <x:c r="AV33" s="31" t="str"/>
-      <x:c r="AW33" s="31" t="str"/>
-      <x:c r="AX33" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY33" s="31" t="str">
+      <x:c r="AT33" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU33" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ33" s="31" t="str">
+      <x:c r="AV33" s="31" t="str">
         <x:v>GitHub-README mit exaktem Publikationstitel und geprüften Datendateien; 55 Datendatei(en) über GitHub-API bestätigt</x:v>
       </x:c>
     </x:row>
@@ -4116,17 +3952,13 @@
       <x:c r="AQ34" s="31" t="str"/>
       <x:c r="AR34" s="31" t="str"/>
       <x:c r="AS34" s="31" t="str"/>
-      <x:c r="AT34" s="37" t="str"/>
-      <x:c r="AU34" s="31" t="str"/>
-      <x:c r="AV34" s="31" t="str"/>
-      <x:c r="AW34" s="31" t="str"/>
-      <x:c r="AX34" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY34" s="31" t="str">
+      <x:c r="AT34" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU34" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ34" s="31" t="str">
+      <x:c r="AV34" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -4216,17 +4048,13 @@
       <x:c r="AQ35" s="31" t="str"/>
       <x:c r="AR35" s="31" t="str"/>
       <x:c r="AS35" s="31" t="str"/>
-      <x:c r="AT35" s="37" t="str"/>
-      <x:c r="AU35" s="31" t="str"/>
-      <x:c r="AV35" s="31" t="str"/>
-      <x:c r="AW35" s="31" t="str"/>
-      <x:c r="AX35" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY35" s="31" t="str">
+      <x:c r="AT35" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU35" s="31" t="str">
         <x:v>Playwright</x:v>
       </x:c>
-      <x:c r="AZ35" s="31" t="str">
+      <x:c r="AV35" s="31" t="str">
         <x:v>Titel-/Autor:innen-Match (1.00); Landingpage antwortet mit HTTP 403 und ist zugriffsgeschützt</x:v>
       </x:c>
     </x:row>
@@ -4300,17 +4128,13 @@
       <x:c r="AQ36" s="31" t="str"/>
       <x:c r="AR36" s="31" t="str"/>
       <x:c r="AS36" s="31" t="str"/>
-      <x:c r="AT36" s="37" t="str"/>
-      <x:c r="AU36" s="31" t="str"/>
-      <x:c r="AV36" s="31" t="str"/>
-      <x:c r="AW36" s="31" t="str"/>
-      <x:c r="AX36" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY36" s="31" t="str">
+      <x:c r="AT36" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU36" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ36" s="31" t="str">
+      <x:c r="AV36" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -4394,18 +4218,14 @@
       <x:c r="AQ37" s="31" t="str"/>
       <x:c r="AR37" s="31" t="str"/>
       <x:c r="AS37" s="31" t="str"/>
-      <x:c r="AT37" s="37" t="str"/>
-      <x:c r="AU37" s="31" t="str"/>
-      <x:c r="AV37" s="31" t="str"/>
-      <x:c r="AW37" s="31" t="str"/>
-      <x:c r="AX37" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY37" s="31" t="str">
+      <x:c r="AT37" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU37" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ37" s="31" t="str">
-        <x:v>Explizite Data-Availability-Aussage der Verlagsseite</x:v>
+      <x:c r="AV37" s="31" t="str">
+        <x:v>Explizite Data-Availability-Aussage der Verlagsseite; 2 Datendatei(en) über OSF-API bestätigt</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="34" customHeight="1">
@@ -4480,17 +4300,13 @@
       <x:c r="AQ38" s="31" t="str"/>
       <x:c r="AR38" s="31" t="str"/>
       <x:c r="AS38" s="31" t="str"/>
-      <x:c r="AT38" s="37" t="str"/>
-      <x:c r="AU38" s="31" t="str"/>
-      <x:c r="AV38" s="31" t="str"/>
-      <x:c r="AW38" s="31" t="str"/>
-      <x:c r="AX38" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY38" s="31" t="str">
+      <x:c r="AT38" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU38" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ38" s="31" t="str">
+      <x:c r="AV38" s="31" t="str">
         <x:v>Verlagsseite nennt keine eindeutige vorhandene Datenausgabe</x:v>
       </x:c>
     </x:row>
@@ -4566,17 +4382,13 @@
       <x:c r="AQ39" s="31" t="str"/>
       <x:c r="AR39" s="31" t="str"/>
       <x:c r="AS39" s="31" t="str"/>
-      <x:c r="AT39" s="37" t="str"/>
-      <x:c r="AU39" s="31" t="str"/>
-      <x:c r="AV39" s="31" t="str"/>
-      <x:c r="AW39" s="31" t="str"/>
-      <x:c r="AX39" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY39" s="31" t="str">
+      <x:c r="AT39" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU39" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ39" s="31" t="str">
+      <x:c r="AV39" s="31" t="str">
         <x:v>Verlagsseite nennt keine eindeutige vorhandene Datenausgabe</x:v>
       </x:c>
     </x:row>
@@ -4652,17 +4464,13 @@
       <x:c r="AQ40" s="31" t="str"/>
       <x:c r="AR40" s="31" t="str"/>
       <x:c r="AS40" s="31" t="str"/>
-      <x:c r="AT40" s="37" t="str"/>
-      <x:c r="AU40" s="31" t="str"/>
-      <x:c r="AV40" s="31" t="str"/>
-      <x:c r="AW40" s="31" t="str"/>
-      <x:c r="AX40" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY40" s="31" t="str">
+      <x:c r="AT40" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU40" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ40" s="31" t="str">
+      <x:c r="AV40" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -4734,17 +4542,13 @@
       <x:c r="AQ41" s="31" t="str"/>
       <x:c r="AR41" s="31" t="str"/>
       <x:c r="AS41" s="31" t="str"/>
-      <x:c r="AT41" s="37" t="str"/>
-      <x:c r="AU41" s="31" t="str"/>
-      <x:c r="AV41" s="31" t="str"/>
-      <x:c r="AW41" s="31" t="str"/>
-      <x:c r="AX41" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY41" s="31" t="str">
+      <x:c r="AT41" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU41" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ41" s="31" t="str">
+      <x:c r="AV41" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -4820,17 +4624,13 @@
       <x:c r="AQ42" s="31" t="str"/>
       <x:c r="AR42" s="31" t="str"/>
       <x:c r="AS42" s="31" t="str"/>
-      <x:c r="AT42" s="37" t="str"/>
-      <x:c r="AU42" s="31" t="str"/>
-      <x:c r="AV42" s="31" t="str"/>
-      <x:c r="AW42" s="31" t="str"/>
-      <x:c r="AX42" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY42" s="31" t="str">
+      <x:c r="AT42" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU42" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ42" s="31" t="str">
+      <x:c r="AV42" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -4904,17 +4704,13 @@
       <x:c r="AQ43" s="31" t="str"/>
       <x:c r="AR43" s="31" t="str"/>
       <x:c r="AS43" s="31" t="str"/>
-      <x:c r="AT43" s="37" t="str"/>
-      <x:c r="AU43" s="31" t="str"/>
-      <x:c r="AV43" s="31" t="str"/>
-      <x:c r="AW43" s="31" t="str"/>
-      <x:c r="AX43" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY43" s="31" t="str">
+      <x:c r="AT43" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU43" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ43" s="31" t="str">
+      <x:c r="AV43" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -4990,17 +4786,13 @@
       <x:c r="AQ44" s="31" t="str"/>
       <x:c r="AR44" s="31" t="str"/>
       <x:c r="AS44" s="31" t="str"/>
-      <x:c r="AT44" s="37" t="str"/>
-      <x:c r="AU44" s="31" t="str"/>
-      <x:c r="AV44" s="31" t="str"/>
-      <x:c r="AW44" s="31" t="str"/>
-      <x:c r="AX44" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY44" s="31" t="str">
+      <x:c r="AT44" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU44" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ44" s="31" t="str">
+      <x:c r="AV44" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -5076,17 +4868,13 @@
       <x:c r="AQ45" s="31" t="str"/>
       <x:c r="AR45" s="31" t="str"/>
       <x:c r="AS45" s="31" t="str"/>
-      <x:c r="AT45" s="37" t="str"/>
-      <x:c r="AU45" s="31" t="str"/>
-      <x:c r="AV45" s="31" t="str"/>
-      <x:c r="AW45" s="31" t="str"/>
-      <x:c r="AX45" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY45" s="31" t="str">
+      <x:c r="AT45" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU45" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ45" s="31" t="str">
+      <x:c r="AV45" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -5160,17 +4948,13 @@
       <x:c r="AQ46" s="31" t="str"/>
       <x:c r="AR46" s="31" t="str"/>
       <x:c r="AS46" s="31" t="str"/>
-      <x:c r="AT46" s="37" t="str"/>
-      <x:c r="AU46" s="31" t="str"/>
-      <x:c r="AV46" s="31" t="str"/>
-      <x:c r="AW46" s="31" t="str"/>
-      <x:c r="AX46" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY46" s="31" t="str">
+      <x:c r="AT46" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU46" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ46" s="31" t="str">
+      <x:c r="AV46" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -5254,18 +5038,14 @@
       <x:c r="AQ47" s="31" t="str"/>
       <x:c r="AR47" s="31" t="str"/>
       <x:c r="AS47" s="31" t="str"/>
-      <x:c r="AT47" s="37" t="str"/>
-      <x:c r="AU47" s="31" t="str"/>
-      <x:c r="AV47" s="31" t="str"/>
-      <x:c r="AW47" s="31" t="str"/>
-      <x:c r="AX47" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY47" s="31" t="str">
+      <x:c r="AT47" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU47" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ47" s="31" t="str">
-        <x:v>Link aus expliziter Data-Availability-Statement; 6 Datendatei(en) über OSF-API bestätigt</x:v>
+      <x:c r="AV47" s="31" t="str">
+        <x:v>Link aus expliziter Data-Availability-Statement</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="34" customHeight="1">
@@ -5348,18 +5128,14 @@
       <x:c r="AQ48" s="31" t="str"/>
       <x:c r="AR48" s="31" t="str"/>
       <x:c r="AS48" s="31" t="str"/>
-      <x:c r="AT48" s="37" t="str"/>
-      <x:c r="AU48" s="31" t="str"/>
-      <x:c r="AV48" s="31" t="str"/>
-      <x:c r="AW48" s="31" t="str"/>
-      <x:c r="AX48" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY48" s="31" t="str">
+      <x:c r="AT48" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU48" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ48" s="31" t="str">
-        <x:v>Titel-/Autor:innen-Match (1.00); 9 Datendatei(en) über OSF-API bestätigt</x:v>
+      <x:c r="AV48" s="31" t="str">
+        <x:v>Titel-/Autor:innen-Match (1.00)</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="34" customHeight="1">
@@ -5393,19 +5169,27 @@
       <x:c r="J49" s="31" t="str">
         <x:v>no</x:v>
       </x:c>
-      <x:c r="K49" s="33" t="str">
-        <x:v>nein</x:v>
+      <x:c r="K49" s="32" t="str">
+        <x:v>ja</x:v>
       </x:c>
       <x:c r="L49" s="41" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M49" s="31" t="str">
-        <x:v>kein verifizierter Datenlink</x:v>
-      </x:c>
-      <x:c r="N49" s="37" t="str"/>
-      <x:c r="O49" s="31" t="str"/>
-      <x:c r="P49" s="31" t="str"/>
-      <x:c r="Q49" s="31" t="str"/>
+        <x:v>offen</x:v>
+      </x:c>
+      <x:c r="N49" s="37" t="str">
+        <x:v>https://osf.io/jz6wp/</x:v>
+      </x:c>
+      <x:c r="O49" s="31" t="str">
+        <x:v>Provider</x:v>
+      </x:c>
+      <x:c r="P49" s="31" t="str">
+        <x:v>offen</x:v>
+      </x:c>
+      <x:c r="Q49" s="31" t="str">
+        <x:v>HTTP 200; HTTP</x:v>
+      </x:c>
       <x:c r="R49" s="37" t="str"/>
       <x:c r="S49" s="31" t="str"/>
       <x:c r="T49" s="31" t="str"/>
@@ -5434,18 +5218,14 @@
       <x:c r="AQ49" s="31" t="str"/>
       <x:c r="AR49" s="31" t="str"/>
       <x:c r="AS49" s="31" t="str"/>
-      <x:c r="AT49" s="37" t="str"/>
-      <x:c r="AU49" s="31" t="str"/>
-      <x:c r="AV49" s="31" t="str"/>
-      <x:c r="AW49" s="31" t="str"/>
-      <x:c r="AX49" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY49" s="31" t="str">
-        <x:v>HTTP + Playwright-Audit</x:v>
-      </x:c>
-      <x:c r="AZ49" s="31" t="str">
-        <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
+      <x:c r="AT49" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU49" s="31" t="str">
+        <x:v>HTTP</x:v>
+      </x:c>
+      <x:c r="AV49" s="31" t="str">
+        <x:v>De-Gruyter-Datenverfügbarkeitsaussage mit Autor:innenbezug und rekursiv geprüften OSF-Datendateien</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="34" customHeight="1">
@@ -5528,17 +5308,13 @@
       <x:c r="AQ50" s="31" t="str"/>
       <x:c r="AR50" s="31" t="str"/>
       <x:c r="AS50" s="31" t="str"/>
-      <x:c r="AT50" s="37" t="str"/>
-      <x:c r="AU50" s="31" t="str"/>
-      <x:c r="AV50" s="31" t="str"/>
-      <x:c r="AW50" s="31" t="str"/>
-      <x:c r="AX50" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY50" s="31" t="str">
+      <x:c r="AT50" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU50" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ50" s="31" t="str">
+      <x:c r="AV50" s="31" t="str">
         <x:v>Titel-/Autor:innen-Match (1.00)</x:v>
       </x:c>
     </x:row>
@@ -5610,17 +5386,13 @@
       <x:c r="AQ51" s="31" t="str"/>
       <x:c r="AR51" s="31" t="str"/>
       <x:c r="AS51" s="31" t="str"/>
-      <x:c r="AT51" s="37" t="str"/>
-      <x:c r="AU51" s="31" t="str"/>
-      <x:c r="AV51" s="31" t="str"/>
-      <x:c r="AW51" s="31" t="str"/>
-      <x:c r="AX51" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY51" s="31" t="str">
+      <x:c r="AT51" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU51" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ51" s="31" t="str">
+      <x:c r="AV51" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -5694,17 +5466,13 @@
       <x:c r="AQ52" s="31" t="str"/>
       <x:c r="AR52" s="31" t="str"/>
       <x:c r="AS52" s="31" t="str"/>
-      <x:c r="AT52" s="37" t="str"/>
-      <x:c r="AU52" s="31" t="str"/>
-      <x:c r="AV52" s="31" t="str"/>
-      <x:c r="AW52" s="31" t="str"/>
-      <x:c r="AX52" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY52" s="31" t="str">
+      <x:c r="AT52" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU52" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ52" s="31" t="str">
+      <x:c r="AV52" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -5788,18 +5556,14 @@
       <x:c r="AQ53" s="31" t="str"/>
       <x:c r="AR53" s="31" t="str"/>
       <x:c r="AS53" s="31" t="str"/>
-      <x:c r="AT53" s="37" t="str"/>
-      <x:c r="AU53" s="31" t="str"/>
-      <x:c r="AV53" s="31" t="str"/>
-      <x:c r="AW53" s="31" t="str"/>
-      <x:c r="AX53" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY53" s="31" t="str">
+      <x:c r="AT53" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU53" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ53" s="31" t="str">
-        <x:v>Explizite Data-Availability-Aussage der Verlagsseite</x:v>
+      <x:c r="AV53" s="31" t="str">
+        <x:v>Explizite Data-Availability-Aussage der Verlagsseite; 13 Datendatei(en) über OSF-API bestätigt</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="34" customHeight="1">
@@ -5882,17 +5646,13 @@
       <x:c r="AQ54" s="31" t="str"/>
       <x:c r="AR54" s="31" t="str"/>
       <x:c r="AS54" s="31" t="str"/>
-      <x:c r="AT54" s="37" t="str"/>
-      <x:c r="AU54" s="31" t="str"/>
-      <x:c r="AV54" s="31" t="str"/>
-      <x:c r="AW54" s="31" t="str"/>
-      <x:c r="AX54" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY54" s="31" t="str">
+      <x:c r="AT54" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU54" s="31" t="str">
         <x:v>Playwright</x:v>
       </x:c>
-      <x:c r="AZ54" s="31" t="str">
+      <x:c r="AV54" s="31" t="str">
         <x:v>Titel-/Autor:innen-Match (1.00)</x:v>
       </x:c>
     </x:row>
@@ -5968,17 +5728,13 @@
       <x:c r="AQ55" s="31" t="str"/>
       <x:c r="AR55" s="31" t="str"/>
       <x:c r="AS55" s="31" t="str"/>
-      <x:c r="AT55" s="37" t="str"/>
-      <x:c r="AU55" s="31" t="str"/>
-      <x:c r="AV55" s="31" t="str"/>
-      <x:c r="AW55" s="31" t="str"/>
-      <x:c r="AX55" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY55" s="31" t="str">
+      <x:c r="AT55" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU55" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ55" s="31" t="str">
+      <x:c r="AV55" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -6052,17 +5808,13 @@
       <x:c r="AQ56" s="31" t="str"/>
       <x:c r="AR56" s="31" t="str"/>
       <x:c r="AS56" s="31" t="str"/>
-      <x:c r="AT56" s="37" t="str"/>
-      <x:c r="AU56" s="31" t="str"/>
-      <x:c r="AV56" s="31" t="str"/>
-      <x:c r="AW56" s="31" t="str"/>
-      <x:c r="AX56" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY56" s="31" t="str">
+      <x:c r="AT56" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU56" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ56" s="31" t="str">
+      <x:c r="AV56" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -6136,17 +5888,13 @@
       <x:c r="AQ57" s="31" t="str"/>
       <x:c r="AR57" s="31" t="str"/>
       <x:c r="AS57" s="31" t="str"/>
-      <x:c r="AT57" s="37" t="str"/>
-      <x:c r="AU57" s="31" t="str"/>
-      <x:c r="AV57" s="31" t="str"/>
-      <x:c r="AW57" s="31" t="str"/>
-      <x:c r="AX57" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY57" s="31" t="str">
+      <x:c r="AT57" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU57" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ57" s="31" t="str">
+      <x:c r="AV57" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -6181,19 +5929,27 @@
       <x:c r="J58" s="31" t="str">
         <x:v>no</x:v>
       </x:c>
-      <x:c r="K58" s="33" t="str">
-        <x:v>nein</x:v>
+      <x:c r="K58" s="32" t="str">
+        <x:v>ja</x:v>
       </x:c>
       <x:c r="L58" s="41" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M58" s="31" t="str">
-        <x:v>kein verifizierter Datenlink</x:v>
-      </x:c>
-      <x:c r="N58" s="37" t="str"/>
-      <x:c r="O58" s="31" t="str"/>
-      <x:c r="P58" s="31" t="str"/>
-      <x:c r="Q58" s="31" t="str"/>
+        <x:v>offen</x:v>
+      </x:c>
+      <x:c r="N58" s="37" t="str">
+        <x:v>https://osf.io/aq7zd</x:v>
+      </x:c>
+      <x:c r="O58" s="31" t="str">
+        <x:v>Provider</x:v>
+      </x:c>
+      <x:c r="P58" s="31" t="str">
+        <x:v>offen</x:v>
+      </x:c>
+      <x:c r="Q58" s="31" t="str">
+        <x:v>HTTP 200; HTTP</x:v>
+      </x:c>
       <x:c r="R58" s="37" t="str"/>
       <x:c r="S58" s="31" t="str"/>
       <x:c r="T58" s="31" t="str"/>
@@ -6222,18 +5978,14 @@
       <x:c r="AQ58" s="31" t="str"/>
       <x:c r="AR58" s="31" t="str"/>
       <x:c r="AS58" s="31" t="str"/>
-      <x:c r="AT58" s="37" t="str"/>
-      <x:c r="AU58" s="31" t="str"/>
-      <x:c r="AV58" s="31" t="str"/>
-      <x:c r="AW58" s="31" t="str"/>
-      <x:c r="AX58" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY58" s="31" t="str">
-        <x:v>HTTP + Playwright-Audit</x:v>
-      </x:c>
-      <x:c r="AZ58" s="31" t="str">
-        <x:v>Verlagsseite nennt keine eindeutige vorhandene Datenausgabe; Dataset-Treffer ohne hinreichend engen Publikationsbezug (0.00)</x:v>
+      <x:c r="AT58" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU58" s="31" t="str">
+        <x:v>HTTP</x:v>
+      </x:c>
+      <x:c r="AV58" s="31" t="str">
+        <x:v>Cambridge-verlinktes OSF-Projekt mit Autor:innenbezug und rekursiv geprüften Datendateien</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="34" customHeight="1">
@@ -6306,17 +6058,13 @@
       <x:c r="AQ59" s="31" t="str"/>
       <x:c r="AR59" s="31" t="str"/>
       <x:c r="AS59" s="31" t="str"/>
-      <x:c r="AT59" s="37" t="str"/>
-      <x:c r="AU59" s="31" t="str"/>
-      <x:c r="AV59" s="31" t="str"/>
-      <x:c r="AW59" s="31" t="str"/>
-      <x:c r="AX59" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY59" s="31" t="str">
+      <x:c r="AT59" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU59" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ59" s="31" t="str">
+      <x:c r="AV59" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -6390,17 +6138,13 @@
       <x:c r="AQ60" s="31" t="str"/>
       <x:c r="AR60" s="31" t="str"/>
       <x:c r="AS60" s="31" t="str"/>
-      <x:c r="AT60" s="37" t="str"/>
-      <x:c r="AU60" s="31" t="str"/>
-      <x:c r="AV60" s="31" t="str"/>
-      <x:c r="AW60" s="31" t="str"/>
-      <x:c r="AX60" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY60" s="31" t="str">
+      <x:c r="AT60" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU60" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ60" s="31" t="str">
+      <x:c r="AV60" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -6476,17 +6220,13 @@
       <x:c r="AQ61" s="31" t="str"/>
       <x:c r="AR61" s="31" t="str"/>
       <x:c r="AS61" s="31" t="str"/>
-      <x:c r="AT61" s="37" t="str"/>
-      <x:c r="AU61" s="31" t="str"/>
-      <x:c r="AV61" s="31" t="str"/>
-      <x:c r="AW61" s="31" t="str"/>
-      <x:c r="AX61" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY61" s="31" t="str">
+      <x:c r="AT61" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU61" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ61" s="31" t="str">
+      <x:c r="AV61" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -6560,17 +6300,13 @@
       <x:c r="AQ62" s="31" t="str"/>
       <x:c r="AR62" s="31" t="str"/>
       <x:c r="AS62" s="31" t="str"/>
-      <x:c r="AT62" s="37" t="str"/>
-      <x:c r="AU62" s="31" t="str"/>
-      <x:c r="AV62" s="31" t="str"/>
-      <x:c r="AW62" s="31" t="str"/>
-      <x:c r="AX62" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY62" s="31" t="str">
+      <x:c r="AT62" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU62" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ62" s="31" t="str">
+      <x:c r="AV62" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -6646,17 +6382,13 @@
       <x:c r="AQ63" s="31" t="str"/>
       <x:c r="AR63" s="31" t="str"/>
       <x:c r="AS63" s="31" t="str"/>
-      <x:c r="AT63" s="37" t="str"/>
-      <x:c r="AU63" s="31" t="str"/>
-      <x:c r="AV63" s="31" t="str"/>
-      <x:c r="AW63" s="31" t="str"/>
-      <x:c r="AX63" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY63" s="31" t="str">
+      <x:c r="AT63" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU63" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ63" s="31" t="str">
+      <x:c r="AV63" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -6732,17 +6464,13 @@
       <x:c r="AQ64" s="31" t="str"/>
       <x:c r="AR64" s="31" t="str"/>
       <x:c r="AS64" s="31" t="str"/>
-      <x:c r="AT64" s="37" t="str"/>
-      <x:c r="AU64" s="31" t="str"/>
-      <x:c r="AV64" s="31" t="str"/>
-      <x:c r="AW64" s="31" t="str"/>
-      <x:c r="AX64" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY64" s="31" t="str">
+      <x:c r="AT64" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU64" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ64" s="31" t="str">
+      <x:c r="AV64" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -6818,17 +6546,13 @@
       <x:c r="AQ65" s="31" t="str"/>
       <x:c r="AR65" s="31" t="str"/>
       <x:c r="AS65" s="31" t="str"/>
-      <x:c r="AT65" s="37" t="str"/>
-      <x:c r="AU65" s="31" t="str"/>
-      <x:c r="AV65" s="31" t="str"/>
-      <x:c r="AW65" s="31" t="str"/>
-      <x:c r="AX65" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY65" s="31" t="str">
+      <x:c r="AT65" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU65" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ65" s="31" t="str">
+      <x:c r="AV65" s="31" t="str">
         <x:v>Dataset-Treffer ohne hinreichend engen Publikationsbezug (0.00)</x:v>
       </x:c>
     </x:row>
@@ -6904,17 +6628,13 @@
       <x:c r="AQ66" s="31" t="str"/>
       <x:c r="AR66" s="31" t="str"/>
       <x:c r="AS66" s="31" t="str"/>
-      <x:c r="AT66" s="37" t="str"/>
-      <x:c r="AU66" s="31" t="str"/>
-      <x:c r="AV66" s="31" t="str"/>
-      <x:c r="AW66" s="31" t="str"/>
-      <x:c r="AX66" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY66" s="31" t="str">
+      <x:c r="AT66" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU66" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ66" s="31" t="str">
+      <x:c r="AV66" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -6990,17 +6710,13 @@
       <x:c r="AQ67" s="31" t="str"/>
       <x:c r="AR67" s="31" t="str"/>
       <x:c r="AS67" s="31" t="str"/>
-      <x:c r="AT67" s="37" t="str"/>
-      <x:c r="AU67" s="31" t="str"/>
-      <x:c r="AV67" s="31" t="str"/>
-      <x:c r="AW67" s="31" t="str"/>
-      <x:c r="AX67" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY67" s="31" t="str">
+      <x:c r="AT67" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU67" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ67" s="31" t="str">
+      <x:c r="AV67" s="31" t="str">
         <x:v>Studienprotokoll/Registered Report ohne bereits belegte Datenausgabe</x:v>
       </x:c>
     </x:row>
@@ -7076,17 +6792,13 @@
       <x:c r="AQ68" s="31" t="str"/>
       <x:c r="AR68" s="31" t="str"/>
       <x:c r="AS68" s="31" t="str"/>
-      <x:c r="AT68" s="37" t="str"/>
-      <x:c r="AU68" s="31" t="str"/>
-      <x:c r="AV68" s="31" t="str"/>
-      <x:c r="AW68" s="31" t="str"/>
-      <x:c r="AX68" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY68" s="31" t="str">
+      <x:c r="AT68" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU68" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ68" s="31" t="str">
+      <x:c r="AV68" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -7160,17 +6872,13 @@
       <x:c r="AQ69" s="31" t="str"/>
       <x:c r="AR69" s="31" t="str"/>
       <x:c r="AS69" s="31" t="str"/>
-      <x:c r="AT69" s="37" t="str"/>
-      <x:c r="AU69" s="31" t="str"/>
-      <x:c r="AV69" s="31" t="str"/>
-      <x:c r="AW69" s="31" t="str"/>
-      <x:c r="AX69" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY69" s="31" t="str">
+      <x:c r="AT69" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU69" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ69" s="31" t="str">
+      <x:c r="AV69" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -7246,17 +6954,13 @@
       <x:c r="AQ70" s="31" t="str"/>
       <x:c r="AR70" s="31" t="str"/>
       <x:c r="AS70" s="31" t="str"/>
-      <x:c r="AT70" s="37" t="str"/>
-      <x:c r="AU70" s="31" t="str"/>
-      <x:c r="AV70" s="31" t="str"/>
-      <x:c r="AW70" s="31" t="str"/>
-      <x:c r="AX70" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY70" s="31" t="str">
+      <x:c r="AT70" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU70" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ70" s="31" t="str">
+      <x:c r="AV70" s="31" t="str">
         <x:v>Verlagsseite nennt keine eindeutige vorhandene Datenausgabe</x:v>
       </x:c>
     </x:row>
@@ -7330,17 +7034,13 @@
       <x:c r="AQ71" s="31" t="str"/>
       <x:c r="AR71" s="31" t="str"/>
       <x:c r="AS71" s="31" t="str"/>
-      <x:c r="AT71" s="37" t="str"/>
-      <x:c r="AU71" s="31" t="str"/>
-      <x:c r="AV71" s="31" t="str"/>
-      <x:c r="AW71" s="31" t="str"/>
-      <x:c r="AX71" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY71" s="31" t="str">
+      <x:c r="AT71" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU71" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ71" s="31" t="str">
+      <x:c r="AV71" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -7416,17 +7116,13 @@
       <x:c r="AQ72" s="31" t="str"/>
       <x:c r="AR72" s="31" t="str"/>
       <x:c r="AS72" s="31" t="str"/>
-      <x:c r="AT72" s="37" t="str"/>
-      <x:c r="AU72" s="31" t="str"/>
-      <x:c r="AV72" s="31" t="str"/>
-      <x:c r="AW72" s="31" t="str"/>
-      <x:c r="AX72" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY72" s="31" t="str">
+      <x:c r="AT72" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU72" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ72" s="31" t="str">
+      <x:c r="AV72" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -7500,17 +7196,13 @@
       <x:c r="AQ73" s="31" t="str"/>
       <x:c r="AR73" s="31" t="str"/>
       <x:c r="AS73" s="31" t="str"/>
-      <x:c r="AT73" s="37" t="str"/>
-      <x:c r="AU73" s="31" t="str"/>
-      <x:c r="AV73" s="31" t="str"/>
-      <x:c r="AW73" s="31" t="str"/>
-      <x:c r="AX73" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY73" s="31" t="str">
+      <x:c r="AT73" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU73" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ73" s="31" t="str">
+      <x:c r="AV73" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -7585,17 +7277,13 @@
       <x:c r="AQ74" s="31" t="str"/>
       <x:c r="AR74" s="31" t="str"/>
       <x:c r="AS74" s="31" t="str"/>
-      <x:c r="AT74" s="37" t="str"/>
-      <x:c r="AU74" s="31" t="str"/>
-      <x:c r="AV74" s="31" t="str"/>
-      <x:c r="AW74" s="31" t="str"/>
-      <x:c r="AX74" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY74" s="31" t="str">
+      <x:c r="AT74" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU74" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ74" s="31" t="str">
+      <x:c r="AV74" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -7669,17 +7357,13 @@
       <x:c r="AQ75" s="31" t="str"/>
       <x:c r="AR75" s="31" t="str"/>
       <x:c r="AS75" s="31" t="str"/>
-      <x:c r="AT75" s="37" t="str"/>
-      <x:c r="AU75" s="31" t="str"/>
-      <x:c r="AV75" s="31" t="str"/>
-      <x:c r="AW75" s="31" t="str"/>
-      <x:c r="AX75" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY75" s="31" t="str">
+      <x:c r="AT75" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU75" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ75" s="31" t="str">
+      <x:c r="AV75" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -7763,17 +7447,13 @@
       <x:c r="AQ76" s="31" t="str"/>
       <x:c r="AR76" s="31" t="str"/>
       <x:c r="AS76" s="31" t="str"/>
-      <x:c r="AT76" s="37" t="str"/>
-      <x:c r="AU76" s="31" t="str"/>
-      <x:c r="AV76" s="31" t="str"/>
-      <x:c r="AW76" s="31" t="str"/>
-      <x:c r="AX76" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY76" s="31" t="str">
+      <x:c r="AT76" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU76" s="31" t="str">
         <x:v>Playwright</x:v>
       </x:c>
-      <x:c r="AZ76" s="31" t="str">
+      <x:c r="AV76" s="31" t="str">
         <x:v>Direkter Data-and-Code-Link auf der AEA-Artikelseite; Landingpage antwortet mit HTTP 403 und ist zugriffsgeschützt</x:v>
       </x:c>
     </x:row>
@@ -7847,17 +7527,13 @@
       <x:c r="AQ77" s="31" t="str"/>
       <x:c r="AR77" s="31" t="str"/>
       <x:c r="AS77" s="31" t="str"/>
-      <x:c r="AT77" s="37" t="str"/>
-      <x:c r="AU77" s="31" t="str"/>
-      <x:c r="AV77" s="31" t="str"/>
-      <x:c r="AW77" s="31" t="str"/>
-      <x:c r="AX77" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY77" s="31" t="str">
+      <x:c r="AT77" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU77" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ77" s="31" t="str">
+      <x:c r="AV77" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -7941,18 +7617,14 @@
       <x:c r="AQ78" s="31" t="str"/>
       <x:c r="AR78" s="31" t="str"/>
       <x:c r="AS78" s="31" t="str"/>
-      <x:c r="AT78" s="37" t="str"/>
-      <x:c r="AU78" s="31" t="str"/>
-      <x:c r="AV78" s="31" t="str"/>
-      <x:c r="AW78" s="31" t="str"/>
-      <x:c r="AX78" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY78" s="31" t="str">
+      <x:c r="AT78" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU78" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ78" s="31" t="str">
-        <x:v>Link aus expliziter Data-Availability-Statement; 6 Datendatei(en) über OSF-API bestätigt</x:v>
+      <x:c r="AV78" s="31" t="str">
+        <x:v>Link aus expliziter Data-Availability-Statement</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="34" customHeight="1">
@@ -8035,17 +7707,13 @@
       <x:c r="AQ79" s="31" t="str"/>
       <x:c r="AR79" s="31" t="str"/>
       <x:c r="AS79" s="31" t="str"/>
-      <x:c r="AT79" s="37" t="str"/>
-      <x:c r="AU79" s="31" t="str"/>
-      <x:c r="AV79" s="31" t="str"/>
-      <x:c r="AW79" s="31" t="str"/>
-      <x:c r="AX79" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY79" s="31" t="str">
+      <x:c r="AT79" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU79" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ79" s="31" t="str">
+      <x:c r="AV79" s="31" t="str">
         <x:v>Link aus expliziter Data-Availability-Statement</x:v>
       </x:c>
     </x:row>
@@ -8119,17 +7787,13 @@
       <x:c r="AQ80" s="31" t="str"/>
       <x:c r="AR80" s="31" t="str"/>
       <x:c r="AS80" s="31" t="str"/>
-      <x:c r="AT80" s="37" t="str"/>
-      <x:c r="AU80" s="31" t="str"/>
-      <x:c r="AV80" s="31" t="str"/>
-      <x:c r="AW80" s="31" t="str"/>
-      <x:c r="AX80" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY80" s="31" t="str">
+      <x:c r="AT80" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU80" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ80" s="31" t="str">
+      <x:c r="AV80" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -8203,17 +7867,13 @@
       <x:c r="AQ81" s="31" t="str"/>
       <x:c r="AR81" s="31" t="str"/>
       <x:c r="AS81" s="31" t="str"/>
-      <x:c r="AT81" s="37" t="str"/>
-      <x:c r="AU81" s="31" t="str"/>
-      <x:c r="AV81" s="31" t="str"/>
-      <x:c r="AW81" s="31" t="str"/>
-      <x:c r="AX81" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY81" s="31" t="str">
+      <x:c r="AT81" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU81" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ81" s="31" t="str">
+      <x:c r="AV81" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -8289,17 +7949,13 @@
       <x:c r="AQ82" s="31" t="str"/>
       <x:c r="AR82" s="31" t="str"/>
       <x:c r="AS82" s="31" t="str"/>
-      <x:c r="AT82" s="37" t="str"/>
-      <x:c r="AU82" s="31" t="str"/>
-      <x:c r="AV82" s="31" t="str"/>
-      <x:c r="AW82" s="31" t="str"/>
-      <x:c r="AX82" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY82" s="31" t="str">
+      <x:c r="AT82" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU82" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ82" s="31" t="str">
+      <x:c r="AV82" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -8375,17 +8031,13 @@
       <x:c r="AQ83" s="31" t="str"/>
       <x:c r="AR83" s="31" t="str"/>
       <x:c r="AS83" s="31" t="str"/>
-      <x:c r="AT83" s="37" t="str"/>
-      <x:c r="AU83" s="31" t="str"/>
-      <x:c r="AV83" s="31" t="str"/>
-      <x:c r="AW83" s="31" t="str"/>
-      <x:c r="AX83" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY83" s="31" t="str">
+      <x:c r="AT83" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU83" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ83" s="31" t="str">
+      <x:c r="AV83" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -8461,17 +8113,13 @@
       <x:c r="AQ84" s="31" t="str"/>
       <x:c r="AR84" s="31" t="str"/>
       <x:c r="AS84" s="31" t="str"/>
-      <x:c r="AT84" s="37" t="str"/>
-      <x:c r="AU84" s="31" t="str"/>
-      <x:c r="AV84" s="31" t="str"/>
-      <x:c r="AW84" s="31" t="str"/>
-      <x:c r="AX84" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY84" s="31" t="str">
+      <x:c r="AT84" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU84" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ84" s="31" t="str">
+      <x:c r="AV84" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -8545,17 +8193,13 @@
       <x:c r="AQ85" s="31" t="str"/>
       <x:c r="AR85" s="31" t="str"/>
       <x:c r="AS85" s="31" t="str"/>
-      <x:c r="AT85" s="37" t="str"/>
-      <x:c r="AU85" s="31" t="str"/>
-      <x:c r="AV85" s="31" t="str"/>
-      <x:c r="AW85" s="31" t="str"/>
-      <x:c r="AX85" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY85" s="31" t="str">
+      <x:c r="AT85" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU85" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ85" s="31" t="str">
+      <x:c r="AV85" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -8630,17 +8274,13 @@
       <x:c r="AQ86" s="31" t="str"/>
       <x:c r="AR86" s="31" t="str"/>
       <x:c r="AS86" s="31" t="str"/>
-      <x:c r="AT86" s="37" t="str"/>
-      <x:c r="AU86" s="31" t="str"/>
-      <x:c r="AV86" s="31" t="str"/>
-      <x:c r="AW86" s="31" t="str"/>
-      <x:c r="AX86" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY86" s="31" t="str">
+      <x:c r="AT86" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU86" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ86" s="31" t="str">
+      <x:c r="AV86" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -8714,17 +8354,13 @@
       <x:c r="AQ87" s="31" t="str"/>
       <x:c r="AR87" s="31" t="str"/>
       <x:c r="AS87" s="31" t="str"/>
-      <x:c r="AT87" s="37" t="str"/>
-      <x:c r="AU87" s="31" t="str"/>
-      <x:c r="AV87" s="31" t="str"/>
-      <x:c r="AW87" s="31" t="str"/>
-      <x:c r="AX87" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY87" s="31" t="str">
+      <x:c r="AT87" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU87" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ87" s="31" t="str">
+      <x:c r="AV87" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -8798,17 +8434,13 @@
       <x:c r="AQ88" s="31" t="str"/>
       <x:c r="AR88" s="31" t="str"/>
       <x:c r="AS88" s="31" t="str"/>
-      <x:c r="AT88" s="37" t="str"/>
-      <x:c r="AU88" s="31" t="str"/>
-      <x:c r="AV88" s="31" t="str"/>
-      <x:c r="AW88" s="31" t="str"/>
-      <x:c r="AX88" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY88" s="31" t="str">
+      <x:c r="AT88" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU88" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ88" s="31" t="str">
+      <x:c r="AV88" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -8882,17 +8514,13 @@
       <x:c r="AQ89" s="31" t="str"/>
       <x:c r="AR89" s="31" t="str"/>
       <x:c r="AS89" s="31" t="str"/>
-      <x:c r="AT89" s="37" t="str"/>
-      <x:c r="AU89" s="31" t="str"/>
-      <x:c r="AV89" s="31" t="str"/>
-      <x:c r="AW89" s="31" t="str"/>
-      <x:c r="AX89" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY89" s="31" t="str">
+      <x:c r="AT89" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU89" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ89" s="31" t="str">
+      <x:c r="AV89" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -8976,17 +8604,13 @@
       <x:c r="AQ90" s="31" t="str"/>
       <x:c r="AR90" s="31" t="str"/>
       <x:c r="AS90" s="31" t="str"/>
-      <x:c r="AT90" s="37" t="str"/>
-      <x:c r="AU90" s="31" t="str"/>
-      <x:c r="AV90" s="31" t="str"/>
-      <x:c r="AW90" s="31" t="str"/>
-      <x:c r="AX90" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY90" s="31" t="str">
+      <x:c r="AT90" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU90" s="31" t="str">
         <x:v>Playwright</x:v>
       </x:c>
-      <x:c r="AZ90" s="31" t="str">
+      <x:c r="AV90" s="31" t="str">
         <x:v>Direkter Data-and-Code-Link auf der AEA-Artikelseite; Landingpage antwortet mit HTTP 403 und ist zugriffsgeschützt</x:v>
       </x:c>
     </x:row>
@@ -9070,17 +8694,13 @@
       <x:c r="AQ91" s="31" t="str"/>
       <x:c r="AR91" s="31" t="str"/>
       <x:c r="AS91" s="31" t="str"/>
-      <x:c r="AT91" s="37" t="str"/>
-      <x:c r="AU91" s="31" t="str"/>
-      <x:c r="AV91" s="31" t="str"/>
-      <x:c r="AW91" s="31" t="str"/>
-      <x:c r="AX91" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY91" s="31" t="str">
+      <x:c r="AT91" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU91" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ91" s="31" t="str">
+      <x:c r="AV91" s="31" t="str">
         <x:v>Titel-/Autor:innen-Match (1.00)</x:v>
       </x:c>
     </x:row>
@@ -9154,17 +8774,13 @@
       <x:c r="AQ92" s="31" t="str"/>
       <x:c r="AR92" s="31" t="str"/>
       <x:c r="AS92" s="31" t="str"/>
-      <x:c r="AT92" s="37" t="str"/>
-      <x:c r="AU92" s="31" t="str"/>
-      <x:c r="AV92" s="31" t="str"/>
-      <x:c r="AW92" s="31" t="str"/>
-      <x:c r="AX92" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY92" s="31" t="str">
+      <x:c r="AT92" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU92" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ92" s="31" t="str">
+      <x:c r="AV92" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -9238,17 +8854,13 @@
       <x:c r="AQ93" s="31" t="str"/>
       <x:c r="AR93" s="31" t="str"/>
       <x:c r="AS93" s="31" t="str"/>
-      <x:c r="AT93" s="37" t="str"/>
-      <x:c r="AU93" s="31" t="str"/>
-      <x:c r="AV93" s="31" t="str"/>
-      <x:c r="AW93" s="31" t="str"/>
-      <x:c r="AX93" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY93" s="31" t="str">
+      <x:c r="AT93" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU93" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ93" s="31" t="str">
+      <x:c r="AV93" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -9322,17 +8934,13 @@
       <x:c r="AQ94" s="31" t="str"/>
       <x:c r="AR94" s="31" t="str"/>
       <x:c r="AS94" s="31" t="str"/>
-      <x:c r="AT94" s="37" t="str"/>
-      <x:c r="AU94" s="31" t="str"/>
-      <x:c r="AV94" s="31" t="str"/>
-      <x:c r="AW94" s="31" t="str"/>
-      <x:c r="AX94" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY94" s="31" t="str">
+      <x:c r="AT94" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU94" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ94" s="31" t="str">
+      <x:c r="AV94" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -9406,17 +9014,13 @@
       <x:c r="AQ95" s="31" t="str"/>
       <x:c r="AR95" s="31" t="str"/>
       <x:c r="AS95" s="31" t="str"/>
-      <x:c r="AT95" s="37" t="str"/>
-      <x:c r="AU95" s="31" t="str"/>
-      <x:c r="AV95" s="31" t="str"/>
-      <x:c r="AW95" s="31" t="str"/>
-      <x:c r="AX95" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY95" s="31" t="str">
+      <x:c r="AT95" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU95" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ95" s="31" t="str">
+      <x:c r="AV95" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -9451,23 +9055,39 @@
       <x:c r="J96" s="31" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="K96" s="33" t="str">
-        <x:v>nein</x:v>
+      <x:c r="K96" s="32" t="str">
+        <x:v>ja</x:v>
       </x:c>
       <x:c r="L96" s="41" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="M96" s="31" t="str">
-        <x:v>kein verifizierter Datenlink</x:v>
-      </x:c>
-      <x:c r="N96" s="37" t="str"/>
-      <x:c r="O96" s="31" t="str"/>
-      <x:c r="P96" s="31" t="str"/>
-      <x:c r="Q96" s="31" t="str"/>
-      <x:c r="R96" s="37" t="str"/>
-      <x:c r="S96" s="31" t="str"/>
-      <x:c r="T96" s="31" t="str"/>
-      <x:c r="U96" s="31" t="str"/>
+        <x:v>offen über View-only-Link</x:v>
+      </x:c>
+      <x:c r="N96" s="37" t="str">
+        <x:v>https://osf.io/adeh5/?view_only=9d3c95593d2a4fe4a4a835f2ac572b09</x:v>
+      </x:c>
+      <x:c r="O96" s="31" t="str">
+        <x:v>Provider</x:v>
+      </x:c>
+      <x:c r="P96" s="39" t="str">
+        <x:v>offen über View-only-Link</x:v>
+      </x:c>
+      <x:c r="Q96" s="31" t="str">
+        <x:v>HTTP 200; HTTP</x:v>
+      </x:c>
+      <x:c r="R96" s="37" t="str">
+        <x:v>https://osf.io/wrfn6/?view_only=23f44ea20641426695b71f78b2985f8d</x:v>
+      </x:c>
+      <x:c r="S96" s="31" t="str">
+        <x:v>Provider</x:v>
+      </x:c>
+      <x:c r="T96" s="39" t="str">
+        <x:v>offen über View-only-Link</x:v>
+      </x:c>
+      <x:c r="U96" s="31" t="str">
+        <x:v>HTTP 200; HTTP</x:v>
+      </x:c>
       <x:c r="V96" s="37" t="str"/>
       <x:c r="W96" s="31" t="str"/>
       <x:c r="X96" s="31" t="str"/>
@@ -9492,18 +9112,14 @@
       <x:c r="AQ96" s="31" t="str"/>
       <x:c r="AR96" s="31" t="str"/>
       <x:c r="AS96" s="31" t="str"/>
-      <x:c r="AT96" s="37" t="str"/>
-      <x:c r="AU96" s="31" t="str"/>
-      <x:c r="AV96" s="31" t="str"/>
-      <x:c r="AW96" s="31" t="str"/>
-      <x:c r="AX96" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY96" s="31" t="str">
-        <x:v>HTTP + Playwright-Audit</x:v>
-      </x:c>
-      <x:c r="AZ96" s="31" t="str">
-        <x:v>Verlagsseite nennt keine eindeutige vorhandene Datenausgabe</x:v>
+      <x:c r="AT96" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU96" s="31" t="str">
+        <x:v>HTTP</x:v>
+      </x:c>
+      <x:c r="AV96" s="31" t="str">
+        <x:v>Cambridge-verlinktes OSF-Projekt mit Autor:innenbezug und rekursiv geprüften Datendateien</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="34" customHeight="1">
@@ -9578,17 +9194,13 @@
       <x:c r="AQ97" s="31" t="str"/>
       <x:c r="AR97" s="31" t="str"/>
       <x:c r="AS97" s="31" t="str"/>
-      <x:c r="AT97" s="37" t="str"/>
-      <x:c r="AU97" s="31" t="str"/>
-      <x:c r="AV97" s="31" t="str"/>
-      <x:c r="AW97" s="31" t="str"/>
-      <x:c r="AX97" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY97" s="31" t="str">
+      <x:c r="AT97" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU97" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ97" s="31" t="str">
+      <x:c r="AV97" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -9664,17 +9276,13 @@
       <x:c r="AQ98" s="31" t="str"/>
       <x:c r="AR98" s="31" t="str"/>
       <x:c r="AS98" s="31" t="str"/>
-      <x:c r="AT98" s="37" t="str"/>
-      <x:c r="AU98" s="31" t="str"/>
-      <x:c r="AV98" s="31" t="str"/>
-      <x:c r="AW98" s="31" t="str"/>
-      <x:c r="AX98" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY98" s="31" t="str">
+      <x:c r="AT98" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU98" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ98" s="31" t="str">
+      <x:c r="AV98" s="31" t="str">
         <x:v>Dataset-Treffer ohne hinreichend engen Publikationsbezug (0.00)</x:v>
       </x:c>
     </x:row>
@@ -9754,17 +9362,13 @@
       <x:c r="AQ99" s="31" t="str"/>
       <x:c r="AR99" s="31" t="str"/>
       <x:c r="AS99" s="31" t="str"/>
-      <x:c r="AT99" s="37" t="str"/>
-      <x:c r="AU99" s="31" t="str"/>
-      <x:c r="AV99" s="31" t="str"/>
-      <x:c r="AW99" s="31" t="str"/>
-      <x:c r="AX99" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY99" s="31" t="str">
+      <x:c r="AT99" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU99" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ99" s="31" t="str">
+      <x:c r="AV99" s="31" t="str">
         <x:v>Titel-/Autor:innen-Match (1.00)</x:v>
       </x:c>
     </x:row>
@@ -9838,17 +9442,13 @@
       <x:c r="AQ100" s="31" t="str"/>
       <x:c r="AR100" s="31" t="str"/>
       <x:c r="AS100" s="31" t="str"/>
-      <x:c r="AT100" s="37" t="str"/>
-      <x:c r="AU100" s="31" t="str"/>
-      <x:c r="AV100" s="31" t="str"/>
-      <x:c r="AW100" s="31" t="str"/>
-      <x:c r="AX100" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY100" s="31" t="str">
+      <x:c r="AT100" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU100" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ100" s="31" t="str">
+      <x:c r="AV100" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -9924,17 +9524,13 @@
       <x:c r="AQ101" s="31" t="str"/>
       <x:c r="AR101" s="31" t="str"/>
       <x:c r="AS101" s="31" t="str"/>
-      <x:c r="AT101" s="37" t="str"/>
-      <x:c r="AU101" s="31" t="str"/>
-      <x:c r="AV101" s="31" t="str"/>
-      <x:c r="AW101" s="31" t="str"/>
-      <x:c r="AX101" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY101" s="31" t="str">
+      <x:c r="AT101" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU101" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ101" s="31" t="str">
+      <x:c r="AV101" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -10010,17 +9606,13 @@
       <x:c r="AQ102" s="31" t="str"/>
       <x:c r="AR102" s="31" t="str"/>
       <x:c r="AS102" s="31" t="str"/>
-      <x:c r="AT102" s="37" t="str"/>
-      <x:c r="AU102" s="31" t="str"/>
-      <x:c r="AV102" s="31" t="str"/>
-      <x:c r="AW102" s="31" t="str"/>
-      <x:c r="AX102" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY102" s="31" t="str">
+      <x:c r="AT102" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU102" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ102" s="31" t="str">
+      <x:c r="AV102" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -10104,18 +9696,14 @@
       <x:c r="AQ103" s="31" t="str"/>
       <x:c r="AR103" s="31" t="str"/>
       <x:c r="AS103" s="31" t="str"/>
-      <x:c r="AT103" s="37" t="str"/>
-      <x:c r="AU103" s="31" t="str"/>
-      <x:c r="AV103" s="31" t="str"/>
-      <x:c r="AW103" s="31" t="str"/>
-      <x:c r="AX103" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY103" s="31" t="str">
+      <x:c r="AT103" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU103" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ103" s="31" t="str">
-        <x:v>Link aus Data-Availability-Abschnitt des öffentlichen PuRe-Volltexts; 1 Datendatei(en) über OSF-API bestätigt</x:v>
+      <x:c r="AV103" s="31" t="str">
+        <x:v>Link aus Data-Availability-Abschnitt des öffentlichen PuRe-Volltexts</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="34" customHeight="1">
@@ -10188,17 +9776,13 @@
       <x:c r="AQ104" s="31" t="str"/>
       <x:c r="AR104" s="31" t="str"/>
       <x:c r="AS104" s="31" t="str"/>
-      <x:c r="AT104" s="37" t="str"/>
-      <x:c r="AU104" s="31" t="str"/>
-      <x:c r="AV104" s="31" t="str"/>
-      <x:c r="AW104" s="31" t="str"/>
-      <x:c r="AX104" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY104" s="31" t="str">
+      <x:c r="AT104" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU104" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ104" s="31" t="str">
+      <x:c r="AV104" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -10274,17 +9858,13 @@
       <x:c r="AQ105" s="31" t="str"/>
       <x:c r="AR105" s="31" t="str"/>
       <x:c r="AS105" s="31" t="str"/>
-      <x:c r="AT105" s="37" t="str"/>
-      <x:c r="AU105" s="31" t="str"/>
-      <x:c r="AV105" s="31" t="str"/>
-      <x:c r="AW105" s="31" t="str"/>
-      <x:c r="AX105" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY105" s="31" t="str">
+      <x:c r="AT105" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU105" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ105" s="31" t="str">
+      <x:c r="AV105" s="31" t="str">
         <x:v>Dataset-Treffer ohne hinreichend engen Publikationsbezug (0.14); Dataset-Treffer ohne hinreichend engen Publikationsbezug (0.50); Dataset-Treffer ohne hinreichend engen Publikationsbezug (0.00)</x:v>
       </x:c>
     </x:row>
@@ -10358,17 +9938,13 @@
       <x:c r="AQ106" s="31" t="str"/>
       <x:c r="AR106" s="31" t="str"/>
       <x:c r="AS106" s="31" t="str"/>
-      <x:c r="AT106" s="37" t="str"/>
-      <x:c r="AU106" s="31" t="str"/>
-      <x:c r="AV106" s="31" t="str"/>
-      <x:c r="AW106" s="31" t="str"/>
-      <x:c r="AX106" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY106" s="31" t="str">
+      <x:c r="AT106" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU106" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ106" s="31" t="str">
+      <x:c r="AV106" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -10443,17 +10019,13 @@
       <x:c r="AQ107" s="31" t="str"/>
       <x:c r="AR107" s="31" t="str"/>
       <x:c r="AS107" s="31" t="str"/>
-      <x:c r="AT107" s="37" t="str"/>
-      <x:c r="AU107" s="31" t="str"/>
-      <x:c r="AV107" s="31" t="str"/>
-      <x:c r="AW107" s="31" t="str"/>
-      <x:c r="AX107" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY107" s="31" t="str">
+      <x:c r="AT107" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU107" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ107" s="31" t="str">
+      <x:c r="AV107" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -10529,17 +10101,13 @@
       <x:c r="AQ108" s="31" t="str"/>
       <x:c r="AR108" s="31" t="str"/>
       <x:c r="AS108" s="31" t="str"/>
-      <x:c r="AT108" s="37" t="str"/>
-      <x:c r="AU108" s="31" t="str"/>
-      <x:c r="AV108" s="31" t="str"/>
-      <x:c r="AW108" s="31" t="str"/>
-      <x:c r="AX108" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY108" s="31" t="str">
+      <x:c r="AT108" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU108" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ108" s="31" t="str">
+      <x:c r="AV108" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -10615,17 +10183,13 @@
       <x:c r="AQ109" s="31" t="str"/>
       <x:c r="AR109" s="31" t="str"/>
       <x:c r="AS109" s="31" t="str"/>
-      <x:c r="AT109" s="37" t="str"/>
-      <x:c r="AU109" s="31" t="str"/>
-      <x:c r="AV109" s="31" t="str"/>
-      <x:c r="AW109" s="31" t="str"/>
-      <x:c r="AX109" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY109" s="31" t="str">
+      <x:c r="AT109" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU109" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ109" s="31" t="str">
+      <x:c r="AV109" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -10699,17 +10263,13 @@
       <x:c r="AQ110" s="31" t="str"/>
       <x:c r="AR110" s="31" t="str"/>
       <x:c r="AS110" s="31" t="str"/>
-      <x:c r="AT110" s="37" t="str"/>
-      <x:c r="AU110" s="31" t="str"/>
-      <x:c r="AV110" s="31" t="str"/>
-      <x:c r="AW110" s="31" t="str"/>
-      <x:c r="AX110" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY110" s="31" t="str">
+      <x:c r="AT110" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU110" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ110" s="31" t="str">
+      <x:c r="AV110" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -10783,17 +10343,13 @@
       <x:c r="AQ111" s="31" t="str"/>
       <x:c r="AR111" s="31" t="str"/>
       <x:c r="AS111" s="31" t="str"/>
-      <x:c r="AT111" s="37" t="str"/>
-      <x:c r="AU111" s="31" t="str"/>
-      <x:c r="AV111" s="31" t="str"/>
-      <x:c r="AW111" s="31" t="str"/>
-      <x:c r="AX111" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY111" s="31" t="str">
+      <x:c r="AT111" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU111" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ111" s="31" t="str">
+      <x:c r="AV111" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -10867,17 +10423,13 @@
       <x:c r="AQ112" s="31" t="str"/>
       <x:c r="AR112" s="31" t="str"/>
       <x:c r="AS112" s="31" t="str"/>
-      <x:c r="AT112" s="37" t="str"/>
-      <x:c r="AU112" s="31" t="str"/>
-      <x:c r="AV112" s="31" t="str"/>
-      <x:c r="AW112" s="31" t="str"/>
-      <x:c r="AX112" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY112" s="31" t="str">
+      <x:c r="AT112" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU112" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ112" s="31" t="str">
+      <x:c r="AV112" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -10953,17 +10505,13 @@
       <x:c r="AQ113" s="31" t="str"/>
       <x:c r="AR113" s="31" t="str"/>
       <x:c r="AS113" s="31" t="str"/>
-      <x:c r="AT113" s="37" t="str"/>
-      <x:c r="AU113" s="31" t="str"/>
-      <x:c r="AV113" s="31" t="str"/>
-      <x:c r="AW113" s="31" t="str"/>
-      <x:c r="AX113" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY113" s="31" t="str">
+      <x:c r="AT113" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU113" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ113" s="31" t="str">
+      <x:c r="AV113" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -11039,17 +10587,13 @@
       <x:c r="AQ114" s="31" t="str"/>
       <x:c r="AR114" s="31" t="str"/>
       <x:c r="AS114" s="31" t="str"/>
-      <x:c r="AT114" s="37" t="str"/>
-      <x:c r="AU114" s="31" t="str"/>
-      <x:c r="AV114" s="31" t="str"/>
-      <x:c r="AW114" s="31" t="str"/>
-      <x:c r="AX114" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY114" s="31" t="str">
+      <x:c r="AT114" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU114" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ114" s="31" t="str">
+      <x:c r="AV114" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -11123,17 +10667,13 @@
       <x:c r="AQ115" s="31" t="str"/>
       <x:c r="AR115" s="31" t="str"/>
       <x:c r="AS115" s="31" t="str"/>
-      <x:c r="AT115" s="37" t="str"/>
-      <x:c r="AU115" s="31" t="str"/>
-      <x:c r="AV115" s="31" t="str"/>
-      <x:c r="AW115" s="31" t="str"/>
-      <x:c r="AX115" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY115" s="31" t="str">
+      <x:c r="AT115" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU115" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ115" s="31" t="str">
+      <x:c r="AV115" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -11207,17 +10747,13 @@
       <x:c r="AQ116" s="31" t="str"/>
       <x:c r="AR116" s="31" t="str"/>
       <x:c r="AS116" s="31" t="str"/>
-      <x:c r="AT116" s="37" t="str"/>
-      <x:c r="AU116" s="31" t="str"/>
-      <x:c r="AV116" s="31" t="str"/>
-      <x:c r="AW116" s="31" t="str"/>
-      <x:c r="AX116" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY116" s="31" t="str">
+      <x:c r="AT116" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU116" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ116" s="31" t="str">
+      <x:c r="AV116" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -11291,17 +10827,13 @@
       <x:c r="AQ117" s="31" t="str"/>
       <x:c r="AR117" s="31" t="str"/>
       <x:c r="AS117" s="31" t="str"/>
-      <x:c r="AT117" s="37" t="str"/>
-      <x:c r="AU117" s="31" t="str"/>
-      <x:c r="AV117" s="31" t="str"/>
-      <x:c r="AW117" s="31" t="str"/>
-      <x:c r="AX117" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY117" s="31" t="str">
+      <x:c r="AT117" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU117" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ117" s="31" t="str">
+      <x:c r="AV117" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -11375,17 +10907,13 @@
       <x:c r="AQ118" s="31" t="str"/>
       <x:c r="AR118" s="31" t="str"/>
       <x:c r="AS118" s="31" t="str"/>
-      <x:c r="AT118" s="37" t="str"/>
-      <x:c r="AU118" s="31" t="str"/>
-      <x:c r="AV118" s="31" t="str"/>
-      <x:c r="AW118" s="31" t="str"/>
-      <x:c r="AX118" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY118" s="31" t="str">
+      <x:c r="AT118" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU118" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ118" s="31" t="str">
+      <x:c r="AV118" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -11459,17 +10987,13 @@
       <x:c r="AQ119" s="31" t="str"/>
       <x:c r="AR119" s="31" t="str"/>
       <x:c r="AS119" s="31" t="str"/>
-      <x:c r="AT119" s="37" t="str"/>
-      <x:c r="AU119" s="31" t="str"/>
-      <x:c r="AV119" s="31" t="str"/>
-      <x:c r="AW119" s="31" t="str"/>
-      <x:c r="AX119" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY119" s="31" t="str">
+      <x:c r="AT119" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU119" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ119" s="31" t="str">
+      <x:c r="AV119" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -11543,17 +11067,13 @@
       <x:c r="AQ120" s="31" t="str"/>
       <x:c r="AR120" s="31" t="str"/>
       <x:c r="AS120" s="31" t="str"/>
-      <x:c r="AT120" s="37" t="str"/>
-      <x:c r="AU120" s="31" t="str"/>
-      <x:c r="AV120" s="31" t="str"/>
-      <x:c r="AW120" s="31" t="str"/>
-      <x:c r="AX120" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY120" s="31" t="str">
+      <x:c r="AT120" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU120" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ120" s="31" t="str">
+      <x:c r="AV120" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -11629,17 +11149,13 @@
       <x:c r="AQ121" s="31" t="str"/>
       <x:c r="AR121" s="31" t="str"/>
       <x:c r="AS121" s="31" t="str"/>
-      <x:c r="AT121" s="37" t="str"/>
-      <x:c r="AU121" s="31" t="str"/>
-      <x:c r="AV121" s="31" t="str"/>
-      <x:c r="AW121" s="31" t="str"/>
-      <x:c r="AX121" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY121" s="31" t="str">
+      <x:c r="AT121" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU121" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ121" s="31" t="str">
+      <x:c r="AV121" s="31" t="str">
         <x:v>Verlagsseite nennt keine eindeutige vorhandene Datenausgabe</x:v>
       </x:c>
     </x:row>
@@ -11763,18 +11279,14 @@
       <x:c r="AQ122" s="31" t="str"/>
       <x:c r="AR122" s="31" t="str"/>
       <x:c r="AS122" s="31" t="str"/>
-      <x:c r="AT122" s="37" t="str"/>
-      <x:c r="AU122" s="31" t="str"/>
-      <x:c r="AV122" s="31" t="str"/>
-      <x:c r="AW122" s="31" t="str"/>
-      <x:c r="AX122" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY122" s="31" t="str">
+      <x:c r="AT122" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU122" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ122" s="31" t="str">
-        <x:v>Link aus expliziter Data-Availability-Statement; 6 Datendatei(en) über OSF-API bestätigt; Link aus expliziter Data-Availability-Statement</x:v>
+      <x:c r="AV122" s="31" t="str">
+        <x:v>Link aus expliziter Data-Availability-Statement</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="34" customHeight="1">
@@ -11847,17 +11359,13 @@
       <x:c r="AQ123" s="31" t="str"/>
       <x:c r="AR123" s="31" t="str"/>
       <x:c r="AS123" s="31" t="str"/>
-      <x:c r="AT123" s="37" t="str"/>
-      <x:c r="AU123" s="31" t="str"/>
-      <x:c r="AV123" s="31" t="str"/>
-      <x:c r="AW123" s="31" t="str"/>
-      <x:c r="AX123" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY123" s="31" t="str">
+      <x:c r="AT123" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU123" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ123" s="31" t="str">
+      <x:c r="AV123" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -11931,17 +11439,13 @@
       <x:c r="AQ124" s="31" t="str"/>
       <x:c r="AR124" s="31" t="str"/>
       <x:c r="AS124" s="31" t="str"/>
-      <x:c r="AT124" s="37" t="str"/>
-      <x:c r="AU124" s="31" t="str"/>
-      <x:c r="AV124" s="31" t="str"/>
-      <x:c r="AW124" s="31" t="str"/>
-      <x:c r="AX124" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY124" s="31" t="str">
+      <x:c r="AT124" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU124" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ124" s="31" t="str">
+      <x:c r="AV124" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -11976,27 +11480,51 @@
       <x:c r="J125" s="31" t="str">
         <x:v>no</x:v>
       </x:c>
-      <x:c r="K125" s="33" t="str">
-        <x:v>nein</x:v>
+      <x:c r="K125" s="32" t="str">
+        <x:v>ja</x:v>
       </x:c>
       <x:c r="L125" s="41" t="n">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="M125" s="31" t="str">
-        <x:v>kein verifizierter Datenlink</x:v>
-      </x:c>
-      <x:c r="N125" s="37" t="str"/>
-      <x:c r="O125" s="31" t="str"/>
-      <x:c r="P125" s="31" t="str"/>
-      <x:c r="Q125" s="31" t="str"/>
-      <x:c r="R125" s="37" t="str"/>
-      <x:c r="S125" s="31" t="str"/>
-      <x:c r="T125" s="31" t="str"/>
-      <x:c r="U125" s="31" t="str"/>
-      <x:c r="V125" s="37" t="str"/>
-      <x:c r="W125" s="31" t="str"/>
-      <x:c r="X125" s="31" t="str"/>
-      <x:c r="Y125" s="31" t="str"/>
+        <x:v>offen</x:v>
+      </x:c>
+      <x:c r="N125" s="37" t="str">
+        <x:v>https://huggingface.co/datasets/joelniklaus/SwissLawTranslations</x:v>
+      </x:c>
+      <x:c r="O125" s="31" t="str">
+        <x:v>Provider</x:v>
+      </x:c>
+      <x:c r="P125" s="31" t="str">
+        <x:v>offen</x:v>
+      </x:c>
+      <x:c r="Q125" s="31" t="str">
+        <x:v>HTTP 200; HTTP</x:v>
+      </x:c>
+      <x:c r="R125" s="37" t="str">
+        <x:v>https://huggingface.co/datasets/joelniklaus/SwissDecisionSummaryTranslations</x:v>
+      </x:c>
+      <x:c r="S125" s="31" t="str">
+        <x:v>Provider</x:v>
+      </x:c>
+      <x:c r="T125" s="31" t="str">
+        <x:v>offen</x:v>
+      </x:c>
+      <x:c r="U125" s="31" t="str">
+        <x:v>HTTP 200; HTTP</x:v>
+      </x:c>
+      <x:c r="V125" s="37" t="str">
+        <x:v>https://huggingface.co/datasets/joelniklaus/SwissSupremeCourtPressReleaseTranslations</x:v>
+      </x:c>
+      <x:c r="W125" s="31" t="str">
+        <x:v>Provider</x:v>
+      </x:c>
+      <x:c r="X125" s="31" t="str">
+        <x:v>offen</x:v>
+      </x:c>
+      <x:c r="Y125" s="31" t="str">
+        <x:v>HTTP 200; HTTP</x:v>
+      </x:c>
       <x:c r="Z125" s="37" t="str"/>
       <x:c r="AA125" s="31" t="str"/>
       <x:c r="AB125" s="31" t="str"/>
@@ -12017,18 +11545,14 @@
       <x:c r="AQ125" s="31" t="str"/>
       <x:c r="AR125" s="31" t="str"/>
       <x:c r="AS125" s="31" t="str"/>
-      <x:c r="AT125" s="37" t="str"/>
-      <x:c r="AU125" s="31" t="str"/>
-      <x:c r="AV125" s="31" t="str"/>
-      <x:c r="AW125" s="31" t="str"/>
-      <x:c r="AX125" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY125" s="31" t="str">
-        <x:v>HTTP + Playwright-Audit</x:v>
-      </x:c>
-      <x:c r="AZ125" s="31" t="str">
-        <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
+      <x:c r="AT125" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU125" s="31" t="str">
+        <x:v>HTTP</x:v>
+      </x:c>
+      <x:c r="AV125" s="31" t="str">
+        <x:v>Öffentlicher Hugging-Face-Datensatz mit exaktem arXiv-Tag und geprüften Datendateien</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="34" customHeight="1">
@@ -12101,17 +11625,13 @@
       <x:c r="AQ126" s="31" t="str"/>
       <x:c r="AR126" s="31" t="str"/>
       <x:c r="AS126" s="31" t="str"/>
-      <x:c r="AT126" s="37" t="str"/>
-      <x:c r="AU126" s="31" t="str"/>
-      <x:c r="AV126" s="31" t="str"/>
-      <x:c r="AW126" s="31" t="str"/>
-      <x:c r="AX126" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY126" s="31" t="str">
+      <x:c r="AT126" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU126" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ126" s="31" t="str">
+      <x:c r="AV126" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -12195,17 +11715,13 @@
       <x:c r="AQ127" s="31" t="str"/>
       <x:c r="AR127" s="31" t="str"/>
       <x:c r="AS127" s="31" t="str"/>
-      <x:c r="AT127" s="37" t="str"/>
-      <x:c r="AU127" s="31" t="str"/>
-      <x:c r="AV127" s="31" t="str"/>
-      <x:c r="AW127" s="31" t="str"/>
-      <x:c r="AX127" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY127" s="31" t="str">
+      <x:c r="AT127" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU127" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ127" s="31" t="str">
+      <x:c r="AV127" s="31" t="str">
         <x:v>Strukturierte eLife-Data-Availability-Aussage mit öffentlichem Datensatzlink; 32 Datendatei(en) über GitHub-API bestätigt</x:v>
       </x:c>
     </x:row>
@@ -12279,17 +11795,13 @@
       <x:c r="AQ128" s="31" t="str"/>
       <x:c r="AR128" s="31" t="str"/>
       <x:c r="AS128" s="31" t="str"/>
-      <x:c r="AT128" s="37" t="str"/>
-      <x:c r="AU128" s="31" t="str"/>
-      <x:c r="AV128" s="31" t="str"/>
-      <x:c r="AW128" s="31" t="str"/>
-      <x:c r="AX128" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY128" s="31" t="str">
+      <x:c r="AT128" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU128" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ128" s="31" t="str">
+      <x:c r="AV128" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -12363,17 +11875,13 @@
       <x:c r="AQ129" s="31" t="str"/>
       <x:c r="AR129" s="31" t="str"/>
       <x:c r="AS129" s="31" t="str"/>
-      <x:c r="AT129" s="37" t="str"/>
-      <x:c r="AU129" s="31" t="str"/>
-      <x:c r="AV129" s="31" t="str"/>
-      <x:c r="AW129" s="31" t="str"/>
-      <x:c r="AX129" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY129" s="31" t="str">
+      <x:c r="AT129" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU129" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ129" s="31" t="str">
+      <x:c r="AV129" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -12449,17 +11957,13 @@
       <x:c r="AQ130" s="31" t="str"/>
       <x:c r="AR130" s="31" t="str"/>
       <x:c r="AS130" s="31" t="str"/>
-      <x:c r="AT130" s="37" t="str"/>
-      <x:c r="AU130" s="31" t="str"/>
-      <x:c r="AV130" s="31" t="str"/>
-      <x:c r="AW130" s="31" t="str"/>
-      <x:c r="AX130" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY130" s="31" t="str">
+      <x:c r="AT130" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU130" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ130" s="31" t="str">
+      <x:c r="AV130" s="31" t="str">
         <x:v>Dataset-Treffer ohne hinreichend engen Publikationsbezug (0.00)</x:v>
       </x:c>
     </x:row>
@@ -12533,17 +12037,13 @@
       <x:c r="AQ131" s="31" t="str"/>
       <x:c r="AR131" s="31" t="str"/>
       <x:c r="AS131" s="31" t="str"/>
-      <x:c r="AT131" s="37" t="str"/>
-      <x:c r="AU131" s="31" t="str"/>
-      <x:c r="AV131" s="31" t="str"/>
-      <x:c r="AW131" s="31" t="str"/>
-      <x:c r="AX131" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY131" s="31" t="str">
+      <x:c r="AT131" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU131" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ131" s="31" t="str">
+      <x:c r="AV131" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -12619,17 +12119,13 @@
       <x:c r="AQ132" s="31" t="str"/>
       <x:c r="AR132" s="31" t="str"/>
       <x:c r="AS132" s="31" t="str"/>
-      <x:c r="AT132" s="37" t="str"/>
-      <x:c r="AU132" s="31" t="str"/>
-      <x:c r="AV132" s="31" t="str"/>
-      <x:c r="AW132" s="31" t="str"/>
-      <x:c r="AX132" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY132" s="31" t="str">
+      <x:c r="AT132" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU132" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ132" s="31" t="str">
+      <x:c r="AV132" s="31" t="str">
         <x:v>Verlagsseite nennt keine eindeutige vorhandene Datenausgabe</x:v>
       </x:c>
     </x:row>
@@ -12705,17 +12201,13 @@
       <x:c r="AQ133" s="31" t="str"/>
       <x:c r="AR133" s="31" t="str"/>
       <x:c r="AS133" s="31" t="str"/>
-      <x:c r="AT133" s="37" t="str"/>
-      <x:c r="AU133" s="31" t="str"/>
-      <x:c r="AV133" s="31" t="str"/>
-      <x:c r="AW133" s="31" t="str"/>
-      <x:c r="AX133" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY133" s="31" t="str">
+      <x:c r="AT133" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU133" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ133" s="31" t="str">
+      <x:c r="AV133" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -12789,17 +12281,13 @@
       <x:c r="AQ134" s="31" t="str"/>
       <x:c r="AR134" s="31" t="str"/>
       <x:c r="AS134" s="31" t="str"/>
-      <x:c r="AT134" s="37" t="str"/>
-      <x:c r="AU134" s="31" t="str"/>
-      <x:c r="AV134" s="31" t="str"/>
-      <x:c r="AW134" s="31" t="str"/>
-      <x:c r="AX134" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY134" s="31" t="str">
+      <x:c r="AT134" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU134" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ134" s="31" t="str">
+      <x:c r="AV134" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -12875,17 +12363,13 @@
       <x:c r="AQ135" s="31" t="str"/>
       <x:c r="AR135" s="31" t="str"/>
       <x:c r="AS135" s="31" t="str"/>
-      <x:c r="AT135" s="37" t="str"/>
-      <x:c r="AU135" s="31" t="str"/>
-      <x:c r="AV135" s="31" t="str"/>
-      <x:c r="AW135" s="31" t="str"/>
-      <x:c r="AX135" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY135" s="31" t="str">
+      <x:c r="AT135" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU135" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ135" s="31" t="str">
+      <x:c r="AV135" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -12969,17 +12453,13 @@
       <x:c r="AQ136" s="31" t="str"/>
       <x:c r="AR136" s="31" t="str"/>
       <x:c r="AS136" s="31" t="str"/>
-      <x:c r="AT136" s="37" t="str"/>
-      <x:c r="AU136" s="31" t="str"/>
-      <x:c r="AV136" s="31" t="str"/>
-      <x:c r="AW136" s="31" t="str"/>
-      <x:c r="AX136" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY136" s="31" t="str">
+      <x:c r="AT136" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU136" s="31" t="str">
         <x:v>Playwright</x:v>
       </x:c>
-      <x:c r="AZ136" s="31" t="str">
+      <x:c r="AV136" s="31" t="str">
         <x:v>Offizielles INFORMS-Replikationsarchiv mit geprüften Datendateien</x:v>
       </x:c>
     </x:row>
@@ -13053,17 +12533,13 @@
       <x:c r="AQ137" s="31" t="str"/>
       <x:c r="AR137" s="31" t="str"/>
       <x:c r="AS137" s="31" t="str"/>
-      <x:c r="AT137" s="37" t="str"/>
-      <x:c r="AU137" s="31" t="str"/>
-      <x:c r="AV137" s="31" t="str"/>
-      <x:c r="AW137" s="31" t="str"/>
-      <x:c r="AX137" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY137" s="31" t="str">
+      <x:c r="AT137" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU137" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ137" s="31" t="str">
+      <x:c r="AV137" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -13137,17 +12613,13 @@
       <x:c r="AQ138" s="31" t="str"/>
       <x:c r="AR138" s="31" t="str"/>
       <x:c r="AS138" s="31" t="str"/>
-      <x:c r="AT138" s="37" t="str"/>
-      <x:c r="AU138" s="31" t="str"/>
-      <x:c r="AV138" s="31" t="str"/>
-      <x:c r="AW138" s="31" t="str"/>
-      <x:c r="AX138" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY138" s="31" t="str">
+      <x:c r="AT138" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU138" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ138" s="31" t="str">
+      <x:c r="AV138" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -13223,17 +12695,13 @@
       <x:c r="AQ139" s="31" t="str"/>
       <x:c r="AR139" s="31" t="str"/>
       <x:c r="AS139" s="31" t="str"/>
-      <x:c r="AT139" s="37" t="str"/>
-      <x:c r="AU139" s="31" t="str"/>
-      <x:c r="AV139" s="31" t="str"/>
-      <x:c r="AW139" s="31" t="str"/>
-      <x:c r="AX139" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY139" s="31" t="str">
+      <x:c r="AT139" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU139" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ139" s="31" t="str">
+      <x:c r="AV139" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -13309,17 +12777,13 @@
       <x:c r="AQ140" s="31" t="str"/>
       <x:c r="AR140" s="31" t="str"/>
       <x:c r="AS140" s="31" t="str"/>
-      <x:c r="AT140" s="37" t="str"/>
-      <x:c r="AU140" s="31" t="str"/>
-      <x:c r="AV140" s="31" t="str"/>
-      <x:c r="AW140" s="31" t="str"/>
-      <x:c r="AX140" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY140" s="31" t="str">
+      <x:c r="AT140" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU140" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ140" s="31" t="str">
+      <x:c r="AV140" s="31" t="str">
         <x:v>Dataset-Treffer ohne hinreichend engen Publikationsbezug (0.00)</x:v>
       </x:c>
     </x:row>
@@ -13393,17 +12857,13 @@
       <x:c r="AQ141" s="31" t="str"/>
       <x:c r="AR141" s="31" t="str"/>
       <x:c r="AS141" s="31" t="str"/>
-      <x:c r="AT141" s="37" t="str"/>
-      <x:c r="AU141" s="31" t="str"/>
-      <x:c r="AV141" s="31" t="str"/>
-      <x:c r="AW141" s="31" t="str"/>
-      <x:c r="AX141" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY141" s="31" t="str">
+      <x:c r="AT141" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU141" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ141" s="31" t="str">
+      <x:c r="AV141" s="31" t="str">
         <x:v>Dataset-Treffer ohne hinreichend engen Publikationsbezug (0.00)</x:v>
       </x:c>
     </x:row>
@@ -13442,7 +12902,7 @@
         <x:v>ja</x:v>
       </x:c>
       <x:c r="L142" s="41" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="M142" s="31" t="str">
         <x:v>offen</x:v>
@@ -13459,14 +12919,30 @@
       <x:c r="Q142" s="31" t="str">
         <x:v>HTTP 200; HTTP</x:v>
       </x:c>
-      <x:c r="R142" s="37" t="str"/>
-      <x:c r="S142" s="31" t="str"/>
-      <x:c r="T142" s="31" t="str"/>
-      <x:c r="U142" s="31" t="str"/>
-      <x:c r="V142" s="37" t="str"/>
-      <x:c r="W142" s="31" t="str"/>
-      <x:c r="X142" s="31" t="str"/>
-      <x:c r="Y142" s="31" t="str"/>
+      <x:c r="R142" s="37" t="str">
+        <x:v>https://huggingface.co/datasets/ricdomolm/lawma-tasks</x:v>
+      </x:c>
+      <x:c r="S142" s="31" t="str">
+        <x:v>Provider</x:v>
+      </x:c>
+      <x:c r="T142" s="31" t="str">
+        <x:v>offen</x:v>
+      </x:c>
+      <x:c r="U142" s="31" t="str">
+        <x:v>HTTP 200; Playwright</x:v>
+      </x:c>
+      <x:c r="V142" s="37" t="str">
+        <x:v>https://huggingface.co/datasets/ricdomolm/lawma-all-tasks</x:v>
+      </x:c>
+      <x:c r="W142" s="31" t="str">
+        <x:v>Provider</x:v>
+      </x:c>
+      <x:c r="X142" s="31" t="str">
+        <x:v>offen</x:v>
+      </x:c>
+      <x:c r="Y142" s="31" t="str">
+        <x:v>HTTP 200; HTTP</x:v>
+      </x:c>
       <x:c r="Z142" s="37" t="str"/>
       <x:c r="AA142" s="31" t="str"/>
       <x:c r="AB142" s="31" t="str"/>
@@ -13487,18 +12963,14 @@
       <x:c r="AQ142" s="31" t="str"/>
       <x:c r="AR142" s="31" t="str"/>
       <x:c r="AS142" s="31" t="str"/>
-      <x:c r="AT142" s="37" t="str"/>
-      <x:c r="AU142" s="31" t="str"/>
-      <x:c r="AV142" s="31" t="str"/>
-      <x:c r="AW142" s="31" t="str"/>
-      <x:c r="AX142" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY142" s="31" t="str">
-        <x:v>HTTP</x:v>
-      </x:c>
-      <x:c r="AZ142" s="31" t="str">
-        <x:v>GitHub-README mit exaktem Publikationstitel und geprüften Datendateien; 7424 Datendatei(en) über GitHub-API bestätigt</x:v>
+      <x:c r="AT142" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU142" s="31" t="str">
+        <x:v>HTTP; Playwright</x:v>
+      </x:c>
+      <x:c r="AV142" s="31" t="str">
+        <x:v>GitHub-README mit exaktem Publikationstitel und geprüften Datendateien; 7424 Datendatei(en) über GitHub-API bestätigt; Öffentlicher Hugging-Face-Datensatz mit exaktem arXiv-Tag und geprüften Datendateien</x:v>
       </x:c>
     </x:row>
     <x:row r="143" ht="34" customHeight="1">
@@ -13571,17 +13043,13 @@
       <x:c r="AQ143" s="31" t="str"/>
       <x:c r="AR143" s="31" t="str"/>
       <x:c r="AS143" s="31" t="str"/>
-      <x:c r="AT143" s="37" t="str"/>
-      <x:c r="AU143" s="31" t="str"/>
-      <x:c r="AV143" s="31" t="str"/>
-      <x:c r="AW143" s="31" t="str"/>
-      <x:c r="AX143" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY143" s="31" t="str">
+      <x:c r="AT143" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU143" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ143" s="31" t="str">
+      <x:c r="AV143" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -13655,17 +13123,13 @@
       <x:c r="AQ144" s="31" t="str"/>
       <x:c r="AR144" s="31" t="str"/>
       <x:c r="AS144" s="31" t="str"/>
-      <x:c r="AT144" s="37" t="str"/>
-      <x:c r="AU144" s="31" t="str"/>
-      <x:c r="AV144" s="31" t="str"/>
-      <x:c r="AW144" s="31" t="str"/>
-      <x:c r="AX144" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY144" s="31" t="str">
+      <x:c r="AT144" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU144" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ144" s="31" t="str">
+      <x:c r="AV144" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -13741,17 +13205,13 @@
       <x:c r="AQ145" s="31" t="str"/>
       <x:c r="AR145" s="31" t="str"/>
       <x:c r="AS145" s="31" t="str"/>
-      <x:c r="AT145" s="37" t="str"/>
-      <x:c r="AU145" s="31" t="str"/>
-      <x:c r="AV145" s="31" t="str"/>
-      <x:c r="AW145" s="31" t="str"/>
-      <x:c r="AX145" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY145" s="31" t="str">
+      <x:c r="AT145" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU145" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ145" s="31" t="str">
+      <x:c r="AV145" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -13825,17 +13285,13 @@
       <x:c r="AQ146" s="31" t="str"/>
       <x:c r="AR146" s="31" t="str"/>
       <x:c r="AS146" s="31" t="str"/>
-      <x:c r="AT146" s="37" t="str"/>
-      <x:c r="AU146" s="31" t="str"/>
-      <x:c r="AV146" s="31" t="str"/>
-      <x:c r="AW146" s="31" t="str"/>
-      <x:c r="AX146" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY146" s="31" t="str">
+      <x:c r="AT146" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU146" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ146" s="31" t="str">
+      <x:c r="AV146" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -13909,17 +13365,13 @@
       <x:c r="AQ147" s="31" t="str"/>
       <x:c r="AR147" s="31" t="str"/>
       <x:c r="AS147" s="31" t="str"/>
-      <x:c r="AT147" s="37" t="str"/>
-      <x:c r="AU147" s="31" t="str"/>
-      <x:c r="AV147" s="31" t="str"/>
-      <x:c r="AW147" s="31" t="str"/>
-      <x:c r="AX147" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY147" s="31" t="str">
+      <x:c r="AT147" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU147" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ147" s="31" t="str">
+      <x:c r="AV147" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -13993,17 +13445,13 @@
       <x:c r="AQ148" s="31" t="str"/>
       <x:c r="AR148" s="31" t="str"/>
       <x:c r="AS148" s="31" t="str"/>
-      <x:c r="AT148" s="37" t="str"/>
-      <x:c r="AU148" s="31" t="str"/>
-      <x:c r="AV148" s="31" t="str"/>
-      <x:c r="AW148" s="31" t="str"/>
-      <x:c r="AX148" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY148" s="31" t="str">
+      <x:c r="AT148" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU148" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ148" s="31" t="str">
+      <x:c r="AV148" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -14087,17 +13535,13 @@
       <x:c r="AQ149" s="31" t="str"/>
       <x:c r="AR149" s="31" t="str"/>
       <x:c r="AS149" s="31" t="str"/>
-      <x:c r="AT149" s="37" t="str"/>
-      <x:c r="AU149" s="31" t="str"/>
-      <x:c r="AV149" s="31" t="str"/>
-      <x:c r="AW149" s="31" t="str"/>
-      <x:c r="AX149" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY149" s="31" t="str">
+      <x:c r="AT149" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU149" s="31" t="str">
         <x:v>Playwright</x:v>
       </x:c>
-      <x:c r="AZ149" s="31" t="str">
+      <x:c r="AV149" s="31" t="str">
         <x:v>Offizielles INFORMS-Replikationsarchiv mit geprüften Datendateien</x:v>
       </x:c>
     </x:row>
@@ -14171,17 +13615,13 @@
       <x:c r="AQ150" s="31" t="str"/>
       <x:c r="AR150" s="31" t="str"/>
       <x:c r="AS150" s="31" t="str"/>
-      <x:c r="AT150" s="37" t="str"/>
-      <x:c r="AU150" s="31" t="str"/>
-      <x:c r="AV150" s="31" t="str"/>
-      <x:c r="AW150" s="31" t="str"/>
-      <x:c r="AX150" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY150" s="31" t="str">
+      <x:c r="AT150" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU150" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ150" s="31" t="str">
+      <x:c r="AV150" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -14257,17 +13697,13 @@
       <x:c r="AQ151" s="31" t="str"/>
       <x:c r="AR151" s="31" t="str"/>
       <x:c r="AS151" s="31" t="str"/>
-      <x:c r="AT151" s="37" t="str"/>
-      <x:c r="AU151" s="31" t="str"/>
-      <x:c r="AV151" s="31" t="str"/>
-      <x:c r="AW151" s="31" t="str"/>
-      <x:c r="AX151" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY151" s="31" t="str">
+      <x:c r="AT151" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU151" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ151" s="31" t="str">
+      <x:c r="AV151" s="31" t="str">
         <x:v>Verlagsseite nennt keine eindeutige vorhandene Datenausgabe</x:v>
       </x:c>
     </x:row>
@@ -14341,17 +13777,13 @@
       <x:c r="AQ152" s="31" t="str"/>
       <x:c r="AR152" s="31" t="str"/>
       <x:c r="AS152" s="31" t="str"/>
-      <x:c r="AT152" s="37" t="str"/>
-      <x:c r="AU152" s="31" t="str"/>
-      <x:c r="AV152" s="31" t="str"/>
-      <x:c r="AW152" s="31" t="str"/>
-      <x:c r="AX152" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY152" s="31" t="str">
+      <x:c r="AT152" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU152" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ152" s="31" t="str">
+      <x:c r="AV152" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -14433,17 +13865,13 @@
       <x:c r="AQ153" s="31" t="str"/>
       <x:c r="AR153" s="31" t="str"/>
       <x:c r="AS153" s="31" t="str"/>
-      <x:c r="AT153" s="37" t="str"/>
-      <x:c r="AU153" s="31" t="str"/>
-      <x:c r="AV153" s="31" t="str"/>
-      <x:c r="AW153" s="31" t="str"/>
-      <x:c r="AX153" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY153" s="31" t="str">
+      <x:c r="AT153" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU153" s="31" t="str">
         <x:v>Playwright</x:v>
       </x:c>
-      <x:c r="AZ153" s="31" t="str">
+      <x:c r="AV153" s="31" t="str">
         <x:v>Titel-/Autor:innen-Match (1.00)</x:v>
       </x:c>
     </x:row>
@@ -14519,17 +13947,13 @@
       <x:c r="AQ154" s="31" t="str"/>
       <x:c r="AR154" s="31" t="str"/>
       <x:c r="AS154" s="31" t="str"/>
-      <x:c r="AT154" s="37" t="str"/>
-      <x:c r="AU154" s="31" t="str"/>
-      <x:c r="AV154" s="31" t="str"/>
-      <x:c r="AW154" s="31" t="str"/>
-      <x:c r="AX154" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY154" s="31" t="str">
+      <x:c r="AT154" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU154" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ154" s="31" t="str">
+      <x:c r="AV154" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -14603,17 +14027,13 @@
       <x:c r="AQ155" s="31" t="str"/>
       <x:c r="AR155" s="31" t="str"/>
       <x:c r="AS155" s="31" t="str"/>
-      <x:c r="AT155" s="37" t="str"/>
-      <x:c r="AU155" s="31" t="str"/>
-      <x:c r="AV155" s="31" t="str"/>
-      <x:c r="AW155" s="31" t="str"/>
-      <x:c r="AX155" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY155" s="31" t="str">
+      <x:c r="AT155" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU155" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ155" s="31" t="str">
+      <x:c r="AV155" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -14687,17 +14107,13 @@
       <x:c r="AQ156" s="31" t="str"/>
       <x:c r="AR156" s="31" t="str"/>
       <x:c r="AS156" s="31" t="str"/>
-      <x:c r="AT156" s="37" t="str"/>
-      <x:c r="AU156" s="31" t="str"/>
-      <x:c r="AV156" s="31" t="str"/>
-      <x:c r="AW156" s="31" t="str"/>
-      <x:c r="AX156" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY156" s="31" t="str">
+      <x:c r="AT156" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU156" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ156" s="31" t="str">
+      <x:c r="AV156" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -14771,17 +14187,13 @@
       <x:c r="AQ157" s="31" t="str"/>
       <x:c r="AR157" s="31" t="str"/>
       <x:c r="AS157" s="31" t="str"/>
-      <x:c r="AT157" s="37" t="str"/>
-      <x:c r="AU157" s="31" t="str"/>
-      <x:c r="AV157" s="31" t="str"/>
-      <x:c r="AW157" s="31" t="str"/>
-      <x:c r="AX157" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY157" s="31" t="str">
+      <x:c r="AT157" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU157" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ157" s="31" t="str">
+      <x:c r="AV157" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -14857,17 +14269,13 @@
       <x:c r="AQ158" s="31" t="str"/>
       <x:c r="AR158" s="31" t="str"/>
       <x:c r="AS158" s="31" t="str"/>
-      <x:c r="AT158" s="37" t="str"/>
-      <x:c r="AU158" s="31" t="str"/>
-      <x:c r="AV158" s="31" t="str"/>
-      <x:c r="AW158" s="31" t="str"/>
-      <x:c r="AX158" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY158" s="31" t="str">
+      <x:c r="AT158" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU158" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ158" s="31" t="str">
+      <x:c r="AV158" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -14943,17 +14351,13 @@
       <x:c r="AQ159" s="31" t="str"/>
       <x:c r="AR159" s="31" t="str"/>
       <x:c r="AS159" s="31" t="str"/>
-      <x:c r="AT159" s="37" t="str"/>
-      <x:c r="AU159" s="31" t="str"/>
-      <x:c r="AV159" s="31" t="str"/>
-      <x:c r="AW159" s="31" t="str"/>
-      <x:c r="AX159" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY159" s="31" t="str">
+      <x:c r="AT159" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU159" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ159" s="31" t="str">
+      <x:c r="AV159" s="31" t="str">
         <x:v>Dataset-Treffer ohne hinreichend engen Publikationsbezug (1.00)</x:v>
       </x:c>
     </x:row>
@@ -15037,17 +14441,13 @@
       <x:c r="AQ160" s="31" t="str"/>
       <x:c r="AR160" s="31" t="str"/>
       <x:c r="AS160" s="31" t="str"/>
-      <x:c r="AT160" s="37" t="str"/>
-      <x:c r="AU160" s="31" t="str"/>
-      <x:c r="AV160" s="31" t="str"/>
-      <x:c r="AW160" s="31" t="str"/>
-      <x:c r="AX160" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY160" s="31" t="str">
+      <x:c r="AT160" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU160" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ160" s="31" t="str">
+      <x:c r="AV160" s="31" t="str">
         <x:v>Link aus expliziter Data-Availability-Statement; 202 Datendatei(en) über GitHub-API bestätigt</x:v>
       </x:c>
     </x:row>
@@ -15121,17 +14521,13 @@
       <x:c r="AQ161" s="31" t="str"/>
       <x:c r="AR161" s="31" t="str"/>
       <x:c r="AS161" s="31" t="str"/>
-      <x:c r="AT161" s="37" t="str"/>
-      <x:c r="AU161" s="31" t="str"/>
-      <x:c r="AV161" s="31" t="str"/>
-      <x:c r="AW161" s="31" t="str"/>
-      <x:c r="AX161" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY161" s="31" t="str">
+      <x:c r="AT161" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU161" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ161" s="31" t="str">
+      <x:c r="AV161" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -15205,17 +14601,13 @@
       <x:c r="AQ162" s="31" t="str"/>
       <x:c r="AR162" s="31" t="str"/>
       <x:c r="AS162" s="31" t="str"/>
-      <x:c r="AT162" s="37" t="str"/>
-      <x:c r="AU162" s="31" t="str"/>
-      <x:c r="AV162" s="31" t="str"/>
-      <x:c r="AW162" s="31" t="str"/>
-      <x:c r="AX162" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY162" s="31" t="str">
+      <x:c r="AT162" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU162" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ162" s="31" t="str">
+      <x:c r="AV162" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -15289,17 +14681,13 @@
       <x:c r="AQ163" s="31" t="str"/>
       <x:c r="AR163" s="31" t="str"/>
       <x:c r="AS163" s="31" t="str"/>
-      <x:c r="AT163" s="37" t="str"/>
-      <x:c r="AU163" s="31" t="str"/>
-      <x:c r="AV163" s="31" t="str"/>
-      <x:c r="AW163" s="31" t="str"/>
-      <x:c r="AX163" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY163" s="31" t="str">
+      <x:c r="AT163" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU163" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ163" s="31" t="str">
+      <x:c r="AV163" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -15373,17 +14761,13 @@
       <x:c r="AQ164" s="31" t="str"/>
       <x:c r="AR164" s="31" t="str"/>
       <x:c r="AS164" s="31" t="str"/>
-      <x:c r="AT164" s="37" t="str"/>
-      <x:c r="AU164" s="31" t="str"/>
-      <x:c r="AV164" s="31" t="str"/>
-      <x:c r="AW164" s="31" t="str"/>
-      <x:c r="AX164" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY164" s="31" t="str">
+      <x:c r="AT164" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU164" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ164" s="31" t="str">
+      <x:c r="AV164" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -15455,17 +14839,13 @@
       <x:c r="AQ165" s="31" t="str"/>
       <x:c r="AR165" s="31" t="str"/>
       <x:c r="AS165" s="31" t="str"/>
-      <x:c r="AT165" s="37" t="str"/>
-      <x:c r="AU165" s="31" t="str"/>
-      <x:c r="AV165" s="31" t="str"/>
-      <x:c r="AW165" s="31" t="str"/>
-      <x:c r="AX165" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY165" s="31" t="str">
+      <x:c r="AT165" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU165" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ165" s="31" t="str">
+      <x:c r="AV165" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -15547,17 +14927,13 @@
       <x:c r="AQ166" s="31" t="str"/>
       <x:c r="AR166" s="31" t="str"/>
       <x:c r="AS166" s="31" t="str"/>
-      <x:c r="AT166" s="37" t="str"/>
-      <x:c r="AU166" s="31" t="str"/>
-      <x:c r="AV166" s="31" t="str"/>
-      <x:c r="AW166" s="31" t="str"/>
-      <x:c r="AX166" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY166" s="31" t="str">
+      <x:c r="AT166" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU166" s="31" t="str">
         <x:v>Playwright</x:v>
       </x:c>
-      <x:c r="AZ166" s="31" t="str">
+      <x:c r="AV166" s="31" t="str">
         <x:v>Titel-/Autor:innen-Match (1.00)</x:v>
       </x:c>
     </x:row>
@@ -15631,17 +15007,13 @@
       <x:c r="AQ167" s="31" t="str"/>
       <x:c r="AR167" s="31" t="str"/>
       <x:c r="AS167" s="31" t="str"/>
-      <x:c r="AT167" s="37" t="str"/>
-      <x:c r="AU167" s="31" t="str"/>
-      <x:c r="AV167" s="31" t="str"/>
-      <x:c r="AW167" s="31" t="str"/>
-      <x:c r="AX167" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY167" s="31" t="str">
+      <x:c r="AT167" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU167" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ167" s="31" t="str">
+      <x:c r="AV167" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -15717,17 +15089,13 @@
       <x:c r="AQ168" s="31" t="str"/>
       <x:c r="AR168" s="31" t="str"/>
       <x:c r="AS168" s="31" t="str"/>
-      <x:c r="AT168" s="37" t="str"/>
-      <x:c r="AU168" s="31" t="str"/>
-      <x:c r="AV168" s="31" t="str"/>
-      <x:c r="AW168" s="31" t="str"/>
-      <x:c r="AX168" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY168" s="31" t="str">
+      <x:c r="AT168" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU168" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ168" s="31" t="str">
+      <x:c r="AV168" s="31" t="str">
         <x:v>Dataset-Treffer ohne hinreichend engen Publikationsbezug (0.25); Dataset-Treffer ohne hinreichend engen Publikationsbezug (0.00); Dataset-Treffer ohne hinreichend engen Publikationsbezug (0.22)</x:v>
       </x:c>
     </x:row>
@@ -15809,17 +15177,13 @@
       <x:c r="AQ169" s="31" t="str"/>
       <x:c r="AR169" s="31" t="str"/>
       <x:c r="AS169" s="31" t="str"/>
-      <x:c r="AT169" s="37" t="str"/>
-      <x:c r="AU169" s="31" t="str"/>
-      <x:c r="AV169" s="31" t="str"/>
-      <x:c r="AW169" s="31" t="str"/>
-      <x:c r="AX169" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY169" s="31" t="str">
+      <x:c r="AT169" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU169" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ169" s="31" t="str">
+      <x:c r="AV169" s="31" t="str">
         <x:v>Titel-/Autor:innen-Match (1.00)</x:v>
       </x:c>
     </x:row>
@@ -15893,17 +15257,13 @@
       <x:c r="AQ170" s="31" t="str"/>
       <x:c r="AR170" s="31" t="str"/>
       <x:c r="AS170" s="31" t="str"/>
-      <x:c r="AT170" s="37" t="str"/>
-      <x:c r="AU170" s="31" t="str"/>
-      <x:c r="AV170" s="31" t="str"/>
-      <x:c r="AW170" s="31" t="str"/>
-      <x:c r="AX170" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY170" s="31" t="str">
+      <x:c r="AT170" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU170" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ170" s="31" t="str">
+      <x:c r="AV170" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -15979,17 +15339,13 @@
       <x:c r="AQ171" s="31" t="str"/>
       <x:c r="AR171" s="31" t="str"/>
       <x:c r="AS171" s="31" t="str"/>
-      <x:c r="AT171" s="37" t="str"/>
-      <x:c r="AU171" s="31" t="str"/>
-      <x:c r="AV171" s="31" t="str"/>
-      <x:c r="AW171" s="31" t="str"/>
-      <x:c r="AX171" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY171" s="31" t="str">
+      <x:c r="AT171" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU171" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ171" s="31" t="str">
+      <x:c r="AV171" s="31" t="str">
         <x:v>Dataset-Treffer ohne hinreichend engen Publikationsbezug (0.43); Dataset-Treffer ohne hinreichend engen Publikationsbezug (0.00)</x:v>
       </x:c>
     </x:row>
@@ -16065,17 +15421,13 @@
       <x:c r="AQ172" s="31" t="str"/>
       <x:c r="AR172" s="31" t="str"/>
       <x:c r="AS172" s="31" t="str"/>
-      <x:c r="AT172" s="37" t="str"/>
-      <x:c r="AU172" s="31" t="str"/>
-      <x:c r="AV172" s="31" t="str"/>
-      <x:c r="AW172" s="31" t="str"/>
-      <x:c r="AX172" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY172" s="31" t="str">
+      <x:c r="AT172" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU172" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ172" s="31" t="str">
+      <x:c r="AV172" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -16149,17 +15501,13 @@
       <x:c r="AQ173" s="31" t="str"/>
       <x:c r="AR173" s="31" t="str"/>
       <x:c r="AS173" s="31" t="str"/>
-      <x:c r="AT173" s="37" t="str"/>
-      <x:c r="AU173" s="31" t="str"/>
-      <x:c r="AV173" s="31" t="str"/>
-      <x:c r="AW173" s="31" t="str"/>
-      <x:c r="AX173" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY173" s="31" t="str">
+      <x:c r="AT173" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU173" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ173" s="31" t="str">
+      <x:c r="AV173" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -16241,17 +15589,13 @@
       <x:c r="AQ174" s="31" t="str"/>
       <x:c r="AR174" s="31" t="str"/>
       <x:c r="AS174" s="31" t="str"/>
-      <x:c r="AT174" s="37" t="str"/>
-      <x:c r="AU174" s="31" t="str"/>
-      <x:c r="AV174" s="31" t="str"/>
-      <x:c r="AW174" s="31" t="str"/>
-      <x:c r="AX174" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY174" s="31" t="str">
+      <x:c r="AT174" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU174" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ174" s="31" t="str">
+      <x:c r="AV174" s="31" t="str">
         <x:v>Identischer normalisierter Titel und starke Autor:innenüberschneidung mit item_3686548; Titel-/Autor:innen-Match (1.00); 208 Datendatei(en) über OSF-API bestätigt</x:v>
       </x:c>
     </x:row>
@@ -16335,18 +15679,14 @@
       <x:c r="AQ175" s="31" t="str"/>
       <x:c r="AR175" s="31" t="str"/>
       <x:c r="AS175" s="31" t="str"/>
-      <x:c r="AT175" s="37" t="str"/>
-      <x:c r="AU175" s="31" t="str"/>
-      <x:c r="AV175" s="31" t="str"/>
-      <x:c r="AW175" s="31" t="str"/>
-      <x:c r="AX175" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY175" s="31" t="str">
+      <x:c r="AT175" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU175" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ175" s="31" t="str">
-        <x:v>Link aus expliziter Data-Availability-Statement; 1 Datendatei(en) über OSF-API bestätigt</x:v>
+      <x:c r="AV175" s="31" t="str">
+        <x:v>Link aus expliziter Data-Availability-Statement</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="34" customHeight="1">
@@ -16421,17 +15761,13 @@
       <x:c r="AQ176" s="31" t="str"/>
       <x:c r="AR176" s="31" t="str"/>
       <x:c r="AS176" s="31" t="str"/>
-      <x:c r="AT176" s="37" t="str"/>
-      <x:c r="AU176" s="31" t="str"/>
-      <x:c r="AV176" s="31" t="str"/>
-      <x:c r="AW176" s="31" t="str"/>
-      <x:c r="AX176" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY176" s="31" t="str">
+      <x:c r="AT176" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU176" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ176" s="31" t="str">
+      <x:c r="AV176" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -16505,17 +15841,13 @@
       <x:c r="AQ177" s="31" t="str"/>
       <x:c r="AR177" s="31" t="str"/>
       <x:c r="AS177" s="31" t="str"/>
-      <x:c r="AT177" s="37" t="str"/>
-      <x:c r="AU177" s="31" t="str"/>
-      <x:c r="AV177" s="31" t="str"/>
-      <x:c r="AW177" s="31" t="str"/>
-      <x:c r="AX177" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY177" s="31" t="str">
+      <x:c r="AT177" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU177" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ177" s="31" t="str">
+      <x:c r="AV177" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -16591,17 +15923,13 @@
       <x:c r="AQ178" s="31" t="str"/>
       <x:c r="AR178" s="31" t="str"/>
       <x:c r="AS178" s="31" t="str"/>
-      <x:c r="AT178" s="37" t="str"/>
-      <x:c r="AU178" s="31" t="str"/>
-      <x:c r="AV178" s="31" t="str"/>
-      <x:c r="AW178" s="31" t="str"/>
-      <x:c r="AX178" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY178" s="31" t="str">
+      <x:c r="AT178" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU178" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ178" s="31" t="str">
+      <x:c r="AV178" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -16677,17 +16005,13 @@
       <x:c r="AQ179" s="31" t="str"/>
       <x:c r="AR179" s="31" t="str"/>
       <x:c r="AS179" s="31" t="str"/>
-      <x:c r="AT179" s="37" t="str"/>
-      <x:c r="AU179" s="31" t="str"/>
-      <x:c r="AV179" s="31" t="str"/>
-      <x:c r="AW179" s="31" t="str"/>
-      <x:c r="AX179" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY179" s="31" t="str">
+      <x:c r="AT179" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU179" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ179" s="31" t="str">
+      <x:c r="AV179" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -16771,17 +16095,13 @@
       <x:c r="AQ180" s="31" t="str"/>
       <x:c r="AR180" s="31" t="str"/>
       <x:c r="AS180" s="31" t="str"/>
-      <x:c r="AT180" s="37" t="str"/>
-      <x:c r="AU180" s="31" t="str"/>
-      <x:c r="AV180" s="31" t="str"/>
-      <x:c r="AW180" s="31" t="str"/>
-      <x:c r="AX180" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY180" s="31" t="str">
+      <x:c r="AT180" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU180" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ180" s="31" t="str">
+      <x:c r="AV180" s="31" t="str">
         <x:v>Link aus Data-Availability-Abschnitt des öffentlichen PuRe-Volltexts</x:v>
       </x:c>
     </x:row>
@@ -16857,17 +16177,13 @@
       <x:c r="AQ181" s="31" t="str"/>
       <x:c r="AR181" s="31" t="str"/>
       <x:c r="AS181" s="31" t="str"/>
-      <x:c r="AT181" s="37" t="str"/>
-      <x:c r="AU181" s="31" t="str"/>
-      <x:c r="AV181" s="31" t="str"/>
-      <x:c r="AW181" s="31" t="str"/>
-      <x:c r="AX181" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY181" s="31" t="str">
+      <x:c r="AT181" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU181" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ181" s="31" t="str">
+      <x:c r="AV181" s="31" t="str">
         <x:v>Dataset-Treffer ohne hinreichend engen Publikationsbezug (0.13); Dataset-Treffer ohne hinreichend engen Publikationsbezug (0.20)</x:v>
       </x:c>
     </x:row>
@@ -16943,17 +16259,13 @@
       <x:c r="AQ182" s="31" t="str"/>
       <x:c r="AR182" s="31" t="str"/>
       <x:c r="AS182" s="31" t="str"/>
-      <x:c r="AT182" s="37" t="str"/>
-      <x:c r="AU182" s="31" t="str"/>
-      <x:c r="AV182" s="31" t="str"/>
-      <x:c r="AW182" s="31" t="str"/>
-      <x:c r="AX182" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY182" s="31" t="str">
+      <x:c r="AT182" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU182" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ182" s="31" t="str">
+      <x:c r="AV182" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -17027,17 +16339,13 @@
       <x:c r="AQ183" s="31" t="str"/>
       <x:c r="AR183" s="31" t="str"/>
       <x:c r="AS183" s="31" t="str"/>
-      <x:c r="AT183" s="37" t="str"/>
-      <x:c r="AU183" s="31" t="str"/>
-      <x:c r="AV183" s="31" t="str"/>
-      <x:c r="AW183" s="31" t="str"/>
-      <x:c r="AX183" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY183" s="31" t="str">
+      <x:c r="AT183" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU183" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ183" s="31" t="str">
+      <x:c r="AV183" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -17113,17 +16421,13 @@
       <x:c r="AQ184" s="31" t="str"/>
       <x:c r="AR184" s="31" t="str"/>
       <x:c r="AS184" s="31" t="str"/>
-      <x:c r="AT184" s="37" t="str"/>
-      <x:c r="AU184" s="31" t="str"/>
-      <x:c r="AV184" s="31" t="str"/>
-      <x:c r="AW184" s="31" t="str"/>
-      <x:c r="AX184" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY184" s="31" t="str">
+      <x:c r="AT184" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU184" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ184" s="31" t="str">
+      <x:c r="AV184" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -17197,17 +16501,13 @@
       <x:c r="AQ185" s="31" t="str"/>
       <x:c r="AR185" s="31" t="str"/>
       <x:c r="AS185" s="31" t="str"/>
-      <x:c r="AT185" s="37" t="str"/>
-      <x:c r="AU185" s="31" t="str"/>
-      <x:c r="AV185" s="31" t="str"/>
-      <x:c r="AW185" s="31" t="str"/>
-      <x:c r="AX185" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY185" s="31" t="str">
+      <x:c r="AT185" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU185" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ185" s="31" t="str">
+      <x:c r="AV185" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -17281,17 +16581,13 @@
       <x:c r="AQ186" s="31" t="str"/>
       <x:c r="AR186" s="31" t="str"/>
       <x:c r="AS186" s="31" t="str"/>
-      <x:c r="AT186" s="37" t="str"/>
-      <x:c r="AU186" s="31" t="str"/>
-      <x:c r="AV186" s="31" t="str"/>
-      <x:c r="AW186" s="31" t="str"/>
-      <x:c r="AX186" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY186" s="31" t="str">
+      <x:c r="AT186" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU186" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ186" s="31" t="str">
+      <x:c r="AV186" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -17365,17 +16661,13 @@
       <x:c r="AQ187" s="31" t="str"/>
       <x:c r="AR187" s="31" t="str"/>
       <x:c r="AS187" s="31" t="str"/>
-      <x:c r="AT187" s="37" t="str"/>
-      <x:c r="AU187" s="31" t="str"/>
-      <x:c r="AV187" s="31" t="str"/>
-      <x:c r="AW187" s="31" t="str"/>
-      <x:c r="AX187" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY187" s="31" t="str">
+      <x:c r="AT187" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU187" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ187" s="31" t="str">
+      <x:c r="AV187" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -17449,17 +16741,13 @@
       <x:c r="AQ188" s="31" t="str"/>
       <x:c r="AR188" s="31" t="str"/>
       <x:c r="AS188" s="31" t="str"/>
-      <x:c r="AT188" s="37" t="str"/>
-      <x:c r="AU188" s="31" t="str"/>
-      <x:c r="AV188" s="31" t="str"/>
-      <x:c r="AW188" s="31" t="str"/>
-      <x:c r="AX188" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY188" s="31" t="str">
+      <x:c r="AT188" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU188" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ188" s="31" t="str">
+      <x:c r="AV188" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -17535,17 +16823,13 @@
       <x:c r="AQ189" s="31" t="str"/>
       <x:c r="AR189" s="31" t="str"/>
       <x:c r="AS189" s="31" t="str"/>
-      <x:c r="AT189" s="37" t="str"/>
-      <x:c r="AU189" s="31" t="str"/>
-      <x:c r="AV189" s="31" t="str"/>
-      <x:c r="AW189" s="31" t="str"/>
-      <x:c r="AX189" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY189" s="31" t="str">
+      <x:c r="AT189" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU189" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ189" s="31" t="str">
+      <x:c r="AV189" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -17621,17 +16905,13 @@
       <x:c r="AQ190" s="31" t="str"/>
       <x:c r="AR190" s="31" t="str"/>
       <x:c r="AS190" s="31" t="str"/>
-      <x:c r="AT190" s="37" t="str"/>
-      <x:c r="AU190" s="31" t="str"/>
-      <x:c r="AV190" s="31" t="str"/>
-      <x:c r="AW190" s="31" t="str"/>
-      <x:c r="AX190" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY190" s="31" t="str">
+      <x:c r="AT190" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU190" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ190" s="31" t="str">
+      <x:c r="AV190" s="31" t="str">
         <x:v>Verlagsseite nennt keine eindeutige vorhandene Datenausgabe</x:v>
       </x:c>
     </x:row>
@@ -17705,17 +16985,13 @@
       <x:c r="AQ191" s="31" t="str"/>
       <x:c r="AR191" s="31" t="str"/>
       <x:c r="AS191" s="31" t="str"/>
-      <x:c r="AT191" s="37" t="str"/>
-      <x:c r="AU191" s="31" t="str"/>
-      <x:c r="AV191" s="31" t="str"/>
-      <x:c r="AW191" s="31" t="str"/>
-      <x:c r="AX191" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY191" s="31" t="str">
+      <x:c r="AT191" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU191" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ191" s="31" t="str">
+      <x:c r="AV191" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -17791,17 +17067,13 @@
       <x:c r="AQ192" s="31" t="str"/>
       <x:c r="AR192" s="31" t="str"/>
       <x:c r="AS192" s="31" t="str"/>
-      <x:c r="AT192" s="37" t="str"/>
-      <x:c r="AU192" s="31" t="str"/>
-      <x:c r="AV192" s="31" t="str"/>
-      <x:c r="AW192" s="31" t="str"/>
-      <x:c r="AX192" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY192" s="31" t="str">
+      <x:c r="AT192" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU192" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ192" s="31" t="str">
+      <x:c r="AV192" s="31" t="str">
         <x:v>Dataset-Treffer ohne hinreichend engen Publikationsbezug (0.00)</x:v>
       </x:c>
     </x:row>
@@ -17875,17 +17147,13 @@
       <x:c r="AQ193" s="31" t="str"/>
       <x:c r="AR193" s="31" t="str"/>
       <x:c r="AS193" s="31" t="str"/>
-      <x:c r="AT193" s="37" t="str"/>
-      <x:c r="AU193" s="31" t="str"/>
-      <x:c r="AV193" s="31" t="str"/>
-      <x:c r="AW193" s="31" t="str"/>
-      <x:c r="AX193" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY193" s="31" t="str">
+      <x:c r="AT193" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU193" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ193" s="31" t="str">
+      <x:c r="AV193" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -17959,17 +17227,13 @@
       <x:c r="AQ194" s="31" t="str"/>
       <x:c r="AR194" s="31" t="str"/>
       <x:c r="AS194" s="31" t="str"/>
-      <x:c r="AT194" s="37" t="str"/>
-      <x:c r="AU194" s="31" t="str"/>
-      <x:c r="AV194" s="31" t="str"/>
-      <x:c r="AW194" s="31" t="str"/>
-      <x:c r="AX194" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY194" s="31" t="str">
+      <x:c r="AT194" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU194" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ194" s="31" t="str">
+      <x:c r="AV194" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -18043,17 +17307,13 @@
       <x:c r="AQ195" s="31" t="str"/>
       <x:c r="AR195" s="31" t="str"/>
       <x:c r="AS195" s="31" t="str"/>
-      <x:c r="AT195" s="37" t="str"/>
-      <x:c r="AU195" s="31" t="str"/>
-      <x:c r="AV195" s="31" t="str"/>
-      <x:c r="AW195" s="31" t="str"/>
-      <x:c r="AX195" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY195" s="31" t="str">
+      <x:c r="AT195" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU195" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ195" s="31" t="str">
+      <x:c r="AV195" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -18129,17 +17389,13 @@
       <x:c r="AQ196" s="31" t="str"/>
       <x:c r="AR196" s="31" t="str"/>
       <x:c r="AS196" s="31" t="str"/>
-      <x:c r="AT196" s="37" t="str"/>
-      <x:c r="AU196" s="31" t="str"/>
-      <x:c r="AV196" s="31" t="str"/>
-      <x:c r="AW196" s="31" t="str"/>
-      <x:c r="AX196" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY196" s="31" t="str">
+      <x:c r="AT196" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU196" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ196" s="31" t="str">
+      <x:c r="AV196" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -18213,17 +17469,13 @@
       <x:c r="AQ197" s="31" t="str"/>
       <x:c r="AR197" s="31" t="str"/>
       <x:c r="AS197" s="31" t="str"/>
-      <x:c r="AT197" s="37" t="str"/>
-      <x:c r="AU197" s="31" t="str"/>
-      <x:c r="AV197" s="31" t="str"/>
-      <x:c r="AW197" s="31" t="str"/>
-      <x:c r="AX197" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY197" s="31" t="str">
+      <x:c r="AT197" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU197" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ197" s="31" t="str">
+      <x:c r="AV197" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -18297,17 +17549,13 @@
       <x:c r="AQ198" s="31" t="str"/>
       <x:c r="AR198" s="31" t="str"/>
       <x:c r="AS198" s="31" t="str"/>
-      <x:c r="AT198" s="37" t="str"/>
-      <x:c r="AU198" s="31" t="str"/>
-      <x:c r="AV198" s="31" t="str"/>
-      <x:c r="AW198" s="31" t="str"/>
-      <x:c r="AX198" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY198" s="31" t="str">
+      <x:c r="AT198" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU198" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ198" s="31" t="str">
+      <x:c r="AV198" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -18383,17 +17631,13 @@
       <x:c r="AQ199" s="31" t="str"/>
       <x:c r="AR199" s="31" t="str"/>
       <x:c r="AS199" s="31" t="str"/>
-      <x:c r="AT199" s="37" t="str"/>
-      <x:c r="AU199" s="31" t="str"/>
-      <x:c r="AV199" s="31" t="str"/>
-      <x:c r="AW199" s="31" t="str"/>
-      <x:c r="AX199" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY199" s="31" t="str">
+      <x:c r="AT199" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU199" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ199" s="31" t="str">
+      <x:c r="AV199" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -18469,17 +17713,13 @@
       <x:c r="AQ200" s="31" t="str"/>
       <x:c r="AR200" s="31" t="str"/>
       <x:c r="AS200" s="31" t="str"/>
-      <x:c r="AT200" s="37" t="str"/>
-      <x:c r="AU200" s="31" t="str"/>
-      <x:c r="AV200" s="31" t="str"/>
-      <x:c r="AW200" s="31" t="str"/>
-      <x:c r="AX200" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY200" s="31" t="str">
+      <x:c r="AT200" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU200" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ200" s="31" t="str">
+      <x:c r="AV200" s="31" t="str">
         <x:v>Dataset-Treffer ohne hinreichend engen Publikationsbezug (0.00)</x:v>
       </x:c>
     </x:row>
@@ -18553,17 +17793,13 @@
       <x:c r="AQ201" s="31" t="str"/>
       <x:c r="AR201" s="31" t="str"/>
       <x:c r="AS201" s="31" t="str"/>
-      <x:c r="AT201" s="37" t="str"/>
-      <x:c r="AU201" s="31" t="str"/>
-      <x:c r="AV201" s="31" t="str"/>
-      <x:c r="AW201" s="31" t="str"/>
-      <x:c r="AX201" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY201" s="31" t="str">
+      <x:c r="AT201" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU201" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ201" s="31" t="str">
+      <x:c r="AV201" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -18645,17 +17881,13 @@
       <x:c r="AQ202" s="31" t="str"/>
       <x:c r="AR202" s="31" t="str"/>
       <x:c r="AS202" s="31" t="str"/>
-      <x:c r="AT202" s="37" t="str"/>
-      <x:c r="AU202" s="31" t="str"/>
-      <x:c r="AV202" s="31" t="str"/>
-      <x:c r="AW202" s="31" t="str"/>
-      <x:c r="AX202" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY202" s="31" t="str">
+      <x:c r="AT202" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU202" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ202" s="31" t="str">
+      <x:c r="AV202" s="31" t="str">
         <x:v>Identischer normalisierter Titel und starke Autor:innenüberschneidung mit item_3612851; Kuratiertes PuRe-Forschungsdatenfeld</x:v>
       </x:c>
     </x:row>
@@ -18731,17 +17963,13 @@
       <x:c r="AQ203" s="31" t="str"/>
       <x:c r="AR203" s="31" t="str"/>
       <x:c r="AS203" s="31" t="str"/>
-      <x:c r="AT203" s="37" t="str"/>
-      <x:c r="AU203" s="31" t="str"/>
-      <x:c r="AV203" s="31" t="str"/>
-      <x:c r="AW203" s="31" t="str"/>
-      <x:c r="AX203" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY203" s="31" t="str">
+      <x:c r="AT203" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU203" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ203" s="31" t="str">
+      <x:c r="AV203" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -18815,17 +18043,13 @@
       <x:c r="AQ204" s="31" t="str"/>
       <x:c r="AR204" s="31" t="str"/>
       <x:c r="AS204" s="31" t="str"/>
-      <x:c r="AT204" s="37" t="str"/>
-      <x:c r="AU204" s="31" t="str"/>
-      <x:c r="AV204" s="31" t="str"/>
-      <x:c r="AW204" s="31" t="str"/>
-      <x:c r="AX204" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY204" s="31" t="str">
+      <x:c r="AT204" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU204" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ204" s="31" t="str">
+      <x:c r="AV204" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -18901,17 +18125,13 @@
       <x:c r="AQ205" s="31" t="str"/>
       <x:c r="AR205" s="31" t="str"/>
       <x:c r="AS205" s="31" t="str"/>
-      <x:c r="AT205" s="37" t="str"/>
-      <x:c r="AU205" s="31" t="str"/>
-      <x:c r="AV205" s="31" t="str"/>
-      <x:c r="AW205" s="31" t="str"/>
-      <x:c r="AX205" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY205" s="31" t="str">
+      <x:c r="AT205" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU205" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ205" s="31" t="str">
+      <x:c r="AV205" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -18985,17 +18205,13 @@
       <x:c r="AQ206" s="31" t="str"/>
       <x:c r="AR206" s="31" t="str"/>
       <x:c r="AS206" s="31" t="str"/>
-      <x:c r="AT206" s="37" t="str"/>
-      <x:c r="AU206" s="31" t="str"/>
-      <x:c r="AV206" s="31" t="str"/>
-      <x:c r="AW206" s="31" t="str"/>
-      <x:c r="AX206" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY206" s="31" t="str">
+      <x:c r="AT206" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU206" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ206" s="31" t="str">
+      <x:c r="AV206" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -19071,17 +18287,13 @@
       <x:c r="AQ207" s="31" t="str"/>
       <x:c r="AR207" s="31" t="str"/>
       <x:c r="AS207" s="31" t="str"/>
-      <x:c r="AT207" s="37" t="str"/>
-      <x:c r="AU207" s="31" t="str"/>
-      <x:c r="AV207" s="31" t="str"/>
-      <x:c r="AW207" s="31" t="str"/>
-      <x:c r="AX207" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY207" s="31" t="str">
+      <x:c r="AT207" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU207" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ207" s="31" t="str">
+      <x:c r="AV207" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -19155,17 +18367,13 @@
       <x:c r="AQ208" s="31" t="str"/>
       <x:c r="AR208" s="31" t="str"/>
       <x:c r="AS208" s="31" t="str"/>
-      <x:c r="AT208" s="37" t="str"/>
-      <x:c r="AU208" s="31" t="str"/>
-      <x:c r="AV208" s="31" t="str"/>
-      <x:c r="AW208" s="31" t="str"/>
-      <x:c r="AX208" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY208" s="31" t="str">
+      <x:c r="AT208" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU208" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ208" s="31" t="str">
+      <x:c r="AV208" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -19241,17 +18449,13 @@
       <x:c r="AQ209" s="31" t="str"/>
       <x:c r="AR209" s="31" t="str"/>
       <x:c r="AS209" s="31" t="str"/>
-      <x:c r="AT209" s="37" t="str"/>
-      <x:c r="AU209" s="31" t="str"/>
-      <x:c r="AV209" s="31" t="str"/>
-      <x:c r="AW209" s="31" t="str"/>
-      <x:c r="AX209" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY209" s="31" t="str">
+      <x:c r="AT209" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU209" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ209" s="31" t="str">
+      <x:c r="AV209" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -19327,17 +18531,13 @@
       <x:c r="AQ210" s="31" t="str"/>
       <x:c r="AR210" s="31" t="str"/>
       <x:c r="AS210" s="31" t="str"/>
-      <x:c r="AT210" s="37" t="str"/>
-      <x:c r="AU210" s="31" t="str"/>
-      <x:c r="AV210" s="31" t="str"/>
-      <x:c r="AW210" s="31" t="str"/>
-      <x:c r="AX210" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY210" s="31" t="str">
+      <x:c r="AT210" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU210" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ210" s="31" t="str">
+      <x:c r="AV210" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -19413,17 +18613,13 @@
       <x:c r="AQ211" s="31" t="str"/>
       <x:c r="AR211" s="31" t="str"/>
       <x:c r="AS211" s="31" t="str"/>
-      <x:c r="AT211" s="37" t="str"/>
-      <x:c r="AU211" s="31" t="str"/>
-      <x:c r="AV211" s="31" t="str"/>
-      <x:c r="AW211" s="31" t="str"/>
-      <x:c r="AX211" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY211" s="31" t="str">
+      <x:c r="AT211" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU211" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ211" s="31" t="str">
+      <x:c r="AV211" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -19499,17 +18695,13 @@
       <x:c r="AQ212" s="31" t="str"/>
       <x:c r="AR212" s="31" t="str"/>
       <x:c r="AS212" s="31" t="str"/>
-      <x:c r="AT212" s="37" t="str"/>
-      <x:c r="AU212" s="31" t="str"/>
-      <x:c r="AV212" s="31" t="str"/>
-      <x:c r="AW212" s="31" t="str"/>
-      <x:c r="AX212" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY212" s="31" t="str">
+      <x:c r="AT212" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU212" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ212" s="31" t="str">
+      <x:c r="AV212" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -19583,17 +18775,13 @@
       <x:c r="AQ213" s="31" t="str"/>
       <x:c r="AR213" s="31" t="str"/>
       <x:c r="AS213" s="31" t="str"/>
-      <x:c r="AT213" s="37" t="str"/>
-      <x:c r="AU213" s="31" t="str"/>
-      <x:c r="AV213" s="31" t="str"/>
-      <x:c r="AW213" s="31" t="str"/>
-      <x:c r="AX213" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY213" s="31" t="str">
+      <x:c r="AT213" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU213" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ213" s="31" t="str">
+      <x:c r="AV213" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -19715,18 +18903,14 @@
       <x:c r="AQ214" s="31" t="str"/>
       <x:c r="AR214" s="31" t="str"/>
       <x:c r="AS214" s="31" t="str"/>
-      <x:c r="AT214" s="37" t="str"/>
-      <x:c r="AU214" s="31" t="str"/>
-      <x:c r="AV214" s="31" t="str"/>
-      <x:c r="AW214" s="31" t="str"/>
-      <x:c r="AX214" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY214" s="31" t="str">
+      <x:c r="AT214" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU214" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ214" s="31" t="str">
-        <x:v>Identischer normalisierter Titel und starke Autor:innenüberschneidung mit item_3657005; Link aus expliziter Data-Availability-Statement; 6 Datendatei(en) über OSF-API bestätigt; Identischer normalisierter Titel und starke Autor:innenüberschneidung mit item_3657005; Link aus expliziter Data-Availability-Statement</x:v>
+      <x:c r="AV214" s="31" t="str">
+        <x:v>Identischer normalisierter Titel und starke Autor:innenüberschneidung mit item_3657005; Link aus expliziter Data-Availability-Statement</x:v>
       </x:c>
     </x:row>
     <x:row r="215" ht="34" customHeight="1">
@@ -19801,17 +18985,13 @@
       <x:c r="AQ215" s="31" t="str"/>
       <x:c r="AR215" s="31" t="str"/>
       <x:c r="AS215" s="31" t="str"/>
-      <x:c r="AT215" s="37" t="str"/>
-      <x:c r="AU215" s="31" t="str"/>
-      <x:c r="AV215" s="31" t="str"/>
-      <x:c r="AW215" s="31" t="str"/>
-      <x:c r="AX215" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY215" s="31" t="str">
+      <x:c r="AT215" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU215" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ215" s="31" t="str">
+      <x:c r="AV215" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -19887,17 +19067,13 @@
       <x:c r="AQ216" s="31" t="str"/>
       <x:c r="AR216" s="31" t="str"/>
       <x:c r="AS216" s="31" t="str"/>
-      <x:c r="AT216" s="37" t="str"/>
-      <x:c r="AU216" s="31" t="str"/>
-      <x:c r="AV216" s="31" t="str"/>
-      <x:c r="AW216" s="31" t="str"/>
-      <x:c r="AX216" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY216" s="31" t="str">
+      <x:c r="AT216" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU216" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ216" s="31" t="str">
+      <x:c r="AV216" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -19973,17 +19149,13 @@
       <x:c r="AQ217" s="31" t="str"/>
       <x:c r="AR217" s="31" t="str"/>
       <x:c r="AS217" s="31" t="str"/>
-      <x:c r="AT217" s="37" t="str"/>
-      <x:c r="AU217" s="31" t="str"/>
-      <x:c r="AV217" s="31" t="str"/>
-      <x:c r="AW217" s="31" t="str"/>
-      <x:c r="AX217" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY217" s="31" t="str">
+      <x:c r="AT217" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU217" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ217" s="31" t="str">
+      <x:c r="AV217" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -20059,17 +19231,13 @@
       <x:c r="AQ218" s="31" t="str"/>
       <x:c r="AR218" s="31" t="str"/>
       <x:c r="AS218" s="31" t="str"/>
-      <x:c r="AT218" s="37" t="str"/>
-      <x:c r="AU218" s="31" t="str"/>
-      <x:c r="AV218" s="31" t="str"/>
-      <x:c r="AW218" s="31" t="str"/>
-      <x:c r="AX218" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY218" s="31" t="str">
+      <x:c r="AT218" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU218" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ218" s="31" t="str">
+      <x:c r="AV218" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -20145,17 +19313,13 @@
       <x:c r="AQ219" s="31" t="str"/>
       <x:c r="AR219" s="31" t="str"/>
       <x:c r="AS219" s="31" t="str"/>
-      <x:c r="AT219" s="37" t="str"/>
-      <x:c r="AU219" s="31" t="str"/>
-      <x:c r="AV219" s="31" t="str"/>
-      <x:c r="AW219" s="31" t="str"/>
-      <x:c r="AX219" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY219" s="31" t="str">
+      <x:c r="AT219" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU219" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ219" s="31" t="str">
+      <x:c r="AV219" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -20231,17 +19395,13 @@
       <x:c r="AQ220" s="31" t="str"/>
       <x:c r="AR220" s="31" t="str"/>
       <x:c r="AS220" s="31" t="str"/>
-      <x:c r="AT220" s="37" t="str"/>
-      <x:c r="AU220" s="31" t="str"/>
-      <x:c r="AV220" s="31" t="str"/>
-      <x:c r="AW220" s="31" t="str"/>
-      <x:c r="AX220" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY220" s="31" t="str">
+      <x:c r="AT220" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU220" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ220" s="31" t="str">
+      <x:c r="AV220" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -20317,17 +19477,13 @@
       <x:c r="AQ221" s="31" t="str"/>
       <x:c r="AR221" s="31" t="str"/>
       <x:c r="AS221" s="31" t="str"/>
-      <x:c r="AT221" s="37" t="str"/>
-      <x:c r="AU221" s="31" t="str"/>
-      <x:c r="AV221" s="31" t="str"/>
-      <x:c r="AW221" s="31" t="str"/>
-      <x:c r="AX221" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY221" s="31" t="str">
+      <x:c r="AT221" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU221" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ221" s="31" t="str">
+      <x:c r="AV221" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -20403,17 +19559,13 @@
       <x:c r="AQ222" s="31" t="str"/>
       <x:c r="AR222" s="31" t="str"/>
       <x:c r="AS222" s="31" t="str"/>
-      <x:c r="AT222" s="37" t="str"/>
-      <x:c r="AU222" s="31" t="str"/>
-      <x:c r="AV222" s="31" t="str"/>
-      <x:c r="AW222" s="31" t="str"/>
-      <x:c r="AX222" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY222" s="31" t="str">
+      <x:c r="AT222" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU222" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ222" s="31" t="str">
+      <x:c r="AV222" s="31" t="str">
         <x:v>Dataset-Treffer ohne hinreichend engen Publikationsbezug (0.10); Dataset-Treffer ohne hinreichend engen Publikationsbezug (0.22); Dataset-Treffer ohne hinreichend engen Publikationsbezug (0.17)</x:v>
       </x:c>
     </x:row>
@@ -20497,18 +19649,14 @@
       <x:c r="AQ223" s="31" t="str"/>
       <x:c r="AR223" s="31" t="str"/>
       <x:c r="AS223" s="31" t="str"/>
-      <x:c r="AT223" s="37" t="str"/>
-      <x:c r="AU223" s="31" t="str"/>
-      <x:c r="AV223" s="31" t="str"/>
-      <x:c r="AW223" s="31" t="str"/>
-      <x:c r="AX223" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY223" s="31" t="str">
+      <x:c r="AT223" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU223" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ223" s="31" t="str">
-        <x:v>Wiley-Datenverfügbarkeitsaussage mit rekursiv geprüften OSF-Datendateien; 2 Datendatei(en) über OSF-API bestätigt</x:v>
+      <x:c r="AV223" s="31" t="str">
+        <x:v>Wiley-Datenverfügbarkeitsaussage mit rekursiv geprüften OSF-Datendateien</x:v>
       </x:c>
     </x:row>
     <x:row r="224" ht="34" customHeight="1">
@@ -20581,17 +19729,13 @@
       <x:c r="AQ224" s="31" t="str"/>
       <x:c r="AR224" s="31" t="str"/>
       <x:c r="AS224" s="31" t="str"/>
-      <x:c r="AT224" s="37" t="str"/>
-      <x:c r="AU224" s="31" t="str"/>
-      <x:c r="AV224" s="31" t="str"/>
-      <x:c r="AW224" s="31" t="str"/>
-      <x:c r="AX224" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY224" s="31" t="str">
+      <x:c r="AT224" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU224" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ224" s="31" t="str">
+      <x:c r="AV224" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -20667,17 +19811,13 @@
       <x:c r="AQ225" s="31" t="str"/>
       <x:c r="AR225" s="31" t="str"/>
       <x:c r="AS225" s="31" t="str"/>
-      <x:c r="AT225" s="37" t="str"/>
-      <x:c r="AU225" s="31" t="str"/>
-      <x:c r="AV225" s="31" t="str"/>
-      <x:c r="AW225" s="31" t="str"/>
-      <x:c r="AX225" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY225" s="31" t="str">
+      <x:c r="AT225" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU225" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ225" s="31" t="str">
+      <x:c r="AV225" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -20751,17 +19891,13 @@
       <x:c r="AQ226" s="31" t="str"/>
       <x:c r="AR226" s="31" t="str"/>
       <x:c r="AS226" s="31" t="str"/>
-      <x:c r="AT226" s="37" t="str"/>
-      <x:c r="AU226" s="31" t="str"/>
-      <x:c r="AV226" s="31" t="str"/>
-      <x:c r="AW226" s="31" t="str"/>
-      <x:c r="AX226" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY226" s="31" t="str">
+      <x:c r="AT226" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU226" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ226" s="31" t="str">
+      <x:c r="AV226" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -20835,17 +19971,13 @@
       <x:c r="AQ227" s="31" t="str"/>
       <x:c r="AR227" s="31" t="str"/>
       <x:c r="AS227" s="31" t="str"/>
-      <x:c r="AT227" s="37" t="str"/>
-      <x:c r="AU227" s="31" t="str"/>
-      <x:c r="AV227" s="31" t="str"/>
-      <x:c r="AW227" s="31" t="str"/>
-      <x:c r="AX227" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY227" s="31" t="str">
+      <x:c r="AT227" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU227" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ227" s="31" t="str">
+      <x:c r="AV227" s="31" t="str">
         <x:v>Dataset-Treffer ohne hinreichend engen Publikationsbezug (0.00)</x:v>
       </x:c>
     </x:row>
@@ -20929,18 +20061,14 @@
       <x:c r="AQ228" s="31" t="str"/>
       <x:c r="AR228" s="31" t="str"/>
       <x:c r="AS228" s="31" t="str"/>
-      <x:c r="AT228" s="37" t="str"/>
-      <x:c r="AU228" s="31" t="str"/>
-      <x:c r="AV228" s="31" t="str"/>
-      <x:c r="AW228" s="31" t="str"/>
-      <x:c r="AX228" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY228" s="31" t="str">
+      <x:c r="AT228" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU228" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ228" s="31" t="str">
-        <x:v>Link aus expliziter Data-Availability-Statement; 3 Datendatei(en) über OSF-API bestätigt</x:v>
+      <x:c r="AV228" s="31" t="str">
+        <x:v>Link aus expliziter Data-Availability-Statement</x:v>
       </x:c>
     </x:row>
     <x:row r="229" ht="34" customHeight="1">
@@ -21015,17 +20143,13 @@
       <x:c r="AQ229" s="31" t="str"/>
       <x:c r="AR229" s="31" t="str"/>
       <x:c r="AS229" s="31" t="str"/>
-      <x:c r="AT229" s="37" t="str"/>
-      <x:c r="AU229" s="31" t="str"/>
-      <x:c r="AV229" s="31" t="str"/>
-      <x:c r="AW229" s="31" t="str"/>
-      <x:c r="AX229" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY229" s="31" t="str">
+      <x:c r="AT229" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU229" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ229" s="31" t="str">
+      <x:c r="AV229" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -21109,17 +20233,13 @@
       <x:c r="AQ230" s="31" t="str"/>
       <x:c r="AR230" s="31" t="str"/>
       <x:c r="AS230" s="31" t="str"/>
-      <x:c r="AT230" s="37" t="str"/>
-      <x:c r="AU230" s="31" t="str"/>
-      <x:c r="AV230" s="31" t="str"/>
-      <x:c r="AW230" s="31" t="str"/>
-      <x:c r="AX230" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY230" s="31" t="str">
+      <x:c r="AT230" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU230" s="31" t="str">
         <x:v>Playwright</x:v>
       </x:c>
-      <x:c r="AZ230" s="31" t="str">
+      <x:c r="AV230" s="31" t="str">
         <x:v>Offizielles INFORMS-Replikationsarchiv mit geprüften Datendateien</x:v>
       </x:c>
     </x:row>
@@ -21195,17 +20315,13 @@
       <x:c r="AQ231" s="31" t="str"/>
       <x:c r="AR231" s="31" t="str"/>
       <x:c r="AS231" s="31" t="str"/>
-      <x:c r="AT231" s="37" t="str"/>
-      <x:c r="AU231" s="31" t="str"/>
-      <x:c r="AV231" s="31" t="str"/>
-      <x:c r="AW231" s="31" t="str"/>
-      <x:c r="AX231" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY231" s="31" t="str">
+      <x:c r="AT231" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU231" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ231" s="31" t="str">
+      <x:c r="AV231" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -21279,17 +20395,13 @@
       <x:c r="AQ232" s="31" t="str"/>
       <x:c r="AR232" s="31" t="str"/>
       <x:c r="AS232" s="31" t="str"/>
-      <x:c r="AT232" s="37" t="str"/>
-      <x:c r="AU232" s="31" t="str"/>
-      <x:c r="AV232" s="31" t="str"/>
-      <x:c r="AW232" s="31" t="str"/>
-      <x:c r="AX232" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY232" s="31" t="str">
+      <x:c r="AT232" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU232" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ232" s="31" t="str">
+      <x:c r="AV232" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -21365,17 +20477,13 @@
       <x:c r="AQ233" s="31" t="str"/>
       <x:c r="AR233" s="31" t="str"/>
       <x:c r="AS233" s="31" t="str"/>
-      <x:c r="AT233" s="37" t="str"/>
-      <x:c r="AU233" s="31" t="str"/>
-      <x:c r="AV233" s="31" t="str"/>
-      <x:c r="AW233" s="31" t="str"/>
-      <x:c r="AX233" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY233" s="31" t="str">
+      <x:c r="AT233" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU233" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ233" s="31" t="str">
+      <x:c r="AV233" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -21451,17 +20559,13 @@
       <x:c r="AQ234" s="31" t="str"/>
       <x:c r="AR234" s="31" t="str"/>
       <x:c r="AS234" s="31" t="str"/>
-      <x:c r="AT234" s="37" t="str"/>
-      <x:c r="AU234" s="31" t="str"/>
-      <x:c r="AV234" s="31" t="str"/>
-      <x:c r="AW234" s="31" t="str"/>
-      <x:c r="AX234" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY234" s="31" t="str">
+      <x:c r="AT234" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU234" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ234" s="31" t="str">
+      <x:c r="AV234" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -21537,17 +20641,13 @@
       <x:c r="AQ235" s="31" t="str"/>
       <x:c r="AR235" s="31" t="str"/>
       <x:c r="AS235" s="31" t="str"/>
-      <x:c r="AT235" s="37" t="str"/>
-      <x:c r="AU235" s="31" t="str"/>
-      <x:c r="AV235" s="31" t="str"/>
-      <x:c r="AW235" s="31" t="str"/>
-      <x:c r="AX235" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY235" s="31" t="str">
+      <x:c r="AT235" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU235" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ235" s="31" t="str">
+      <x:c r="AV235" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -21623,17 +20723,13 @@
       <x:c r="AQ236" s="31" t="str"/>
       <x:c r="AR236" s="31" t="str"/>
       <x:c r="AS236" s="31" t="str"/>
-      <x:c r="AT236" s="37" t="str"/>
-      <x:c r="AU236" s="31" t="str"/>
-      <x:c r="AV236" s="31" t="str"/>
-      <x:c r="AW236" s="31" t="str"/>
-      <x:c r="AX236" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY236" s="31" t="str">
+      <x:c r="AT236" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU236" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ236" s="31" t="str">
+      <x:c r="AV236" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -21715,18 +20811,14 @@
       <x:c r="AQ237" s="31" t="str"/>
       <x:c r="AR237" s="31" t="str"/>
       <x:c r="AS237" s="31" t="str"/>
-      <x:c r="AT237" s="37" t="str"/>
-      <x:c r="AU237" s="31" t="str"/>
-      <x:c r="AV237" s="31" t="str"/>
-      <x:c r="AW237" s="31" t="str"/>
-      <x:c r="AX237" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY237" s="31" t="str">
+      <x:c r="AT237" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU237" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ237" s="31" t="str">
-        <x:v>Bereits auditierter Datensatz einer stark identifizierten Publikationsfassung; 3 Datendatei(en) über OSF-API bestätigt</x:v>
+      <x:c r="AV237" s="31" t="str">
+        <x:v>Bereits auditierter Datensatz einer stark identifizierten Publikationsfassung</x:v>
       </x:c>
     </x:row>
     <x:row r="238" ht="34" customHeight="1">
@@ -21801,17 +20893,13 @@
       <x:c r="AQ238" s="31" t="str"/>
       <x:c r="AR238" s="31" t="str"/>
       <x:c r="AS238" s="31" t="str"/>
-      <x:c r="AT238" s="37" t="str"/>
-      <x:c r="AU238" s="31" t="str"/>
-      <x:c r="AV238" s="31" t="str"/>
-      <x:c r="AW238" s="31" t="str"/>
-      <x:c r="AX238" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY238" s="31" t="str">
+      <x:c r="AT238" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU238" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ238" s="31" t="str">
+      <x:c r="AV238" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -21885,17 +20973,13 @@
       <x:c r="AQ239" s="31" t="str"/>
       <x:c r="AR239" s="31" t="str"/>
       <x:c r="AS239" s="31" t="str"/>
-      <x:c r="AT239" s="37" t="str"/>
-      <x:c r="AU239" s="31" t="str"/>
-      <x:c r="AV239" s="31" t="str"/>
-      <x:c r="AW239" s="31" t="str"/>
-      <x:c r="AX239" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY239" s="31" t="str">
+      <x:c r="AT239" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU239" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ239" s="31" t="str">
+      <x:c r="AV239" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -21971,17 +21055,13 @@
       <x:c r="AQ240" s="31" t="str"/>
       <x:c r="AR240" s="31" t="str"/>
       <x:c r="AS240" s="31" t="str"/>
-      <x:c r="AT240" s="37" t="str"/>
-      <x:c r="AU240" s="31" t="str"/>
-      <x:c r="AV240" s="31" t="str"/>
-      <x:c r="AW240" s="31" t="str"/>
-      <x:c r="AX240" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY240" s="31" t="str">
+      <x:c r="AT240" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU240" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ240" s="31" t="str">
+      <x:c r="AV240" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -22057,17 +21137,13 @@
       <x:c r="AQ241" s="31" t="str"/>
       <x:c r="AR241" s="31" t="str"/>
       <x:c r="AS241" s="31" t="str"/>
-      <x:c r="AT241" s="37" t="str"/>
-      <x:c r="AU241" s="31" t="str"/>
-      <x:c r="AV241" s="31" t="str"/>
-      <x:c r="AW241" s="31" t="str"/>
-      <x:c r="AX241" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY241" s="31" t="str">
+      <x:c r="AT241" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU241" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ241" s="31" t="str">
+      <x:c r="AV241" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -22141,17 +21217,13 @@
       <x:c r="AQ242" s="31" t="str"/>
       <x:c r="AR242" s="31" t="str"/>
       <x:c r="AS242" s="31" t="str"/>
-      <x:c r="AT242" s="37" t="str"/>
-      <x:c r="AU242" s="31" t="str"/>
-      <x:c r="AV242" s="31" t="str"/>
-      <x:c r="AW242" s="31" t="str"/>
-      <x:c r="AX242" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY242" s="31" t="str">
+      <x:c r="AT242" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU242" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ242" s="31" t="str">
+      <x:c r="AV242" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -22225,17 +21297,13 @@
       <x:c r="AQ243" s="31" t="str"/>
       <x:c r="AR243" s="31" t="str"/>
       <x:c r="AS243" s="31" t="str"/>
-      <x:c r="AT243" s="37" t="str"/>
-      <x:c r="AU243" s="31" t="str"/>
-      <x:c r="AV243" s="31" t="str"/>
-      <x:c r="AW243" s="31" t="str"/>
-      <x:c r="AX243" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY243" s="31" t="str">
+      <x:c r="AT243" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU243" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ243" s="31" t="str">
+      <x:c r="AV243" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -22311,17 +21379,13 @@
       <x:c r="AQ244" s="31" t="str"/>
       <x:c r="AR244" s="31" t="str"/>
       <x:c r="AS244" s="31" t="str"/>
-      <x:c r="AT244" s="37" t="str"/>
-      <x:c r="AU244" s="31" t="str"/>
-      <x:c r="AV244" s="31" t="str"/>
-      <x:c r="AW244" s="31" t="str"/>
-      <x:c r="AX244" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY244" s="31" t="str">
+      <x:c r="AT244" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU244" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ244" s="31" t="str">
+      <x:c r="AV244" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -22397,17 +21461,13 @@
       <x:c r="AQ245" s="31" t="str"/>
       <x:c r="AR245" s="31" t="str"/>
       <x:c r="AS245" s="31" t="str"/>
-      <x:c r="AT245" s="37" t="str"/>
-      <x:c r="AU245" s="31" t="str"/>
-      <x:c r="AV245" s="31" t="str"/>
-      <x:c r="AW245" s="31" t="str"/>
-      <x:c r="AX245" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY245" s="31" t="str">
+      <x:c r="AT245" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU245" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ245" s="31" t="str">
+      <x:c r="AV245" s="31" t="str">
         <x:v>Dataset-Treffer ohne hinreichend engen Publikationsbezug (0.00)</x:v>
       </x:c>
     </x:row>
@@ -22483,17 +21543,13 @@
       <x:c r="AQ246" s="31" t="str"/>
       <x:c r="AR246" s="31" t="str"/>
       <x:c r="AS246" s="31" t="str"/>
-      <x:c r="AT246" s="37" t="str"/>
-      <x:c r="AU246" s="31" t="str"/>
-      <x:c r="AV246" s="31" t="str"/>
-      <x:c r="AW246" s="31" t="str"/>
-      <x:c r="AX246" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY246" s="31" t="str">
+      <x:c r="AT246" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU246" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ246" s="31" t="str">
+      <x:c r="AV246" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -22567,17 +21623,13 @@
       <x:c r="AQ247" s="31" t="str"/>
       <x:c r="AR247" s="31" t="str"/>
       <x:c r="AS247" s="31" t="str"/>
-      <x:c r="AT247" s="37" t="str"/>
-      <x:c r="AU247" s="31" t="str"/>
-      <x:c r="AV247" s="31" t="str"/>
-      <x:c r="AW247" s="31" t="str"/>
-      <x:c r="AX247" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY247" s="31" t="str">
+      <x:c r="AT247" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU247" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ247" s="31" t="str">
+      <x:c r="AV247" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -22651,17 +21703,13 @@
       <x:c r="AQ248" s="31" t="str"/>
       <x:c r="AR248" s="31" t="str"/>
       <x:c r="AS248" s="31" t="str"/>
-      <x:c r="AT248" s="37" t="str"/>
-      <x:c r="AU248" s="31" t="str"/>
-      <x:c r="AV248" s="31" t="str"/>
-      <x:c r="AW248" s="31" t="str"/>
-      <x:c r="AX248" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY248" s="31" t="str">
+      <x:c r="AT248" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU248" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ248" s="31" t="str">
+      <x:c r="AV248" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -22735,17 +21783,13 @@
       <x:c r="AQ249" s="31" t="str"/>
       <x:c r="AR249" s="31" t="str"/>
       <x:c r="AS249" s="31" t="str"/>
-      <x:c r="AT249" s="37" t="str"/>
-      <x:c r="AU249" s="31" t="str"/>
-      <x:c r="AV249" s="31" t="str"/>
-      <x:c r="AW249" s="31" t="str"/>
-      <x:c r="AX249" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY249" s="31" t="str">
+      <x:c r="AT249" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU249" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ249" s="31" t="str">
+      <x:c r="AV249" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -22819,17 +21863,13 @@
       <x:c r="AQ250" s="31" t="str"/>
       <x:c r="AR250" s="31" t="str"/>
       <x:c r="AS250" s="31" t="str"/>
-      <x:c r="AT250" s="37" t="str"/>
-      <x:c r="AU250" s="31" t="str"/>
-      <x:c r="AV250" s="31" t="str"/>
-      <x:c r="AW250" s="31" t="str"/>
-      <x:c r="AX250" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY250" s="31" t="str">
+      <x:c r="AT250" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU250" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ250" s="31" t="str">
+      <x:c r="AV250" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -22905,17 +21945,13 @@
       <x:c r="AQ251" s="31" t="str"/>
       <x:c r="AR251" s="31" t="str"/>
       <x:c r="AS251" s="31" t="str"/>
-      <x:c r="AT251" s="37" t="str"/>
-      <x:c r="AU251" s="31" t="str"/>
-      <x:c r="AV251" s="31" t="str"/>
-      <x:c r="AW251" s="31" t="str"/>
-      <x:c r="AX251" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY251" s="31" t="str">
+      <x:c r="AT251" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU251" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ251" s="31" t="str">
+      <x:c r="AV251" s="31" t="str">
         <x:v>Verlagsseite nennt keine eindeutige vorhandene Datenausgabe</x:v>
       </x:c>
     </x:row>
@@ -22997,18 +22033,14 @@
       <x:c r="AQ252" s="31" t="str"/>
       <x:c r="AR252" s="31" t="str"/>
       <x:c r="AS252" s="31" t="str"/>
-      <x:c r="AT252" s="37" t="str"/>
-      <x:c r="AU252" s="31" t="str"/>
-      <x:c r="AV252" s="31" t="str"/>
-      <x:c r="AW252" s="31" t="str"/>
-      <x:c r="AX252" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY252" s="31" t="str">
+      <x:c r="AT252" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU252" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ252" s="31" t="str">
-        <x:v>Link aus Data-Availability-Abschnitt des öffentlichen PuRe-Volltexts; 3 Datendatei(en) über OSF-API bestätigt</x:v>
+      <x:c r="AV252" s="31" t="str">
+        <x:v>Link aus Data-Availability-Abschnitt des öffentlichen PuRe-Volltexts</x:v>
       </x:c>
     </x:row>
     <x:row r="253" ht="34" customHeight="1">
@@ -23081,17 +22113,13 @@
       <x:c r="AQ253" s="31" t="str"/>
       <x:c r="AR253" s="31" t="str"/>
       <x:c r="AS253" s="31" t="str"/>
-      <x:c r="AT253" s="37" t="str"/>
-      <x:c r="AU253" s="31" t="str"/>
-      <x:c r="AV253" s="31" t="str"/>
-      <x:c r="AW253" s="31" t="str"/>
-      <x:c r="AX253" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY253" s="31" t="str">
+      <x:c r="AT253" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU253" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ253" s="31" t="str">
+      <x:c r="AV253" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -23175,17 +22203,13 @@
       <x:c r="AQ254" s="31" t="str"/>
       <x:c r="AR254" s="31" t="str"/>
       <x:c r="AS254" s="31" t="str"/>
-      <x:c r="AT254" s="37" t="str"/>
-      <x:c r="AU254" s="31" t="str"/>
-      <x:c r="AV254" s="31" t="str"/>
-      <x:c r="AW254" s="31" t="str"/>
-      <x:c r="AX254" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY254" s="31" t="str">
+      <x:c r="AT254" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU254" s="31" t="str">
         <x:v>Playwright</x:v>
       </x:c>
-      <x:c r="AZ254" s="31" t="str">
+      <x:c r="AV254" s="31" t="str">
         <x:v>Titel-/Autor:innen-Match (1.00); Landingpage antwortet mit HTTP 403 und ist zugriffsgeschützt</x:v>
       </x:c>
     </x:row>
@@ -23261,17 +22285,13 @@
       <x:c r="AQ255" s="31" t="str"/>
       <x:c r="AR255" s="31" t="str"/>
       <x:c r="AS255" s="31" t="str"/>
-      <x:c r="AT255" s="37" t="str"/>
-      <x:c r="AU255" s="31" t="str"/>
-      <x:c r="AV255" s="31" t="str"/>
-      <x:c r="AW255" s="31" t="str"/>
-      <x:c r="AX255" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY255" s="31" t="str">
+      <x:c r="AT255" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU255" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ255" s="31" t="str">
+      <x:c r="AV255" s="31" t="str">
         <x:v>Dataset-Treffer ohne hinreichend engen Publikationsbezug (0.14)</x:v>
       </x:c>
     </x:row>
@@ -23345,17 +22365,13 @@
       <x:c r="AQ256" s="31" t="str"/>
       <x:c r="AR256" s="31" t="str"/>
       <x:c r="AS256" s="31" t="str"/>
-      <x:c r="AT256" s="37" t="str"/>
-      <x:c r="AU256" s="31" t="str"/>
-      <x:c r="AV256" s="31" t="str"/>
-      <x:c r="AW256" s="31" t="str"/>
-      <x:c r="AX256" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY256" s="31" t="str">
+      <x:c r="AT256" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU256" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ256" s="31" t="str">
+      <x:c r="AV256" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -23429,17 +22445,13 @@
       <x:c r="AQ257" s="31" t="str"/>
       <x:c r="AR257" s="31" t="str"/>
       <x:c r="AS257" s="31" t="str"/>
-      <x:c r="AT257" s="37" t="str"/>
-      <x:c r="AU257" s="31" t="str"/>
-      <x:c r="AV257" s="31" t="str"/>
-      <x:c r="AW257" s="31" t="str"/>
-      <x:c r="AX257" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY257" s="31" t="str">
+      <x:c r="AT257" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU257" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ257" s="31" t="str">
+      <x:c r="AV257" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -23523,17 +22535,13 @@
       <x:c r="AQ258" s="31" t="str"/>
       <x:c r="AR258" s="31" t="str"/>
       <x:c r="AS258" s="31" t="str"/>
-      <x:c r="AT258" s="37" t="str"/>
-      <x:c r="AU258" s="31" t="str"/>
-      <x:c r="AV258" s="31" t="str"/>
-      <x:c r="AW258" s="31" t="str"/>
-      <x:c r="AX258" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY258" s="31" t="str">
+      <x:c r="AT258" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU258" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ258" s="31" t="str">
+      <x:c r="AV258" s="31" t="str">
         <x:v>Zenodo-Replikationspaket mit Titel-/Autor:innen-Match und geprüften Datendateien</x:v>
       </x:c>
     </x:row>
@@ -23607,17 +22615,13 @@
       <x:c r="AQ259" s="31" t="str"/>
       <x:c r="AR259" s="31" t="str"/>
       <x:c r="AS259" s="31" t="str"/>
-      <x:c r="AT259" s="37" t="str"/>
-      <x:c r="AU259" s="31" t="str"/>
-      <x:c r="AV259" s="31" t="str"/>
-      <x:c r="AW259" s="31" t="str"/>
-      <x:c r="AX259" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY259" s="31" t="str">
+      <x:c r="AT259" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU259" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ259" s="31" t="str">
+      <x:c r="AV259" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -23693,17 +22697,13 @@
       <x:c r="AQ260" s="31" t="str"/>
       <x:c r="AR260" s="31" t="str"/>
       <x:c r="AS260" s="31" t="str"/>
-      <x:c r="AT260" s="37" t="str"/>
-      <x:c r="AU260" s="31" t="str"/>
-      <x:c r="AV260" s="31" t="str"/>
-      <x:c r="AW260" s="31" t="str"/>
-      <x:c r="AX260" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY260" s="31" t="str">
+      <x:c r="AT260" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU260" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ260" s="31" t="str">
+      <x:c r="AV260" s="31" t="str">
         <x:v>Dataset-Treffer ohne hinreichend engen Publikationsbezug (0.17)</x:v>
       </x:c>
     </x:row>
@@ -23777,17 +22777,13 @@
       <x:c r="AQ261" s="31" t="str"/>
       <x:c r="AR261" s="31" t="str"/>
       <x:c r="AS261" s="31" t="str"/>
-      <x:c r="AT261" s="37" t="str"/>
-      <x:c r="AU261" s="31" t="str"/>
-      <x:c r="AV261" s="31" t="str"/>
-      <x:c r="AW261" s="31" t="str"/>
-      <x:c r="AX261" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY261" s="31" t="str">
+      <x:c r="AT261" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU261" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ261" s="31" t="str">
+      <x:c r="AV261" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -23869,17 +22865,13 @@
       <x:c r="AQ262" s="31" t="str"/>
       <x:c r="AR262" s="31" t="str"/>
       <x:c r="AS262" s="31" t="str"/>
-      <x:c r="AT262" s="37" t="str"/>
-      <x:c r="AU262" s="31" t="str"/>
-      <x:c r="AV262" s="31" t="str"/>
-      <x:c r="AW262" s="31" t="str"/>
-      <x:c r="AX262" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY262" s="31" t="str">
+      <x:c r="AT262" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU262" s="31" t="str">
         <x:v>Playwright</x:v>
       </x:c>
-      <x:c r="AZ262" s="31" t="str">
+      <x:c r="AV262" s="31" t="str">
         <x:v>Bereits auditierter Datensatz einer stark identifizierten Publikationsfassung</x:v>
       </x:c>
     </x:row>
@@ -23953,17 +22945,13 @@
       <x:c r="AQ263" s="31" t="str"/>
       <x:c r="AR263" s="31" t="str"/>
       <x:c r="AS263" s="31" t="str"/>
-      <x:c r="AT263" s="37" t="str"/>
-      <x:c r="AU263" s="31" t="str"/>
-      <x:c r="AV263" s="31" t="str"/>
-      <x:c r="AW263" s="31" t="str"/>
-      <x:c r="AX263" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY263" s="31" t="str">
+      <x:c r="AT263" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU263" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ263" s="31" t="str">
+      <x:c r="AV263" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -24039,17 +23027,13 @@
       <x:c r="AQ264" s="31" t="str"/>
       <x:c r="AR264" s="31" t="str"/>
       <x:c r="AS264" s="31" t="str"/>
-      <x:c r="AT264" s="37" t="str"/>
-      <x:c r="AU264" s="31" t="str"/>
-      <x:c r="AV264" s="31" t="str"/>
-      <x:c r="AW264" s="31" t="str"/>
-      <x:c r="AX264" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY264" s="31" t="str">
+      <x:c r="AT264" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU264" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ264" s="31" t="str">
+      <x:c r="AV264" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -24123,17 +23107,13 @@
       <x:c r="AQ265" s="31" t="str"/>
       <x:c r="AR265" s="31" t="str"/>
       <x:c r="AS265" s="31" t="str"/>
-      <x:c r="AT265" s="37" t="str"/>
-      <x:c r="AU265" s="31" t="str"/>
-      <x:c r="AV265" s="31" t="str"/>
-      <x:c r="AW265" s="31" t="str"/>
-      <x:c r="AX265" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY265" s="31" t="str">
+      <x:c r="AT265" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU265" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ265" s="31" t="str">
+      <x:c r="AV265" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -24209,17 +23189,13 @@
       <x:c r="AQ266" s="31" t="str"/>
       <x:c r="AR266" s="31" t="str"/>
       <x:c r="AS266" s="31" t="str"/>
-      <x:c r="AT266" s="37" t="str"/>
-      <x:c r="AU266" s="31" t="str"/>
-      <x:c r="AV266" s="31" t="str"/>
-      <x:c r="AW266" s="31" t="str"/>
-      <x:c r="AX266" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY266" s="31" t="str">
+      <x:c r="AT266" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU266" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ266" s="31" t="str">
+      <x:c r="AV266" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -24293,17 +23269,13 @@
       <x:c r="AQ267" s="31" t="str"/>
       <x:c r="AR267" s="31" t="str"/>
       <x:c r="AS267" s="31" t="str"/>
-      <x:c r="AT267" s="37" t="str"/>
-      <x:c r="AU267" s="31" t="str"/>
-      <x:c r="AV267" s="31" t="str"/>
-      <x:c r="AW267" s="31" t="str"/>
-      <x:c r="AX267" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY267" s="31" t="str">
+      <x:c r="AT267" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU267" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ267" s="31" t="str">
+      <x:c r="AV267" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -24377,17 +23349,13 @@
       <x:c r="AQ268" s="31" t="str"/>
       <x:c r="AR268" s="31" t="str"/>
       <x:c r="AS268" s="31" t="str"/>
-      <x:c r="AT268" s="37" t="str"/>
-      <x:c r="AU268" s="31" t="str"/>
-      <x:c r="AV268" s="31" t="str"/>
-      <x:c r="AW268" s="31" t="str"/>
-      <x:c r="AX268" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY268" s="31" t="str">
+      <x:c r="AT268" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU268" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ268" s="31" t="str">
+      <x:c r="AV268" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -24471,17 +23439,13 @@
       <x:c r="AQ269" s="31" t="str"/>
       <x:c r="AR269" s="31" t="str"/>
       <x:c r="AS269" s="31" t="str"/>
-      <x:c r="AT269" s="37" t="str"/>
-      <x:c r="AU269" s="31" t="str"/>
-      <x:c r="AV269" s="31" t="str"/>
-      <x:c r="AW269" s="31" t="str"/>
-      <x:c r="AX269" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY269" s="31" t="str">
+      <x:c r="AT269" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU269" s="31" t="str">
         <x:v>HTTP</x:v>
       </x:c>
-      <x:c r="AZ269" s="31" t="str">
+      <x:c r="AV269" s="31" t="str">
         <x:v>Titel-/Autor:innen-Match (1.00)</x:v>
       </x:c>
     </x:row>
@@ -24555,17 +23519,13 @@
       <x:c r="AQ270" s="31" t="str"/>
       <x:c r="AR270" s="31" t="str"/>
       <x:c r="AS270" s="31" t="str"/>
-      <x:c r="AT270" s="37" t="str"/>
-      <x:c r="AU270" s="31" t="str"/>
-      <x:c r="AV270" s="31" t="str"/>
-      <x:c r="AW270" s="31" t="str"/>
-      <x:c r="AX270" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY270" s="31" t="str">
+      <x:c r="AT270" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU270" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ270" s="31" t="str">
+      <x:c r="AV270" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -24639,17 +23599,13 @@
       <x:c r="AQ271" s="31" t="str"/>
       <x:c r="AR271" s="31" t="str"/>
       <x:c r="AS271" s="31" t="str"/>
-      <x:c r="AT271" s="37" t="str"/>
-      <x:c r="AU271" s="31" t="str"/>
-      <x:c r="AV271" s="31" t="str"/>
-      <x:c r="AW271" s="31" t="str"/>
-      <x:c r="AX271" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY271" s="31" t="str">
+      <x:c r="AT271" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU271" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ271" s="31" t="str">
+      <x:c r="AV271" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -24723,17 +23679,13 @@
       <x:c r="AQ272" s="31" t="str"/>
       <x:c r="AR272" s="31" t="str"/>
       <x:c r="AS272" s="31" t="str"/>
-      <x:c r="AT272" s="37" t="str"/>
-      <x:c r="AU272" s="31" t="str"/>
-      <x:c r="AV272" s="31" t="str"/>
-      <x:c r="AW272" s="31" t="str"/>
-      <x:c r="AX272" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY272" s="31" t="str">
+      <x:c r="AT272" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU272" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ272" s="31" t="str">
+      <x:c r="AV272" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -24817,17 +23769,13 @@
       <x:c r="AQ273" s="31" t="str"/>
       <x:c r="AR273" s="31" t="str"/>
       <x:c r="AS273" s="31" t="str"/>
-      <x:c r="AT273" s="37" t="str"/>
-      <x:c r="AU273" s="31" t="str"/>
-      <x:c r="AV273" s="31" t="str"/>
-      <x:c r="AW273" s="31" t="str"/>
-      <x:c r="AX273" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY273" s="31" t="str">
+      <x:c r="AT273" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU273" s="31" t="str">
         <x:v>Playwright</x:v>
       </x:c>
-      <x:c r="AZ273" s="31" t="str">
+      <x:c r="AV273" s="31" t="str">
         <x:v>Titel-/Autor:innen-Match (0.89)</x:v>
       </x:c>
     </x:row>
@@ -24901,17 +23849,13 @@
       <x:c r="AQ274" s="31" t="str"/>
       <x:c r="AR274" s="31" t="str"/>
       <x:c r="AS274" s="31" t="str"/>
-      <x:c r="AT274" s="37" t="str"/>
-      <x:c r="AU274" s="31" t="str"/>
-      <x:c r="AV274" s="31" t="str"/>
-      <x:c r="AW274" s="31" t="str"/>
-      <x:c r="AX274" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY274" s="31" t="str">
+      <x:c r="AT274" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU274" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ274" s="31" t="str">
+      <x:c r="AV274" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -24985,17 +23929,13 @@
       <x:c r="AQ275" s="31" t="str"/>
       <x:c r="AR275" s="31" t="str"/>
       <x:c r="AS275" s="31" t="str"/>
-      <x:c r="AT275" s="37" t="str"/>
-      <x:c r="AU275" s="31" t="str"/>
-      <x:c r="AV275" s="31" t="str"/>
-      <x:c r="AW275" s="31" t="str"/>
-      <x:c r="AX275" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY275" s="31" t="str">
+      <x:c r="AT275" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU275" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ275" s="31" t="str">
+      <x:c r="AV275" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -25071,17 +24011,13 @@
       <x:c r="AQ276" s="31" t="str"/>
       <x:c r="AR276" s="31" t="str"/>
       <x:c r="AS276" s="31" t="str"/>
-      <x:c r="AT276" s="37" t="str"/>
-      <x:c r="AU276" s="31" t="str"/>
-      <x:c r="AV276" s="31" t="str"/>
-      <x:c r="AW276" s="31" t="str"/>
-      <x:c r="AX276" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY276" s="31" t="str">
+      <x:c r="AT276" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU276" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ276" s="31" t="str">
+      <x:c r="AV276" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -25157,17 +24093,13 @@
       <x:c r="AQ277" s="31" t="str"/>
       <x:c r="AR277" s="31" t="str"/>
       <x:c r="AS277" s="31" t="str"/>
-      <x:c r="AT277" s="37" t="str"/>
-      <x:c r="AU277" s="31" t="str"/>
-      <x:c r="AV277" s="31" t="str"/>
-      <x:c r="AW277" s="31" t="str"/>
-      <x:c r="AX277" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY277" s="31" t="str">
+      <x:c r="AT277" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU277" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ277" s="31" t="str">
+      <x:c r="AV277" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -25243,17 +24175,13 @@
       <x:c r="AQ278" s="31" t="str"/>
       <x:c r="AR278" s="31" t="str"/>
       <x:c r="AS278" s="31" t="str"/>
-      <x:c r="AT278" s="37" t="str"/>
-      <x:c r="AU278" s="31" t="str"/>
-      <x:c r="AV278" s="31" t="str"/>
-      <x:c r="AW278" s="31" t="str"/>
-      <x:c r="AX278" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY278" s="31" t="str">
+      <x:c r="AT278" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU278" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ278" s="31" t="str">
+      <x:c r="AV278" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -25329,17 +24257,13 @@
       <x:c r="AQ279" s="31" t="str"/>
       <x:c r="AR279" s="31" t="str"/>
       <x:c r="AS279" s="31" t="str"/>
-      <x:c r="AT279" s="37" t="str"/>
-      <x:c r="AU279" s="31" t="str"/>
-      <x:c r="AV279" s="31" t="str"/>
-      <x:c r="AW279" s="31" t="str"/>
-      <x:c r="AX279" s="31" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY279" s="31" t="str">
+      <x:c r="AT279" s="31" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU279" s="31" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ279" s="31" t="str">
+      <x:c r="AV279" s="31" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
@@ -25415,24 +24339,20 @@
       <x:c r="AQ280" s="34" t="str"/>
       <x:c r="AR280" s="34" t="str"/>
       <x:c r="AS280" s="34" t="str"/>
-      <x:c r="AT280" s="38" t="str"/>
-      <x:c r="AU280" s="34" t="str"/>
-      <x:c r="AV280" s="34" t="str"/>
-      <x:c r="AW280" s="34" t="str"/>
-      <x:c r="AX280" s="34" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="AY280" s="34" t="str">
+      <x:c r="AT280" s="34" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="AU280" s="34" t="str">
         <x:v>HTTP + Playwright-Audit</x:v>
       </x:c>
-      <x:c r="AZ280" s="34" t="str">
+      <x:c r="AV280" s="34" t="str">
         <x:v>Keine verifizierten Forschungsdaten gefunden</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14488b790c734584"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8efb0480ff824de1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25492,13 +24412,13 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="C4" s="29" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D4" s="29" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E4" s="48" t="n">
-        <x:v>0.5555555555555556</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
       <x:c r="F4" s="29" t="n">
         <x:v>3</x:v>
@@ -25515,19 +24435,19 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="C5" s="31" t="n">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D5" s="31" t="n">
-        <x:v>96</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E5" s="49" t="n">
-        <x:v>0.1864406779661017</x:v>
+        <x:v>0.2033898305084746</x:v>
       </x:c>
       <x:c r="F5" s="31" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G5" s="31" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="28" customHeight="1">
@@ -25699,13 +24619,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C13" s="34" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D13" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E13" s="50" t="n">
         <x:v>1</x:v>
-      </x:c>
-      <x:c r="E13" s="50" t="n">
-        <x:v>0.6666666666666666</x:v>
       </x:c>
       <x:c r="F13" s="34" t="n">
         <x:v>0</x:v>
@@ -25747,7 +24667,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbef09546561d4f55"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3bdcc0108ae4881"/>
   </x:tableParts>
 </x:worksheet>
 </file>